--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122289712</v>
+        <v>122289595</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472971</v>
+        <v>472813</v>
       </c>
       <c r="R20" t="n">
-        <v>6815298</v>
+        <v>6815369</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122289699</v>
+        <v>122289602</v>
       </c>
       <c r="B21" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473050</v>
+        <v>472810</v>
       </c>
       <c r="R21" t="n">
-        <v>6815098</v>
+        <v>6815367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122289752</v>
+        <v>122289712</v>
       </c>
       <c r="B22" t="n">
         <v>78645</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473224</v>
+        <v>472971</v>
       </c>
       <c r="R22" t="n">
-        <v>6815578</v>
+        <v>6815298</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122289689</v>
+        <v>122289699</v>
       </c>
       <c r="B23" t="n">
         <v>78645</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472954</v>
+        <v>473050</v>
       </c>
       <c r="R23" t="n">
-        <v>6815041</v>
+        <v>6815098</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122289740</v>
+        <v>122289752</v>
       </c>
       <c r="B24" t="n">
         <v>78645</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473153</v>
+        <v>473224</v>
       </c>
       <c r="R24" t="n">
-        <v>6815381</v>
+        <v>6815578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122289664</v>
+        <v>122289689</v>
       </c>
       <c r="B25" t="n">
         <v>78645</v>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472722</v>
+        <v>472954</v>
       </c>
       <c r="R25" t="n">
-        <v>6815115</v>
+        <v>6815041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122289495</v>
+        <v>122289740</v>
       </c>
       <c r="B26" t="n">
-        <v>74747</v>
+        <v>78645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473212</v>
+        <v>473153</v>
       </c>
       <c r="R26" t="n">
-        <v>6815464</v>
+        <v>6815381</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122289476</v>
+        <v>122289664</v>
       </c>
       <c r="B27" t="n">
-        <v>79263</v>
+        <v>78645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472813</v>
+        <v>472722</v>
       </c>
       <c r="R27" t="n">
-        <v>6815369</v>
+        <v>6815115</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122289595</v>
+        <v>122289495</v>
       </c>
       <c r="B28" t="n">
-        <v>78382</v>
+        <v>74747</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3415,21 +3415,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472813</v>
+        <v>473212</v>
       </c>
       <c r="R28" t="n">
-        <v>6815369</v>
+        <v>6815464</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122289602</v>
+        <v>122289476</v>
       </c>
       <c r="B29" t="n">
-        <v>78382</v>
+        <v>79263</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3517,21 +3517,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472810</v>
+        <v>472813</v>
       </c>
       <c r="R29" t="n">
-        <v>6815367</v>
+        <v>6815369</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289600</v>
+        <v>122289550</v>
       </c>
       <c r="B33" t="n">
-        <v>78382</v>
+        <v>79727</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3925,21 +3925,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472822</v>
+        <v>473037</v>
       </c>
       <c r="R33" t="n">
-        <v>6815541</v>
+        <v>6815182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122289603</v>
+        <v>122289756</v>
       </c>
       <c r="B34" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472794</v>
+        <v>473239</v>
       </c>
       <c r="R34" t="n">
-        <v>6815363</v>
+        <v>6815673</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122289528</v>
+        <v>122289619</v>
       </c>
       <c r="B35" t="n">
-        <v>79234</v>
+        <v>78645</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473019</v>
+        <v>473228</v>
       </c>
       <c r="R35" t="n">
-        <v>6815730</v>
+        <v>6815569</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122289550</v>
+        <v>122289738</v>
       </c>
       <c r="B36" t="n">
-        <v>79727</v>
+        <v>78645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473037</v>
+        <v>473045</v>
       </c>
       <c r="R36" t="n">
-        <v>6815182</v>
+        <v>6815390</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122289615</v>
+        <v>122289720</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4333,39 +4333,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472712</v>
+        <v>472902</v>
       </c>
       <c r="R37" t="n">
-        <v>6815141</v>
+        <v>6815343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4398,11 +4393,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4429,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122289589</v>
+        <v>122289539</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>90799</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4445,39 +4435,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472928</v>
+        <v>473229</v>
       </c>
       <c r="R38" t="n">
-        <v>6815346</v>
+        <v>6815569</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4510,11 +4495,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4541,7 +4521,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122289756</v>
+        <v>122289644</v>
       </c>
       <c r="B39" t="n">
         <v>78645</v>
@@ -4581,10 +4561,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473239</v>
+        <v>472872</v>
       </c>
       <c r="R39" t="n">
-        <v>6815673</v>
+        <v>6815410</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4643,7 +4623,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122289619</v>
+        <v>122289673</v>
       </c>
       <c r="B40" t="n">
         <v>78645</v>
@@ -4683,10 +4663,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473228</v>
+        <v>472729</v>
       </c>
       <c r="R40" t="n">
-        <v>6815569</v>
+        <v>6815062</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4745,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122289738</v>
+        <v>122289551</v>
       </c>
       <c r="B41" t="n">
-        <v>78645</v>
+        <v>79630</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4757,25 +4737,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4785,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473045</v>
+        <v>472884</v>
       </c>
       <c r="R41" t="n">
-        <v>6815390</v>
+        <v>6815478</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4847,7 +4827,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122289720</v>
+        <v>122289742</v>
       </c>
       <c r="B42" t="n">
         <v>78645</v>
@@ -4887,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472902</v>
+        <v>473186</v>
       </c>
       <c r="R42" t="n">
-        <v>6815343</v>
+        <v>6815462</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4949,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122289539</v>
+        <v>122289657</v>
       </c>
       <c r="B43" t="n">
-        <v>90799</v>
+        <v>78645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4965,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4989,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473229</v>
+        <v>472730</v>
       </c>
       <c r="R43" t="n">
-        <v>6815569</v>
+        <v>6815383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5051,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122289644</v>
+        <v>122289600</v>
       </c>
       <c r="B44" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5067,21 +5047,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5091,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472872</v>
+        <v>472822</v>
       </c>
       <c r="R44" t="n">
-        <v>6815410</v>
+        <v>6815541</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5153,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122289673</v>
+        <v>122289603</v>
       </c>
       <c r="B45" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5169,21 +5149,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5193,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472729</v>
+        <v>472794</v>
       </c>
       <c r="R45" t="n">
-        <v>6815062</v>
+        <v>6815363</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5255,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122289551</v>
+        <v>122289528</v>
       </c>
       <c r="B46" t="n">
-        <v>79630</v>
+        <v>79234</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5267,25 +5247,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5295,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472884</v>
+        <v>473019</v>
       </c>
       <c r="R46" t="n">
-        <v>6815478</v>
+        <v>6815730</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5357,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122289742</v>
+        <v>122289615</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5373,34 +5353,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473186</v>
+        <v>472712</v>
       </c>
       <c r="R47" t="n">
-        <v>6815462</v>
+        <v>6815141</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5433,6 +5418,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5459,10 +5449,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122289657</v>
+        <v>122289589</v>
       </c>
       <c r="B48" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5475,34 +5465,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472730</v>
+        <v>472928</v>
       </c>
       <c r="R48" t="n">
-        <v>6815383</v>
+        <v>6815346</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5535,6 +5530,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -8174,10 +8174,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289547</v>
+        <v>122289500</v>
       </c>
       <c r="B74" t="n">
-        <v>79727</v>
+        <v>78679</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472833</v>
+        <v>472769</v>
       </c>
       <c r="R74" t="n">
-        <v>6815619</v>
+        <v>6815363</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122289500</v>
+        <v>122289668</v>
       </c>
       <c r="B75" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8292,21 +8292,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472769</v>
+        <v>472718</v>
       </c>
       <c r="R75" t="n">
-        <v>6815363</v>
+        <v>6815026</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8378,10 +8378,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122289576</v>
+        <v>122289723</v>
       </c>
       <c r="B76" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8394,39 +8394,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>473233</v>
+        <v>472901</v>
       </c>
       <c r="R76" t="n">
-        <v>6815571</v>
+        <v>6815361</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8459,11 +8454,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8490,10 +8480,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122289562</v>
+        <v>122289671</v>
       </c>
       <c r="B77" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8506,39 +8496,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>472869</v>
+        <v>472713</v>
       </c>
       <c r="R77" t="n">
-        <v>6815446</v>
+        <v>6815067</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8571,11 +8556,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8602,10 +8582,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122289583</v>
+        <v>122289624</v>
       </c>
       <c r="B78" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8618,39 +8598,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472856</v>
+        <v>472913</v>
       </c>
       <c r="R78" t="n">
-        <v>6815150</v>
+        <v>6815662</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8683,11 +8658,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8714,7 +8684,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122289668</v>
+        <v>122289755</v>
       </c>
       <c r="B79" t="n">
         <v>78645</v>
@@ -8754,10 +8724,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>472718</v>
+        <v>473241</v>
       </c>
       <c r="R79" t="n">
-        <v>6815026</v>
+        <v>6815645</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8816,7 +8786,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122289723</v>
+        <v>122289672</v>
       </c>
       <c r="B80" t="n">
         <v>78645</v>
@@ -8856,10 +8826,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>472901</v>
+        <v>472720</v>
       </c>
       <c r="R80" t="n">
-        <v>6815361</v>
+        <v>6815067</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8918,7 +8888,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122289671</v>
+        <v>122289693</v>
       </c>
       <c r="B81" t="n">
         <v>78645</v>
@@ -8958,10 +8928,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>472713</v>
+        <v>473002</v>
       </c>
       <c r="R81" t="n">
-        <v>6815067</v>
+        <v>6814987</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9020,10 +8990,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122289624</v>
+        <v>122289547</v>
       </c>
       <c r="B82" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9036,21 +9006,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9060,10 +9030,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>472913</v>
+        <v>472833</v>
       </c>
       <c r="R82" t="n">
-        <v>6815662</v>
+        <v>6815619</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9122,10 +9092,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122289755</v>
+        <v>122289576</v>
       </c>
       <c r="B83" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9138,34 +9108,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>473241</v>
+        <v>473233</v>
       </c>
       <c r="R83" t="n">
-        <v>6815645</v>
+        <v>6815571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9198,6 +9173,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9224,10 +9204,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122289672</v>
+        <v>122289562</v>
       </c>
       <c r="B84" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9240,34 +9220,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>472720</v>
+        <v>472869</v>
       </c>
       <c r="R84" t="n">
-        <v>6815067</v>
+        <v>6815446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9300,6 +9285,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9326,10 +9316,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122289693</v>
+        <v>122289583</v>
       </c>
       <c r="B85" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9342,34 +9332,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>473002</v>
+        <v>472856</v>
       </c>
       <c r="R85" t="n">
-        <v>6814987</v>
+        <v>6815150</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9402,6 +9397,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9632,10 +9632,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122289516</v>
+        <v>122289651</v>
       </c>
       <c r="B88" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9648,21 +9648,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>473107</v>
+        <v>472821</v>
       </c>
       <c r="R88" t="n">
-        <v>6815366</v>
+        <v>6815364</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122289506</v>
+        <v>122289687</v>
       </c>
       <c r="B89" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>473050</v>
+        <v>472899</v>
       </c>
       <c r="R89" t="n">
-        <v>6815098</v>
+        <v>6815079</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122289525</v>
+        <v>122289674</v>
       </c>
       <c r="B90" t="n">
-        <v>95722</v>
+        <v>78645</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9852,21 +9852,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>472724</v>
+        <v>472736</v>
       </c>
       <c r="R90" t="n">
-        <v>6815100</v>
+        <v>6815067</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9938,10 +9938,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122289504</v>
+        <v>122289698</v>
       </c>
       <c r="B91" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9954,21 +9954,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>472835</v>
+        <v>473037</v>
       </c>
       <c r="R91" t="n">
-        <v>6815089</v>
+        <v>6815086</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10040,10 +10040,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122289509</v>
+        <v>122289729</v>
       </c>
       <c r="B92" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10056,21 +10056,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>473014</v>
+        <v>472957</v>
       </c>
       <c r="R92" t="n">
-        <v>6815194</v>
+        <v>6815421</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10142,10 +10142,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122289581</v>
+        <v>122289667</v>
       </c>
       <c r="B93" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10158,39 +10158,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>472821</v>
+        <v>472741</v>
       </c>
       <c r="R93" t="n">
-        <v>6815364</v>
+        <v>6815075</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10223,11 +10218,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10254,10 +10244,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122289572</v>
+        <v>122289634</v>
       </c>
       <c r="B94" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10270,39 +10260,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>472916</v>
+        <v>472785</v>
       </c>
       <c r="R94" t="n">
-        <v>6815362</v>
+        <v>6815675</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10335,11 +10320,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10366,10 +10346,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122289564</v>
+        <v>122289647</v>
       </c>
       <c r="B95" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10382,39 +10362,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>472724</v>
+        <v>472878</v>
       </c>
       <c r="R95" t="n">
-        <v>6815345</v>
+        <v>6815322</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10447,11 +10422,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10478,10 +10448,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122289555</v>
+        <v>122289676</v>
       </c>
       <c r="B96" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10494,39 +10464,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>473055</v>
+        <v>472759</v>
       </c>
       <c r="R96" t="n">
-        <v>6815710</v>
+        <v>6815052</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10559,11 +10524,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10590,10 +10550,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122289585</v>
+        <v>122289666</v>
       </c>
       <c r="B97" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10606,39 +10566,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>473030</v>
+        <v>472737</v>
       </c>
       <c r="R97" t="n">
-        <v>6815053</v>
+        <v>6815084</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10671,11 +10626,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10702,10 +10652,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122289651</v>
+        <v>122289516</v>
       </c>
       <c r="B98" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10718,21 +10668,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10742,10 +10692,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>472821</v>
+        <v>473107</v>
       </c>
       <c r="R98" t="n">
-        <v>6815364</v>
+        <v>6815366</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10804,10 +10754,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122289687</v>
+        <v>122289506</v>
       </c>
       <c r="B99" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10820,21 +10770,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10844,10 +10794,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>472899</v>
+        <v>473050</v>
       </c>
       <c r="R99" t="n">
-        <v>6815079</v>
+        <v>6815098</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10906,10 +10856,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122289674</v>
+        <v>122289525</v>
       </c>
       <c r="B100" t="n">
-        <v>78645</v>
+        <v>95722</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10922,21 +10872,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10946,10 +10896,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472736</v>
+        <v>472724</v>
       </c>
       <c r="R100" t="n">
-        <v>6815067</v>
+        <v>6815100</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11008,10 +10958,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122289698</v>
+        <v>122289504</v>
       </c>
       <c r="B101" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11024,21 +10974,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11048,10 +10998,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>473037</v>
+        <v>472835</v>
       </c>
       <c r="R101" t="n">
-        <v>6815086</v>
+        <v>6815089</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11110,10 +11060,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122289729</v>
+        <v>122289509</v>
       </c>
       <c r="B102" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11126,21 +11076,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11150,10 +11100,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>472957</v>
+        <v>473014</v>
       </c>
       <c r="R102" t="n">
-        <v>6815421</v>
+        <v>6815194</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11212,10 +11162,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122289667</v>
+        <v>122289609</v>
       </c>
       <c r="B103" t="n">
-        <v>78645</v>
+        <v>80602</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11228,21 +11178,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11252,10 +11202,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472741</v>
+        <v>472975</v>
       </c>
       <c r="R103" t="n">
-        <v>6815075</v>
+        <v>6815664</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11314,10 +11264,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122289634</v>
+        <v>122289581</v>
       </c>
       <c r="B104" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11330,34 +11280,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472785</v>
+        <v>472821</v>
       </c>
       <c r="R104" t="n">
-        <v>6815675</v>
+        <v>6815364</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11390,6 +11345,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11416,10 +11376,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122289647</v>
+        <v>122289572</v>
       </c>
       <c r="B105" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11432,34 +11392,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472878</v>
+        <v>472916</v>
       </c>
       <c r="R105" t="n">
-        <v>6815322</v>
+        <v>6815362</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11492,6 +11457,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11518,10 +11488,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122289676</v>
+        <v>122289564</v>
       </c>
       <c r="B106" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11534,34 +11504,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472759</v>
+        <v>472724</v>
       </c>
       <c r="R106" t="n">
-        <v>6815052</v>
+        <v>6815345</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11594,6 +11569,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11620,10 +11600,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122289666</v>
+        <v>122289555</v>
       </c>
       <c r="B107" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11636,34 +11616,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>472737</v>
+        <v>473055</v>
       </c>
       <c r="R107" t="n">
-        <v>6815084</v>
+        <v>6815710</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11696,6 +11681,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11722,10 +11712,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122289609</v>
+        <v>122289585</v>
       </c>
       <c r="B108" t="n">
-        <v>80602</v>
+        <v>57374</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11738,34 +11728,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472975</v>
+        <v>473030</v>
       </c>
       <c r="R108" t="n">
-        <v>6815664</v>
+        <v>6815053</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11798,6 +11793,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11824,10 +11824,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122289715</v>
+        <v>122289512</v>
       </c>
       <c r="B109" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11840,21 +11840,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472966</v>
+        <v>472977</v>
       </c>
       <c r="R109" t="n">
-        <v>6815390</v>
+        <v>6815273</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11926,10 +11926,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122289661</v>
+        <v>122289515</v>
       </c>
       <c r="B110" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11942,21 +11942,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>472693</v>
+        <v>473035</v>
       </c>
       <c r="R110" t="n">
-        <v>6815202</v>
+        <v>6815416</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12028,10 +12028,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122289681</v>
+        <v>122289594</v>
       </c>
       <c r="B111" t="n">
-        <v>78645</v>
+        <v>74742</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12044,21 +12044,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12071,7 +12071,7 @@
         <v>472834</v>
       </c>
       <c r="R111" t="n">
-        <v>6815094</v>
+        <v>6815612</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12130,10 +12130,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122289552</v>
+        <v>122289546</v>
       </c>
       <c r="B112" t="n">
-        <v>79630</v>
+        <v>57390</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12142,38 +12142,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>472870</v>
+        <v>472731</v>
       </c>
       <c r="R112" t="n">
-        <v>6815440</v>
+        <v>6815088</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12232,7 +12237,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122289730</v>
+        <v>122289715</v>
       </c>
       <c r="B113" t="n">
         <v>78645</v>
@@ -12272,10 +12277,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>472958</v>
+        <v>472966</v>
       </c>
       <c r="R113" t="n">
-        <v>6815427</v>
+        <v>6815390</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12334,7 +12339,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122289663</v>
+        <v>122289661</v>
       </c>
       <c r="B114" t="n">
         <v>78645</v>
@@ -12374,10 +12379,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>472719</v>
+        <v>472693</v>
       </c>
       <c r="R114" t="n">
-        <v>6815128</v>
+        <v>6815202</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12436,7 +12441,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122289640</v>
+        <v>122289681</v>
       </c>
       <c r="B115" t="n">
         <v>78645</v>
@@ -12476,10 +12481,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>472893</v>
+        <v>472834</v>
       </c>
       <c r="R115" t="n">
-        <v>6815451</v>
+        <v>6815094</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12538,10 +12543,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122289627</v>
+        <v>122289552</v>
       </c>
       <c r="B116" t="n">
-        <v>78645</v>
+        <v>79630</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12550,25 +12555,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12578,10 +12583,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>472837</v>
+        <v>472870</v>
       </c>
       <c r="R116" t="n">
-        <v>6815704</v>
+        <v>6815440</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12640,7 +12645,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122289679</v>
+        <v>122289730</v>
       </c>
       <c r="B117" t="n">
         <v>78645</v>
@@ -12680,10 +12685,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>472779</v>
+        <v>472958</v>
       </c>
       <c r="R117" t="n">
-        <v>6815051</v>
+        <v>6815427</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12742,10 +12747,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122289512</v>
+        <v>122289663</v>
       </c>
       <c r="B118" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12758,21 +12763,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12782,10 +12787,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>472977</v>
+        <v>472719</v>
       </c>
       <c r="R118" t="n">
-        <v>6815273</v>
+        <v>6815128</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12844,10 +12849,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122289515</v>
+        <v>122289640</v>
       </c>
       <c r="B119" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12860,21 +12865,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12884,10 +12889,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>473035</v>
+        <v>472893</v>
       </c>
       <c r="R119" t="n">
-        <v>6815416</v>
+        <v>6815451</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12946,10 +12951,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122289594</v>
+        <v>122289627</v>
       </c>
       <c r="B120" t="n">
-        <v>74742</v>
+        <v>78645</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12962,21 +12967,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12986,10 +12991,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>472834</v>
+        <v>472837</v>
       </c>
       <c r="R120" t="n">
-        <v>6815612</v>
+        <v>6815704</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13048,10 +13053,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122289546</v>
+        <v>122289679</v>
       </c>
       <c r="B121" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13064,39 +13069,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>472731</v>
+        <v>472779</v>
       </c>
       <c r="R121" t="n">
-        <v>6815088</v>
+        <v>6815051</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -18482,10 +18482,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122289493</v>
+        <v>122289598</v>
       </c>
       <c r="B173" t="n">
-        <v>74747</v>
+        <v>78382</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18498,21 +18498,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18522,10 +18522,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>473003</v>
+        <v>473022</v>
       </c>
       <c r="R173" t="n">
-        <v>6814987</v>
+        <v>6815732</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18584,10 +18584,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122289767</v>
+        <v>122289511</v>
       </c>
       <c r="B174" t="n">
-        <v>90797</v>
+        <v>78679</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18600,21 +18600,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18624,10 +18624,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>472819</v>
+        <v>472998</v>
       </c>
       <c r="R174" t="n">
-        <v>6815624</v>
+        <v>6815243</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18686,10 +18686,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122289749</v>
+        <v>122289501</v>
       </c>
       <c r="B175" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18702,21 +18702,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18726,10 +18726,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>473236</v>
+        <v>472722</v>
       </c>
       <c r="R175" t="n">
-        <v>6815526</v>
+        <v>6815373</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18788,10 +18788,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122289774</v>
+        <v>122289538</v>
       </c>
       <c r="B176" t="n">
-        <v>78029</v>
+        <v>57527</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18804,21 +18804,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18828,10 +18828,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>473192</v>
+        <v>472787</v>
       </c>
       <c r="R176" t="n">
-        <v>6815503</v>
+        <v>6815675</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18890,10 +18890,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122289688</v>
+        <v>122289493</v>
       </c>
       <c r="B177" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18906,21 +18906,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18930,10 +18930,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>472911</v>
+        <v>473003</v>
       </c>
       <c r="R177" t="n">
-        <v>6815063</v>
+        <v>6814987</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18992,10 +18992,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122289745</v>
+        <v>122289767</v>
       </c>
       <c r="B178" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19008,21 +19008,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19032,10 +19032,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>473190</v>
+        <v>472819</v>
       </c>
       <c r="R178" t="n">
-        <v>6815498</v>
+        <v>6815624</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122289732</v>
+        <v>122289749</v>
       </c>
       <c r="B179" t="n">
         <v>78645</v>
@@ -19134,10 +19134,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>472971</v>
+        <v>473236</v>
       </c>
       <c r="R179" t="n">
-        <v>6815467</v>
+        <v>6815526</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19196,10 +19196,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122289711</v>
+        <v>122289774</v>
       </c>
       <c r="B180" t="n">
-        <v>78645</v>
+        <v>78029</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19212,21 +19212,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19236,10 +19236,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>472976</v>
+        <v>473192</v>
       </c>
       <c r="R180" t="n">
-        <v>6815272</v>
+        <v>6815503</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19298,10 +19298,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122289598</v>
+        <v>122289688</v>
       </c>
       <c r="B181" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19314,21 +19314,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19338,10 +19338,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>473022</v>
+        <v>472911</v>
       </c>
       <c r="R181" t="n">
-        <v>6815732</v>
+        <v>6815063</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19400,10 +19400,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122289511</v>
+        <v>122289745</v>
       </c>
       <c r="B182" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19416,21 +19416,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>472998</v>
+        <v>473190</v>
       </c>
       <c r="R182" t="n">
-        <v>6815243</v>
+        <v>6815498</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19502,10 +19502,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289501</v>
+        <v>122289732</v>
       </c>
       <c r="B183" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19518,21 +19518,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19542,10 +19542,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>472722</v>
+        <v>472971</v>
       </c>
       <c r="R183" t="n">
-        <v>6815373</v>
+        <v>6815467</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19604,10 +19604,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289538</v>
+        <v>122289711</v>
       </c>
       <c r="B184" t="n">
-        <v>57527</v>
+        <v>78645</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19620,21 +19620,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19644,10 +19644,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>472787</v>
+        <v>472976</v>
       </c>
       <c r="R184" t="n">
-        <v>6815675</v>
+        <v>6815272</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21903,10 +21903,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122289692</v>
+        <v>122289529</v>
       </c>
       <c r="B206" t="n">
-        <v>78645</v>
+        <v>79234</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21919,21 +21919,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21943,10 +21943,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>472970</v>
+        <v>472881</v>
       </c>
       <c r="R206" t="n">
-        <v>6814989</v>
+        <v>6815396</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22005,7 +22005,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122289726</v>
+        <v>122289692</v>
       </c>
       <c r="B207" t="n">
         <v>78645</v>
@@ -22045,10 +22045,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>472934</v>
+        <v>472970</v>
       </c>
       <c r="R207" t="n">
-        <v>6815384</v>
+        <v>6814989</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22107,7 +22107,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122289639</v>
+        <v>122289726</v>
       </c>
       <c r="B208" t="n">
         <v>78645</v>
@@ -22147,10 +22147,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>472869</v>
+        <v>472934</v>
       </c>
       <c r="R208" t="n">
-        <v>6815500</v>
+        <v>6815384</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22209,7 +22209,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122289636</v>
+        <v>122289639</v>
       </c>
       <c r="B209" t="n">
         <v>78645</v>
@@ -22249,10 +22249,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>472843</v>
+        <v>472869</v>
       </c>
       <c r="R209" t="n">
-        <v>6815598</v>
+        <v>6815500</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22311,7 +22311,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122289635</v>
+        <v>122289636</v>
       </c>
       <c r="B210" t="n">
         <v>78645</v>
@@ -22351,10 +22351,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>472819</v>
+        <v>472843</v>
       </c>
       <c r="R210" t="n">
-        <v>6815642</v>
+        <v>6815598</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22413,10 +22413,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289618</v>
+        <v>122289635</v>
       </c>
       <c r="B211" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22429,21 +22429,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22453,10 +22453,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>473257</v>
+        <v>472819</v>
       </c>
       <c r="R211" t="n">
-        <v>6815716</v>
+        <v>6815642</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22515,10 +22515,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289685</v>
+        <v>122289618</v>
       </c>
       <c r="B212" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22531,21 +22531,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22555,10 +22555,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>472881</v>
+        <v>473257</v>
       </c>
       <c r="R212" t="n">
-        <v>6815128</v>
+        <v>6815716</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22617,7 +22617,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289750</v>
+        <v>122289685</v>
       </c>
       <c r="B213" t="n">
         <v>78645</v>
@@ -22657,10 +22657,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>473232</v>
+        <v>472881</v>
       </c>
       <c r="R213" t="n">
-        <v>6815538</v>
+        <v>6815128</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22719,7 +22719,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289633</v>
+        <v>122289750</v>
       </c>
       <c r="B214" t="n">
         <v>78645</v>
@@ -22759,10 +22759,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>472766</v>
+        <v>473232</v>
       </c>
       <c r="R214" t="n">
-        <v>6815686</v>
+        <v>6815538</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22821,10 +22821,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289490</v>
+        <v>122289633</v>
       </c>
       <c r="B215" t="n">
-        <v>74747</v>
+        <v>78645</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22837,21 +22837,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>472713</v>
+        <v>472766</v>
       </c>
       <c r="R215" t="n">
-        <v>6815143</v>
+        <v>6815686</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22923,10 +22923,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289751</v>
+        <v>122289490</v>
       </c>
       <c r="B216" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22939,21 +22939,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22963,10 +22963,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>473230</v>
+        <v>472713</v>
       </c>
       <c r="R216" t="n">
-        <v>6815539</v>
+        <v>6815143</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23025,7 +23025,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289705</v>
+        <v>122289751</v>
       </c>
       <c r="B217" t="n">
         <v>78645</v>
@@ -23065,10 +23065,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>473019</v>
+        <v>473230</v>
       </c>
       <c r="R217" t="n">
-        <v>6815163</v>
+        <v>6815539</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23127,7 +23127,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122289735</v>
+        <v>122289705</v>
       </c>
       <c r="B218" t="n">
         <v>78645</v>
@@ -23167,10 +23167,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>473015</v>
+        <v>473019</v>
       </c>
       <c r="R218" t="n">
-        <v>6815443</v>
+        <v>6815163</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23229,10 +23229,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289483</v>
+        <v>122289735</v>
       </c>
       <c r="B219" t="n">
-        <v>79263</v>
+        <v>78645</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23245,21 +23245,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23269,10 +23269,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>472999</v>
+        <v>473015</v>
       </c>
       <c r="R219" t="n">
-        <v>6815197</v>
+        <v>6815443</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23331,10 +23331,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289721</v>
+        <v>122289483</v>
       </c>
       <c r="B220" t="n">
-        <v>78645</v>
+        <v>79263</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23347,21 +23347,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23371,10 +23371,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>472897</v>
+        <v>472999</v>
       </c>
       <c r="R220" t="n">
-        <v>6815355</v>
+        <v>6815197</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23433,10 +23433,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289529</v>
+        <v>122289721</v>
       </c>
       <c r="B221" t="n">
-        <v>79234</v>
+        <v>78645</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23449,21 +23449,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23473,10 +23473,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>472881</v>
+        <v>472897</v>
       </c>
       <c r="R221" t="n">
-        <v>6815396</v>
+        <v>6815355</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -7733,10 +7733,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289558</v>
+        <v>122289636</v>
       </c>
       <c r="B70" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7749,39 +7749,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472954</v>
+        <v>472843</v>
       </c>
       <c r="R70" t="n">
-        <v>6815040</v>
+        <v>6815598</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7814,11 +7809,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7845,10 +7835,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289534</v>
+        <v>122289767</v>
       </c>
       <c r="B71" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7861,39 +7851,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472993</v>
+        <v>472819</v>
       </c>
       <c r="R71" t="n">
-        <v>6814991</v>
+        <v>6815624</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7952,10 +7937,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122289591</v>
+        <v>122289714</v>
       </c>
       <c r="B72" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7968,39 +7953,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>473243</v>
+        <v>472966</v>
       </c>
       <c r="R72" t="n">
-        <v>6815620</v>
+        <v>6815345</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8033,11 +8013,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8064,10 +8039,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122289612</v>
+        <v>122289693</v>
       </c>
       <c r="B73" t="n">
-        <v>78382</v>
+        <v>78646</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8080,21 +8055,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8104,10 +8079,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472742</v>
+        <v>473002</v>
       </c>
       <c r="R73" t="n">
-        <v>6815075</v>
+        <v>6814987</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8166,10 +8141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289636</v>
+        <v>122289612</v>
       </c>
       <c r="B74" t="n">
-        <v>78646</v>
+        <v>78382</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8182,21 +8157,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8206,10 +8181,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472843</v>
+        <v>472742</v>
       </c>
       <c r="R74" t="n">
-        <v>6815598</v>
+        <v>6815075</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8268,10 +8243,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122289767</v>
+        <v>122289558</v>
       </c>
       <c r="B75" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8284,34 +8259,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472819</v>
+        <v>472954</v>
       </c>
       <c r="R75" t="n">
-        <v>6815624</v>
+        <v>6815040</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8344,6 +8324,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8370,10 +8355,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122289714</v>
+        <v>122289534</v>
       </c>
       <c r="B76" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8386,34 +8371,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472966</v>
+        <v>472993</v>
       </c>
       <c r="R76" t="n">
-        <v>6815345</v>
+        <v>6814991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8472,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122289693</v>
+        <v>122289591</v>
       </c>
       <c r="B77" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8488,34 +8478,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>473002</v>
+        <v>473243</v>
       </c>
       <c r="R77" t="n">
-        <v>6814987</v>
+        <v>6815620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8548,6 +8543,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -15603,10 +15603,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122289516</v>
+        <v>122289697</v>
       </c>
       <c r="B146" t="n">
-        <v>78680</v>
+        <v>78646</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15619,21 +15619,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15643,10 +15643,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>473107</v>
+        <v>473033</v>
       </c>
       <c r="R146" t="n">
-        <v>6815366</v>
+        <v>6815058</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15705,7 +15705,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122289697</v>
+        <v>122289678</v>
       </c>
       <c r="B147" t="n">
         <v>78646</v>
@@ -15745,10 +15745,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>473033</v>
+        <v>472765</v>
       </c>
       <c r="R147" t="n">
-        <v>6815058</v>
+        <v>6815044</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15807,7 +15807,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122289678</v>
+        <v>122289628</v>
       </c>
       <c r="B148" t="n">
         <v>78646</v>
@@ -15847,10 +15847,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>472765</v>
+        <v>472851</v>
       </c>
       <c r="R148" t="n">
-        <v>6815044</v>
+        <v>6815729</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15909,7 +15909,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122289628</v>
+        <v>122289743</v>
       </c>
       <c r="B149" t="n">
         <v>78646</v>
@@ -15949,10 +15949,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>472851</v>
+        <v>473207</v>
       </c>
       <c r="R149" t="n">
-        <v>6815729</v>
+        <v>6815471</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16011,7 +16011,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122289743</v>
+        <v>122289624</v>
       </c>
       <c r="B150" t="n">
         <v>78646</v>
@@ -16051,10 +16051,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>473207</v>
+        <v>472913</v>
       </c>
       <c r="R150" t="n">
-        <v>6815471</v>
+        <v>6815662</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16113,7 +16113,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122289624</v>
+        <v>122289728</v>
       </c>
       <c r="B151" t="n">
         <v>78646</v>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>472913</v>
+        <v>472936</v>
       </c>
       <c r="R151" t="n">
-        <v>6815662</v>
+        <v>6815401</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16215,10 +16215,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122289728</v>
+        <v>122289576</v>
       </c>
       <c r="B152" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16231,34 +16231,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>472936</v>
+        <v>473233</v>
       </c>
       <c r="R152" t="n">
-        <v>6815401</v>
+        <v>6815571</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16291,6 +16296,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16317,7 +16327,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122289576</v>
+        <v>122289553</v>
       </c>
       <c r="B153" t="n">
         <v>57374</v>
@@ -16353,7 +16363,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -16362,10 +16372,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>473233</v>
+        <v>472880</v>
       </c>
       <c r="R153" t="n">
-        <v>6815571</v>
+        <v>6815136</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16402,7 +16412,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16429,7 +16439,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122289553</v>
+        <v>122289565</v>
       </c>
       <c r="B154" t="n">
         <v>57374</v>
@@ -16474,10 +16484,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>472880</v>
+        <v>472697</v>
       </c>
       <c r="R154" t="n">
-        <v>6815136</v>
+        <v>6815151</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16541,7 +16551,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122289565</v>
+        <v>122289555</v>
       </c>
       <c r="B155" t="n">
         <v>57374</v>
@@ -16586,10 +16596,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>472697</v>
+        <v>473055</v>
       </c>
       <c r="R155" t="n">
-        <v>6815151</v>
+        <v>6815710</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16626,7 +16636,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16653,10 +16663,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122289555</v>
+        <v>122289608</v>
       </c>
       <c r="B156" t="n">
-        <v>57374</v>
+        <v>78383</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16669,39 +16679,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>473055</v>
+        <v>472951</v>
       </c>
       <c r="R156" t="n">
-        <v>6815710</v>
+        <v>6815418</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16734,11 +16739,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16765,10 +16765,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122289651</v>
+        <v>122289530</v>
       </c>
       <c r="B157" t="n">
-        <v>78646</v>
+        <v>79235</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16781,21 +16781,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16805,10 +16805,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>472821</v>
+        <v>473042</v>
       </c>
       <c r="R157" t="n">
-        <v>6815364</v>
+        <v>6815081</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16867,10 +16867,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122289687</v>
+        <v>122289599</v>
       </c>
       <c r="B158" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16883,21 +16883,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16907,10 +16907,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>472899</v>
+        <v>472912</v>
       </c>
       <c r="R158" t="n">
-        <v>6815079</v>
+        <v>6815662</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16969,10 +16969,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122289670</v>
+        <v>122289516</v>
       </c>
       <c r="B159" t="n">
-        <v>78646</v>
+        <v>78680</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16985,21 +16985,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17009,10 +17009,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>472698</v>
+        <v>473107</v>
       </c>
       <c r="R159" t="n">
-        <v>6815034</v>
+        <v>6815366</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17071,7 +17071,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122289711</v>
+        <v>122289651</v>
       </c>
       <c r="B160" t="n">
         <v>78646</v>
@@ -17111,10 +17111,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>472976</v>
+        <v>472821</v>
       </c>
       <c r="R160" t="n">
-        <v>6815272</v>
+        <v>6815364</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17173,10 +17173,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122289608</v>
+        <v>122289687</v>
       </c>
       <c r="B161" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17189,21 +17189,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17213,10 +17213,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>472951</v>
+        <v>472899</v>
       </c>
       <c r="R161" t="n">
-        <v>6815418</v>
+        <v>6815079</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17275,10 +17275,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122289530</v>
+        <v>122289670</v>
       </c>
       <c r="B162" t="n">
-        <v>79235</v>
+        <v>78646</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17291,21 +17291,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>473042</v>
+        <v>472698</v>
       </c>
       <c r="R162" t="n">
-        <v>6815081</v>
+        <v>6815034</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17377,10 +17377,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122289599</v>
+        <v>122289711</v>
       </c>
       <c r="B163" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17393,21 +17393,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17417,10 +17417,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>472912</v>
+        <v>472976</v>
       </c>
       <c r="R163" t="n">
-        <v>6815662</v>
+        <v>6815272</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19024,10 +19024,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122289572</v>
+        <v>122289753</v>
       </c>
       <c r="B179" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19040,39 +19040,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>472916</v>
+        <v>473242</v>
       </c>
       <c r="R179" t="n">
-        <v>6815362</v>
+        <v>6815602</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19105,11 +19100,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19136,10 +19126,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122289577</v>
+        <v>122289719</v>
       </c>
       <c r="B180" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19152,39 +19142,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>472922</v>
+        <v>472906</v>
       </c>
       <c r="R180" t="n">
-        <v>6815653</v>
+        <v>6815327</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19217,11 +19202,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19248,10 +19228,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122289586</v>
+        <v>122289643</v>
       </c>
       <c r="B181" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19264,39 +19244,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>473036</v>
+        <v>472856</v>
       </c>
       <c r="R181" t="n">
-        <v>6815173</v>
+        <v>6815448</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19329,11 +19304,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19360,10 +19330,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122289493</v>
+        <v>122289673</v>
       </c>
       <c r="B182" t="n">
-        <v>74747</v>
+        <v>78646</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19376,21 +19346,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19400,10 +19370,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>473003</v>
+        <v>472729</v>
       </c>
       <c r="R182" t="n">
-        <v>6814987</v>
+        <v>6815062</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19462,7 +19432,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289631</v>
+        <v>122289627</v>
       </c>
       <c r="B183" t="n">
         <v>78646</v>
@@ -19502,10 +19472,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>472746</v>
+        <v>472837</v>
       </c>
       <c r="R183" t="n">
-        <v>6815730</v>
+        <v>6815704</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19564,7 +19534,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289665</v>
+        <v>122289657</v>
       </c>
       <c r="B184" t="n">
         <v>78646</v>
@@ -19604,10 +19574,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>472722</v>
+        <v>472730</v>
       </c>
       <c r="R184" t="n">
-        <v>6815109</v>
+        <v>6815383</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19666,10 +19636,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122289474</v>
+        <v>122289572</v>
       </c>
       <c r="B185" t="n">
-        <v>79264</v>
+        <v>57374</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19682,34 +19652,39 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>473224</v>
+        <v>472916</v>
       </c>
       <c r="R185" t="n">
-        <v>6815618</v>
+        <v>6815362</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19742,6 +19717,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19768,10 +19748,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289490</v>
+        <v>122289577</v>
       </c>
       <c r="B186" t="n">
-        <v>74747</v>
+        <v>57374</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19784,34 +19764,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>472713</v>
+        <v>472922</v>
       </c>
       <c r="R186" t="n">
-        <v>6815143</v>
+        <v>6815653</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19844,6 +19829,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19870,10 +19860,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289753</v>
+        <v>122289586</v>
       </c>
       <c r="B187" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19886,34 +19876,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>473242</v>
+        <v>473036</v>
       </c>
       <c r="R187" t="n">
-        <v>6815602</v>
+        <v>6815173</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19946,6 +19941,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19972,10 +19972,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289719</v>
+        <v>122289493</v>
       </c>
       <c r="B188" t="n">
-        <v>78646</v>
+        <v>74747</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19988,21 +19988,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20012,10 +20012,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>472906</v>
+        <v>473003</v>
       </c>
       <c r="R188" t="n">
-        <v>6815327</v>
+        <v>6814987</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20074,7 +20074,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122289643</v>
+        <v>122289631</v>
       </c>
       <c r="B189" t="n">
         <v>78646</v>
@@ -20114,10 +20114,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>472856</v>
+        <v>472746</v>
       </c>
       <c r="R189" t="n">
-        <v>6815448</v>
+        <v>6815730</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20176,7 +20176,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289673</v>
+        <v>122289665</v>
       </c>
       <c r="B190" t="n">
         <v>78646</v>
@@ -20216,10 +20216,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>472729</v>
+        <v>472722</v>
       </c>
       <c r="R190" t="n">
-        <v>6815062</v>
+        <v>6815109</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20278,10 +20278,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122289627</v>
+        <v>122289474</v>
       </c>
       <c r="B191" t="n">
-        <v>78646</v>
+        <v>79264</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20294,21 +20294,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20318,10 +20318,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>472837</v>
+        <v>473224</v>
       </c>
       <c r="R191" t="n">
-        <v>6815704</v>
+        <v>6815618</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20380,10 +20380,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122289657</v>
+        <v>122289490</v>
       </c>
       <c r="B192" t="n">
-        <v>78646</v>
+        <v>74747</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20396,21 +20396,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20420,10 +20420,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>472730</v>
+        <v>472713</v>
       </c>
       <c r="R192" t="n">
-        <v>6815383</v>
+        <v>6815143</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20686,10 +20686,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122289546</v>
+        <v>122289506</v>
       </c>
       <c r="B195" t="n">
-        <v>57390</v>
+        <v>78680</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20702,39 +20702,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>472731</v>
+        <v>473050</v>
       </c>
       <c r="R195" t="n">
-        <v>6815088</v>
+        <v>6815098</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20793,7 +20788,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122289506</v>
+        <v>122289519</v>
       </c>
       <c r="B196" t="n">
         <v>78680</v>
@@ -20833,10 +20828,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>473050</v>
+        <v>473217</v>
       </c>
       <c r="R196" t="n">
-        <v>6815098</v>
+        <v>6815515</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20895,10 +20890,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122289519</v>
+        <v>122289564</v>
       </c>
       <c r="B197" t="n">
-        <v>78680</v>
+        <v>57374</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20911,34 +20906,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>473217</v>
+        <v>472724</v>
       </c>
       <c r="R197" t="n">
-        <v>6815515</v>
+        <v>6815345</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20971,6 +20971,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20997,10 +21002,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122289696</v>
+        <v>122289574</v>
       </c>
       <c r="B198" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21013,34 +21018,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>473033</v>
+        <v>473230</v>
       </c>
       <c r="R198" t="n">
-        <v>6815029</v>
+        <v>6815538</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21073,6 +21083,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21099,10 +21114,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122289619</v>
+        <v>122289560</v>
       </c>
       <c r="B199" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21115,34 +21130,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>473228</v>
+        <v>472880</v>
       </c>
       <c r="R199" t="n">
-        <v>6815569</v>
+        <v>6815442</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21175,6 +21195,11 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21201,10 +21226,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122289618</v>
+        <v>122289696</v>
       </c>
       <c r="B200" t="n">
-        <v>90807</v>
+        <v>78646</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21217,21 +21242,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21241,10 +21266,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>473257</v>
+        <v>473033</v>
       </c>
       <c r="R200" t="n">
-        <v>6815716</v>
+        <v>6815029</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21303,7 +21328,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122289751</v>
+        <v>122289619</v>
       </c>
       <c r="B201" t="n">
         <v>78646</v>
@@ -21343,10 +21368,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>473230</v>
+        <v>473228</v>
       </c>
       <c r="R201" t="n">
-        <v>6815539</v>
+        <v>6815569</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21405,10 +21430,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122289732</v>
+        <v>122289618</v>
       </c>
       <c r="B202" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21421,21 +21446,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21445,10 +21470,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>472971</v>
+        <v>473257</v>
       </c>
       <c r="R202" t="n">
-        <v>6815467</v>
+        <v>6815716</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21507,7 +21532,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122289746</v>
+        <v>122289751</v>
       </c>
       <c r="B203" t="n">
         <v>78646</v>
@@ -21547,10 +21572,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>473192</v>
+        <v>473230</v>
       </c>
       <c r="R203" t="n">
-        <v>6815502</v>
+        <v>6815539</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21609,10 +21634,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122289564</v>
+        <v>122289732</v>
       </c>
       <c r="B204" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21625,39 +21650,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>472724</v>
+        <v>472971</v>
       </c>
       <c r="R204" t="n">
-        <v>6815345</v>
+        <v>6815467</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21690,11 +21710,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21721,10 +21736,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122289574</v>
+        <v>122289746</v>
       </c>
       <c r="B205" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21737,39 +21752,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>473230</v>
+        <v>473192</v>
       </c>
       <c r="R205" t="n">
-        <v>6815538</v>
+        <v>6815502</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21802,11 +21812,6 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21833,10 +21838,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122289560</v>
+        <v>122289546</v>
       </c>
       <c r="B206" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21849,16 +21854,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -21869,7 +21874,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -21878,10 +21883,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>472880</v>
+        <v>472731</v>
       </c>
       <c r="R206" t="n">
-        <v>6815442</v>
+        <v>6815088</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21914,11 +21919,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23475,10 +23475,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289691</v>
+        <v>122289581</v>
       </c>
       <c r="B222" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23491,34 +23491,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>472974</v>
+        <v>472821</v>
       </c>
       <c r="R222" t="n">
-        <v>6815012</v>
+        <v>6815364</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23551,6 +23556,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23577,10 +23587,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289720</v>
+        <v>122289615</v>
       </c>
       <c r="B223" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23593,34 +23603,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>472902</v>
+        <v>472712</v>
       </c>
       <c r="R223" t="n">
-        <v>6815343</v>
+        <v>6815141</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23653,6 +23668,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23679,10 +23699,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122289622</v>
+        <v>122289592</v>
       </c>
       <c r="B224" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23695,34 +23715,39 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>472955</v>
+        <v>473038</v>
       </c>
       <c r="R224" t="n">
-        <v>6815658</v>
+        <v>6815393</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23781,7 +23806,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122289581</v>
+        <v>122289587</v>
       </c>
       <c r="B225" t="n">
         <v>57374</v>
@@ -23826,10 +23851,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>472821</v>
+        <v>473000</v>
       </c>
       <c r="R225" t="n">
-        <v>6815364</v>
+        <v>6815184</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23893,7 +23918,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122289615</v>
+        <v>122289566</v>
       </c>
       <c r="B226" t="n">
         <v>57374</v>
@@ -23938,10 +23963,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>472712</v>
+        <v>472846</v>
       </c>
       <c r="R226" t="n">
-        <v>6815141</v>
+        <v>6815099</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24005,10 +24030,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122289592</v>
+        <v>122289691</v>
       </c>
       <c r="B227" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24021,39 +24046,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>473038</v>
+        <v>472974</v>
       </c>
       <c r="R227" t="n">
-        <v>6815393</v>
+        <v>6815012</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24112,10 +24132,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122289587</v>
+        <v>122289720</v>
       </c>
       <c r="B228" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24128,39 +24148,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>473000</v>
+        <v>472902</v>
       </c>
       <c r="R228" t="n">
-        <v>6815184</v>
+        <v>6815343</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24193,11 +24208,6 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24224,10 +24234,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122289566</v>
+        <v>122289622</v>
       </c>
       <c r="B229" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24240,39 +24250,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>472846</v>
+        <v>472955</v>
       </c>
       <c r="R229" t="n">
-        <v>6815099</v>
+        <v>6815658</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24305,11 +24310,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26702,10 +26702,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289563</v>
+        <v>122289772</v>
       </c>
       <c r="B253" t="n">
-        <v>57374</v>
+        <v>78030</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26718,39 +26718,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>472874</v>
+        <v>473001</v>
       </c>
       <c r="R253" t="n">
-        <v>6815282</v>
+        <v>6815720</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26783,11 +26778,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26814,10 +26804,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289578</v>
+        <v>122289726</v>
       </c>
       <c r="B254" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26830,39 +26820,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>472860</v>
+        <v>472934</v>
       </c>
       <c r="R254" t="n">
-        <v>6815679</v>
+        <v>6815384</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26895,11 +26880,6 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26926,10 +26906,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289570</v>
+        <v>122289757</v>
       </c>
       <c r="B255" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26942,39 +26922,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>473034</v>
+        <v>473240</v>
       </c>
       <c r="R255" t="n">
-        <v>6815167</v>
+        <v>6815680</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27007,11 +26982,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27038,10 +27008,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289772</v>
+        <v>122289626</v>
       </c>
       <c r="B256" t="n">
-        <v>78030</v>
+        <v>78646</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27054,21 +27024,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -27078,10 +27048,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>473001</v>
+        <v>472855</v>
       </c>
       <c r="R256" t="n">
-        <v>6815720</v>
+        <v>6815671</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27140,10 +27110,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289726</v>
+        <v>122289563</v>
       </c>
       <c r="B257" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27156,34 +27126,39 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>472934</v>
+        <v>472874</v>
       </c>
       <c r="R257" t="n">
-        <v>6815384</v>
+        <v>6815282</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27216,6 +27191,11 @@
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27242,10 +27222,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289757</v>
+        <v>122289578</v>
       </c>
       <c r="B258" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27258,34 +27238,39 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>473240</v>
+        <v>472860</v>
       </c>
       <c r="R258" t="n">
-        <v>6815680</v>
+        <v>6815679</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27318,6 +27303,11 @@
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27344,10 +27334,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289626</v>
+        <v>122289570</v>
       </c>
       <c r="B259" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27360,34 +27350,39 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>472855</v>
+        <v>473034</v>
       </c>
       <c r="R259" t="n">
-        <v>6815671</v>
+        <v>6815167</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27420,6 +27415,11 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD259" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122289482</v>
+        <v>122289564</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,34 +2778,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472988</v>
+        <v>472724</v>
       </c>
       <c r="R22" t="n">
-        <v>6815002</v>
+        <v>6815345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,6 +2843,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122289648</v>
+        <v>122289586</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,34 +2890,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472874</v>
+        <v>473036</v>
       </c>
       <c r="R23" t="n">
-        <v>6815282</v>
+        <v>6815173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2940,6 +2955,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2966,10 +2986,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122289690</v>
+        <v>122289587</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,34 +3002,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472957</v>
+        <v>473000</v>
       </c>
       <c r="R24" t="n">
-        <v>6815023</v>
+        <v>6815184</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,6 +3067,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3068,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122289645</v>
+        <v>122289596</v>
       </c>
       <c r="B25" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,21 +3114,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3108,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472889</v>
+        <v>473223</v>
       </c>
       <c r="R25" t="n">
-        <v>6815359</v>
+        <v>6815621</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122289773</v>
+        <v>122289594</v>
       </c>
       <c r="B26" t="n">
-        <v>78035</v>
+        <v>74747</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3186,21 +3216,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3210,10 +3240,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473042</v>
+        <v>472834</v>
       </c>
       <c r="R26" t="n">
-        <v>6815081</v>
+        <v>6815612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,10 +3302,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122289734</v>
+        <v>122289501</v>
       </c>
       <c r="B27" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3288,21 +3318,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3312,10 +3342,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473018</v>
+        <v>472722</v>
       </c>
       <c r="R27" t="n">
-        <v>6815464</v>
+        <v>6815373</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3404,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122289487</v>
+        <v>122289482</v>
       </c>
       <c r="B28" t="n">
         <v>79269</v>
@@ -3414,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473192</v>
+        <v>472988</v>
       </c>
       <c r="R28" t="n">
-        <v>6815503</v>
+        <v>6815002</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,7 +3506,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122289715</v>
+        <v>122289648</v>
       </c>
       <c r="B29" t="n">
         <v>78651</v>
@@ -3516,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472966</v>
+        <v>472874</v>
       </c>
       <c r="R29" t="n">
-        <v>6815390</v>
+        <v>6815282</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,7 +3608,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289692</v>
+        <v>122289690</v>
       </c>
       <c r="B30" t="n">
         <v>78651</v>
@@ -3618,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472970</v>
+        <v>472957</v>
       </c>
       <c r="R30" t="n">
-        <v>6814989</v>
+        <v>6815023</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,10 +3710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289490</v>
+        <v>122289645</v>
       </c>
       <c r="B31" t="n">
-        <v>74752</v>
+        <v>78651</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3696,21 +3726,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3720,10 +3750,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472713</v>
+        <v>472889</v>
       </c>
       <c r="R31" t="n">
-        <v>6815143</v>
+        <v>6815359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,10 +3812,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122289636</v>
+        <v>122289773</v>
       </c>
       <c r="B32" t="n">
-        <v>78651</v>
+        <v>78035</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3798,21 +3828,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3822,10 +3852,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472843</v>
+        <v>473042</v>
       </c>
       <c r="R32" t="n">
-        <v>6815598</v>
+        <v>6815081</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3884,7 +3914,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289726</v>
+        <v>122289734</v>
       </c>
       <c r="B33" t="n">
         <v>78651</v>
@@ -3924,10 +3954,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472934</v>
+        <v>473018</v>
       </c>
       <c r="R33" t="n">
-        <v>6815384</v>
+        <v>6815464</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3986,7 +4016,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122289481</v>
+        <v>122289487</v>
       </c>
       <c r="B34" t="n">
         <v>79269</v>
@@ -4026,10 +4056,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472871</v>
+        <v>473192</v>
       </c>
       <c r="R34" t="n">
-        <v>6815157</v>
+        <v>6815503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4088,10 +4118,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122289546</v>
+        <v>122289715</v>
       </c>
       <c r="B35" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4104,39 +4134,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472731</v>
+        <v>472966</v>
       </c>
       <c r="R35" t="n">
-        <v>6815088</v>
+        <v>6815390</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4195,10 +4220,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122289596</v>
+        <v>122289692</v>
       </c>
       <c r="B36" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4211,21 +4236,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4235,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473223</v>
+        <v>472970</v>
       </c>
       <c r="R36" t="n">
-        <v>6815621</v>
+        <v>6814989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4297,10 +4322,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122289594</v>
+        <v>122289490</v>
       </c>
       <c r="B37" t="n">
-        <v>74747</v>
+        <v>74752</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4313,21 +4338,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4337,10 +4362,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472834</v>
+        <v>472713</v>
       </c>
       <c r="R37" t="n">
-        <v>6815612</v>
+        <v>6815143</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4399,10 +4424,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122289501</v>
+        <v>122289636</v>
       </c>
       <c r="B38" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4415,21 +4440,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4439,10 +4464,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472722</v>
+        <v>472843</v>
       </c>
       <c r="R38" t="n">
-        <v>6815373</v>
+        <v>6815598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4501,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122289564</v>
+        <v>122289726</v>
       </c>
       <c r="B39" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4517,39 +4542,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472724</v>
+        <v>472934</v>
       </c>
       <c r="R39" t="n">
-        <v>6815345</v>
+        <v>6815384</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4582,11 +4602,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4613,10 +4628,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122289586</v>
+        <v>122289481</v>
       </c>
       <c r="B40" t="n">
-        <v>57379</v>
+        <v>79269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4629,39 +4644,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473036</v>
+        <v>472871</v>
       </c>
       <c r="R40" t="n">
-        <v>6815173</v>
+        <v>6815157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4694,11 +4704,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4725,10 +4730,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122289587</v>
+        <v>122289546</v>
       </c>
       <c r="B41" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,16 +4746,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4770,10 +4775,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473000</v>
+        <v>472731</v>
       </c>
       <c r="R41" t="n">
-        <v>6815184</v>
+        <v>6815088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4806,11 +4811,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4837,10 +4837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122289765</v>
+        <v>122289519</v>
       </c>
       <c r="B42" t="n">
-        <v>90826</v>
+        <v>78685</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4853,21 +4853,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472815</v>
+        <v>473217</v>
       </c>
       <c r="R42" t="n">
-        <v>6815646</v>
+        <v>6815515</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4939,10 +4939,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122289730</v>
+        <v>122289505</v>
       </c>
       <c r="B43" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4955,21 +4955,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472958</v>
+        <v>472846</v>
       </c>
       <c r="R43" t="n">
-        <v>6815427</v>
+        <v>6815101</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5041,10 +5041,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122289532</v>
+        <v>122289765</v>
       </c>
       <c r="B44" t="n">
-        <v>79240</v>
+        <v>90826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5057,21 +5057,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473191</v>
+        <v>472815</v>
       </c>
       <c r="R44" t="n">
-        <v>6815504</v>
+        <v>6815646</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5143,10 +5143,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122289598</v>
+        <v>122289703</v>
       </c>
       <c r="B45" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5159,21 +5159,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473022</v>
+        <v>473050</v>
       </c>
       <c r="R45" t="n">
-        <v>6815732</v>
+        <v>6815176</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122289519</v>
+        <v>122289740</v>
       </c>
       <c r="B46" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473217</v>
+        <v>473153</v>
       </c>
       <c r="R46" t="n">
-        <v>6815515</v>
+        <v>6815381</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122289505</v>
+        <v>122289748</v>
       </c>
       <c r="B47" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472846</v>
+        <v>473217</v>
       </c>
       <c r="R47" t="n">
-        <v>6815101</v>
+        <v>6815515</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122289703</v>
+        <v>122289757</v>
       </c>
       <c r="B48" t="n">
         <v>78651</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473050</v>
+        <v>473240</v>
       </c>
       <c r="R48" t="n">
-        <v>6815176</v>
+        <v>6815680</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122289740</v>
+        <v>122289756</v>
       </c>
       <c r="B49" t="n">
         <v>78651</v>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473153</v>
+        <v>473239</v>
       </c>
       <c r="R49" t="n">
-        <v>6815381</v>
+        <v>6815673</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122289748</v>
+        <v>122289534</v>
       </c>
       <c r="B50" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5669,34 +5669,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473217</v>
+        <v>472993</v>
       </c>
       <c r="R50" t="n">
-        <v>6815515</v>
+        <v>6814991</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5755,10 +5760,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122289757</v>
+        <v>122289578</v>
       </c>
       <c r="B51" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5771,34 +5776,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473240</v>
+        <v>472860</v>
       </c>
       <c r="R51" t="n">
-        <v>6815680</v>
+        <v>6815679</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5831,6 +5841,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5857,7 +5872,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122289638</v>
+        <v>122289730</v>
       </c>
       <c r="B52" t="n">
         <v>78651</v>
@@ -5897,10 +5912,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>472871</v>
+        <v>472958</v>
       </c>
       <c r="R52" t="n">
-        <v>6815512</v>
+        <v>6815427</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5959,7 +5974,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122289652</v>
+        <v>122289638</v>
       </c>
       <c r="B53" t="n">
         <v>78651</v>
@@ -5999,10 +6014,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>472813</v>
+        <v>472871</v>
       </c>
       <c r="R53" t="n">
-        <v>6815369</v>
+        <v>6815512</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6061,7 +6076,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122289756</v>
+        <v>122289652</v>
       </c>
       <c r="B54" t="n">
         <v>78651</v>
@@ -6101,10 +6116,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473239</v>
+        <v>472813</v>
       </c>
       <c r="R54" t="n">
-        <v>6815673</v>
+        <v>6815369</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,10 +6280,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122289534</v>
+        <v>122289532</v>
       </c>
       <c r="B56" t="n">
-        <v>57379</v>
+        <v>79240</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6281,39 +6296,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>472993</v>
+        <v>473191</v>
       </c>
       <c r="R56" t="n">
-        <v>6814991</v>
+        <v>6815504</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6372,10 +6382,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122289578</v>
+        <v>122289598</v>
       </c>
       <c r="B57" t="n">
-        <v>57379</v>
+        <v>78388</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6388,39 +6398,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>472860</v>
+        <v>473022</v>
       </c>
       <c r="R57" t="n">
-        <v>6815679</v>
+        <v>6815732</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6453,11 +6458,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6484,10 +6484,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122289675</v>
+        <v>122289513</v>
       </c>
       <c r="B58" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6500,21 +6500,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>472745</v>
+        <v>472966</v>
       </c>
       <c r="R58" t="n">
-        <v>6815068</v>
+        <v>6815390</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122289619</v>
+        <v>122289675</v>
       </c>
       <c r="B59" t="n">
         <v>78651</v>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473228</v>
+        <v>472745</v>
       </c>
       <c r="R59" t="n">
-        <v>6815569</v>
+        <v>6815068</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122289712</v>
+        <v>122289619</v>
       </c>
       <c r="B60" t="n">
         <v>78651</v>
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>472971</v>
+        <v>473228</v>
       </c>
       <c r="R60" t="n">
-        <v>6815298</v>
+        <v>6815569</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122289613</v>
+        <v>122289712</v>
       </c>
       <c r="B61" t="n">
-        <v>78387</v>
+        <v>78651</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6806,21 +6806,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473014</v>
+        <v>472971</v>
       </c>
       <c r="R61" t="n">
-        <v>6815496</v>
+        <v>6815298</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122289485</v>
+        <v>122289613</v>
       </c>
       <c r="B62" t="n">
-        <v>79269</v>
+        <v>78387</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6908,21 +6908,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122289562</v>
+        <v>122289485</v>
       </c>
       <c r="B63" t="n">
-        <v>57379</v>
+        <v>79269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7010,39 +7010,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>472869</v>
+        <v>473014</v>
       </c>
       <c r="R63" t="n">
-        <v>6815446</v>
+        <v>6815496</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7075,11 +7070,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7106,7 +7096,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122289563</v>
+        <v>122289562</v>
       </c>
       <c r="B64" t="n">
         <v>57379</v>
@@ -7151,10 +7141,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>472874</v>
+        <v>472869</v>
       </c>
       <c r="R64" t="n">
-        <v>6815282</v>
+        <v>6815446</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7218,10 +7208,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122289513</v>
+        <v>122289563</v>
       </c>
       <c r="B65" t="n">
-        <v>78685</v>
+        <v>57379</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7234,34 +7224,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>472966</v>
+        <v>472874</v>
       </c>
       <c r="R65" t="n">
-        <v>6815390</v>
+        <v>6815282</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7294,6 +7289,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7422,10 +7422,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122289716</v>
+        <v>122289608</v>
       </c>
       <c r="B67" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7438,21 +7438,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472966</v>
+        <v>472951</v>
       </c>
       <c r="R67" t="n">
-        <v>6815380</v>
+        <v>6815418</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122289572</v>
+        <v>122289607</v>
       </c>
       <c r="B68" t="n">
-        <v>57379</v>
+        <v>78388</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7540,39 +7540,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472916</v>
+        <v>472871</v>
       </c>
       <c r="R68" t="n">
-        <v>6815362</v>
+        <v>6815157</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7605,11 +7600,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7636,10 +7626,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122289615</v>
+        <v>122289716</v>
       </c>
       <c r="B69" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7652,39 +7642,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472712</v>
+        <v>472966</v>
       </c>
       <c r="R69" t="n">
-        <v>6815141</v>
+        <v>6815380</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7717,11 +7702,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7748,10 +7728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289769</v>
+        <v>122289676</v>
       </c>
       <c r="B70" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7764,39 +7744,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472842</v>
+        <v>472759</v>
       </c>
       <c r="R70" t="n">
-        <v>6815605</v>
+        <v>6815052</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7829,11 +7804,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7860,7 +7830,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289560</v>
+        <v>122289572</v>
       </c>
       <c r="B71" t="n">
         <v>57379</v>
@@ -7905,10 +7875,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472880</v>
+        <v>472916</v>
       </c>
       <c r="R71" t="n">
-        <v>6815442</v>
+        <v>6815362</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7972,10 +7942,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122289676</v>
+        <v>122289615</v>
       </c>
       <c r="B72" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7988,34 +7958,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472759</v>
+        <v>472712</v>
       </c>
       <c r="R72" t="n">
-        <v>6815052</v>
+        <v>6815141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8048,6 +8023,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8074,10 +8054,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122289608</v>
+        <v>122289769</v>
       </c>
       <c r="B73" t="n">
-        <v>78388</v>
+        <v>57379</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8090,34 +8070,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472951</v>
+        <v>472842</v>
       </c>
       <c r="R73" t="n">
-        <v>6815418</v>
+        <v>6815605</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8150,6 +8135,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8176,10 +8166,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289607</v>
+        <v>122289560</v>
       </c>
       <c r="B74" t="n">
-        <v>78388</v>
+        <v>57379</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8192,34 +8182,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472871</v>
+        <v>472880</v>
       </c>
       <c r="R74" t="n">
-        <v>6815157</v>
+        <v>6815442</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8252,6 +8247,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -12749,10 +12749,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122289717</v>
+        <v>122289567</v>
       </c>
       <c r="B118" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12765,34 +12765,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>472949</v>
+        <v>472851</v>
       </c>
       <c r="R118" t="n">
-        <v>6815365</v>
+        <v>6815154</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12825,6 +12830,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12851,10 +12861,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122289750</v>
+        <v>122289588</v>
       </c>
       <c r="B119" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12867,34 +12877,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>473232</v>
+        <v>472971</v>
       </c>
       <c r="R119" t="n">
-        <v>6815538</v>
+        <v>6815298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12927,6 +12942,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12953,10 +12973,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122289657</v>
+        <v>122289580</v>
       </c>
       <c r="B120" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12969,34 +12989,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>472730</v>
+        <v>472862</v>
       </c>
       <c r="R120" t="n">
-        <v>6815383</v>
+        <v>6815472</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13029,6 +13054,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13055,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122289622</v>
+        <v>122289517</v>
       </c>
       <c r="B121" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13071,21 +13101,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13095,10 +13125,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>472955</v>
+        <v>473149</v>
       </c>
       <c r="R121" t="n">
-        <v>6815658</v>
+        <v>6815391</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13157,10 +13187,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122289567</v>
+        <v>122289521</v>
       </c>
       <c r="B122" t="n">
-        <v>57379</v>
+        <v>78685</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13173,39 +13203,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>472851</v>
+        <v>473236</v>
       </c>
       <c r="R122" t="n">
-        <v>6815154</v>
+        <v>6815621</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13238,11 +13263,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13269,10 +13289,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122289517</v>
+        <v>122289750</v>
       </c>
       <c r="B123" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13285,21 +13305,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13309,10 +13329,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>473149</v>
+        <v>473232</v>
       </c>
       <c r="R123" t="n">
-        <v>6815391</v>
+        <v>6815538</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13371,10 +13391,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122289521</v>
+        <v>122289549</v>
       </c>
       <c r="B124" t="n">
-        <v>78685</v>
+        <v>79733</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13387,21 +13407,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13411,10 +13431,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>473236</v>
+        <v>472766</v>
       </c>
       <c r="R124" t="n">
-        <v>6815621</v>
+        <v>6815366</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13473,10 +13493,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122289549</v>
+        <v>122289717</v>
       </c>
       <c r="B125" t="n">
-        <v>79733</v>
+        <v>78651</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13489,21 +13509,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13513,10 +13533,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>472766</v>
+        <v>472949</v>
       </c>
       <c r="R125" t="n">
-        <v>6815366</v>
+        <v>6815365</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13677,10 +13697,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122289588</v>
+        <v>122289657</v>
       </c>
       <c r="B127" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13693,39 +13713,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>472971</v>
+        <v>472730</v>
       </c>
       <c r="R127" t="n">
-        <v>6815298</v>
+        <v>6815383</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13758,11 +13773,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13789,10 +13799,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122289580</v>
+        <v>122289622</v>
       </c>
       <c r="B128" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13805,39 +13815,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>472862</v>
+        <v>472955</v>
       </c>
       <c r="R128" t="n">
-        <v>6815472</v>
+        <v>6815658</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13870,11 +13875,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -19163,10 +19163,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122289696</v>
+        <v>122289507</v>
       </c>
       <c r="B180" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19179,21 +19179,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19203,10 +19203,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>473033</v>
+        <v>473043</v>
       </c>
       <c r="R180" t="n">
-        <v>6815029</v>
+        <v>6815153</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19265,10 +19265,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122289559</v>
+        <v>122289767</v>
       </c>
       <c r="B181" t="n">
-        <v>57379</v>
+        <v>90826</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19281,39 +19281,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>472934</v>
+        <v>472819</v>
       </c>
       <c r="R181" t="n">
-        <v>6815651</v>
+        <v>6815624</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19346,11 +19341,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19377,10 +19367,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122289591</v>
+        <v>122289749</v>
       </c>
       <c r="B182" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19393,39 +19383,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>473243</v>
+        <v>473236</v>
       </c>
       <c r="R182" t="n">
-        <v>6815620</v>
+        <v>6815526</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19458,11 +19443,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19489,10 +19469,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289585</v>
+        <v>122289630</v>
       </c>
       <c r="B183" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19505,39 +19485,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>473030</v>
+        <v>473038</v>
       </c>
       <c r="R183" t="n">
-        <v>6815053</v>
+        <v>6815393</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19570,11 +19545,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19601,10 +19571,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289507</v>
+        <v>122289659</v>
       </c>
       <c r="B184" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19617,21 +19587,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19641,10 +19611,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>473043</v>
+        <v>472724</v>
       </c>
       <c r="R184" t="n">
-        <v>6815153</v>
+        <v>6815345</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19703,10 +19673,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122289767</v>
+        <v>122289727</v>
       </c>
       <c r="B185" t="n">
-        <v>90826</v>
+        <v>78651</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19719,21 +19689,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19743,10 +19713,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>472819</v>
+        <v>472922</v>
       </c>
       <c r="R185" t="n">
-        <v>6815624</v>
+        <v>6815393</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19805,7 +19775,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289749</v>
+        <v>122289696</v>
       </c>
       <c r="B186" t="n">
         <v>78651</v>
@@ -19845,10 +19815,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>473236</v>
+        <v>473033</v>
       </c>
       <c r="R186" t="n">
-        <v>6815526</v>
+        <v>6815029</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19907,10 +19877,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289630</v>
+        <v>122289494</v>
       </c>
       <c r="B187" t="n">
-        <v>78651</v>
+        <v>74752</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19923,21 +19893,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19947,10 +19917,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>473038</v>
+        <v>473044</v>
       </c>
       <c r="R187" t="n">
-        <v>6815393</v>
+        <v>6815169</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20009,7 +19979,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289659</v>
+        <v>122289626</v>
       </c>
       <c r="B188" t="n">
         <v>78651</v>
@@ -20049,10 +20019,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>472724</v>
+        <v>472855</v>
       </c>
       <c r="R188" t="n">
-        <v>6815345</v>
+        <v>6815671</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20111,7 +20081,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122289727</v>
+        <v>122289710</v>
       </c>
       <c r="B189" t="n">
         <v>78651</v>
@@ -20151,10 +20121,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>472922</v>
+        <v>472998</v>
       </c>
       <c r="R189" t="n">
-        <v>6815393</v>
+        <v>6815243</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20213,10 +20183,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289647</v>
+        <v>122289559</v>
       </c>
       <c r="B190" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20229,34 +20199,39 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>472878</v>
+        <v>472934</v>
       </c>
       <c r="R190" t="n">
-        <v>6815322</v>
+        <v>6815651</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20289,6 +20264,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20315,10 +20295,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122289494</v>
+        <v>122289591</v>
       </c>
       <c r="B191" t="n">
-        <v>74752</v>
+        <v>57379</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20331,34 +20311,39 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>473044</v>
+        <v>473243</v>
       </c>
       <c r="R191" t="n">
-        <v>6815169</v>
+        <v>6815620</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20391,6 +20376,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20417,7 +20407,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122289626</v>
+        <v>122289647</v>
       </c>
       <c r="B192" t="n">
         <v>78651</v>
@@ -20457,10 +20447,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>472855</v>
+        <v>472878</v>
       </c>
       <c r="R192" t="n">
-        <v>6815671</v>
+        <v>6815322</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20519,10 +20509,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122289710</v>
+        <v>122289556</v>
       </c>
       <c r="B193" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20535,34 +20525,39 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>472998</v>
+        <v>472995</v>
       </c>
       <c r="R193" t="n">
-        <v>6815243</v>
+        <v>6815217</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20595,6 +20590,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20621,7 +20621,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122289556</v>
+        <v>122289585</v>
       </c>
       <c r="B194" t="n">
         <v>57379</v>
@@ -20657,7 +20657,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -20666,10 +20666,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>472995</v>
+        <v>473030</v>
       </c>
       <c r="R194" t="n">
-        <v>6815217</v>
+        <v>6815053</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20706,7 +20706,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Äldre rnghack (tall)</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25607,10 +25607,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122289611</v>
+        <v>122289526</v>
       </c>
       <c r="B242" t="n">
-        <v>78387</v>
+        <v>79240</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25623,21 +25623,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25647,10 +25647,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>472749</v>
+        <v>473224</v>
       </c>
       <c r="R242" t="n">
-        <v>6815725</v>
+        <v>6815616</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25709,10 +25709,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122289751</v>
+        <v>122289602</v>
       </c>
       <c r="B243" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25725,21 +25725,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25749,10 +25749,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>473230</v>
+        <v>472810</v>
       </c>
       <c r="R243" t="n">
-        <v>6815539</v>
+        <v>6815367</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25811,10 +25811,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122289725</v>
+        <v>122289592</v>
       </c>
       <c r="B244" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25827,34 +25827,39 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>472945</v>
+        <v>473038</v>
       </c>
       <c r="R244" t="n">
-        <v>6815381</v>
+        <v>6815393</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25913,10 +25918,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122289694</v>
+        <v>122289536</v>
       </c>
       <c r="B245" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25929,34 +25934,42 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>473042</v>
+        <v>472980</v>
       </c>
       <c r="R245" t="n">
-        <v>6814969</v>
+        <v>6814994</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26015,10 +26028,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122289702</v>
+        <v>122289511</v>
       </c>
       <c r="B246" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -26031,21 +26044,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -26055,10 +26068,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>473044</v>
+        <v>472998</v>
       </c>
       <c r="R246" t="n">
-        <v>6815169</v>
+        <v>6815243</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26117,10 +26130,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122289679</v>
+        <v>122289524</v>
       </c>
       <c r="B247" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -26133,21 +26146,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -26157,10 +26170,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>472779</v>
+        <v>473242</v>
       </c>
       <c r="R247" t="n">
-        <v>6815051</v>
+        <v>6815724</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26219,10 +26232,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122289743</v>
+        <v>122289611</v>
       </c>
       <c r="B248" t="n">
-        <v>78651</v>
+        <v>78387</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26235,21 +26248,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -26259,10 +26272,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>473207</v>
+        <v>472749</v>
       </c>
       <c r="R248" t="n">
-        <v>6815471</v>
+        <v>6815725</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26321,7 +26334,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122289672</v>
+        <v>122289751</v>
       </c>
       <c r="B249" t="n">
         <v>78651</v>
@@ -26361,10 +26374,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>472720</v>
+        <v>473230</v>
       </c>
       <c r="R249" t="n">
-        <v>6815067</v>
+        <v>6815539</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26423,7 +26436,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122289628</v>
+        <v>122289725</v>
       </c>
       <c r="B250" t="n">
         <v>78651</v>
@@ -26463,10 +26476,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>472851</v>
+        <v>472945</v>
       </c>
       <c r="R250" t="n">
-        <v>6815729</v>
+        <v>6815381</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26525,7 +26538,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122289635</v>
+        <v>122289694</v>
       </c>
       <c r="B251" t="n">
         <v>78651</v>
@@ -26565,10 +26578,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>472819</v>
+        <v>473042</v>
       </c>
       <c r="R251" t="n">
-        <v>6815642</v>
+        <v>6814969</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26627,7 +26640,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122289693</v>
+        <v>122289702</v>
       </c>
       <c r="B252" t="n">
         <v>78651</v>
@@ -26667,10 +26680,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>473002</v>
+        <v>473044</v>
       </c>
       <c r="R252" t="n">
-        <v>6814987</v>
+        <v>6815169</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26729,10 +26742,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289610</v>
+        <v>122289679</v>
       </c>
       <c r="B253" t="n">
-        <v>78387</v>
+        <v>78651</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26745,21 +26758,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26769,10 +26782,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>473044</v>
+        <v>472779</v>
       </c>
       <c r="R253" t="n">
-        <v>6815721</v>
+        <v>6815051</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26831,7 +26844,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289718</v>
+        <v>122289743</v>
       </c>
       <c r="B254" t="n">
         <v>78651</v>
@@ -26871,10 +26884,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>472942</v>
+        <v>473207</v>
       </c>
       <c r="R254" t="n">
-        <v>6815355</v>
+        <v>6815471</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26933,10 +26946,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289539</v>
+        <v>122289672</v>
       </c>
       <c r="B255" t="n">
-        <v>90828</v>
+        <v>78651</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26949,21 +26962,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26973,10 +26986,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>473229</v>
+        <v>472720</v>
       </c>
       <c r="R255" t="n">
-        <v>6815569</v>
+        <v>6815067</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27035,10 +27048,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289592</v>
+        <v>122289628</v>
       </c>
       <c r="B256" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27051,39 +27064,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>473038</v>
+        <v>472851</v>
       </c>
       <c r="R256" t="n">
-        <v>6815393</v>
+        <v>6815729</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27142,10 +27150,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289536</v>
+        <v>122289635</v>
       </c>
       <c r="B257" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27158,42 +27166,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>472980</v>
+        <v>472819</v>
       </c>
       <c r="R257" t="n">
-        <v>6814994</v>
+        <v>6815642</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27252,10 +27252,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289526</v>
+        <v>122289693</v>
       </c>
       <c r="B258" t="n">
-        <v>79240</v>
+        <v>78651</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27268,21 +27268,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27292,10 +27292,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>473224</v>
+        <v>473002</v>
       </c>
       <c r="R258" t="n">
-        <v>6815616</v>
+        <v>6814987</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27354,10 +27354,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289602</v>
+        <v>122289610</v>
       </c>
       <c r="B259" t="n">
-        <v>78388</v>
+        <v>78387</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27370,21 +27370,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27394,10 +27394,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>472810</v>
+        <v>473044</v>
       </c>
       <c r="R259" t="n">
-        <v>6815367</v>
+        <v>6815721</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27456,10 +27456,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122289511</v>
+        <v>122289718</v>
       </c>
       <c r="B260" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27472,21 +27472,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27496,10 +27496,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>472998</v>
+        <v>472942</v>
       </c>
       <c r="R260" t="n">
-        <v>6815243</v>
+        <v>6815355</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27558,10 +27558,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122289524</v>
+        <v>122289539</v>
       </c>
       <c r="B261" t="n">
-        <v>78685</v>
+        <v>90828</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27574,21 +27574,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27598,10 +27598,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>473242</v>
+        <v>473229</v>
       </c>
       <c r="R261" t="n">
-        <v>6815724</v>
+        <v>6815569</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27660,10 +27660,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122289623</v>
+        <v>122289553</v>
       </c>
       <c r="B262" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27676,34 +27676,39 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>472922</v>
+        <v>472880</v>
       </c>
       <c r="R262" t="n">
-        <v>6815653</v>
+        <v>6815136</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27736,6 +27741,11 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27762,10 +27772,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122289476</v>
+        <v>122289583</v>
       </c>
       <c r="B263" t="n">
-        <v>79269</v>
+        <v>57379</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27778,34 +27788,39 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>472813</v>
+        <v>472856</v>
       </c>
       <c r="R263" t="n">
-        <v>6815369</v>
+        <v>6815150</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27838,6 +27853,11 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27864,7 +27884,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122289633</v>
+        <v>122289623</v>
       </c>
       <c r="B264" t="n">
         <v>78651</v>
@@ -27904,10 +27924,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>472766</v>
+        <v>472922</v>
       </c>
       <c r="R264" t="n">
-        <v>6815686</v>
+        <v>6815653</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27966,10 +27986,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122289655</v>
+        <v>122289476</v>
       </c>
       <c r="B265" t="n">
-        <v>78651</v>
+        <v>79269</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27982,21 +28002,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -28006,10 +28026,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>472766</v>
+        <v>472813</v>
       </c>
       <c r="R265" t="n">
-        <v>6815363</v>
+        <v>6815369</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28068,10 +28088,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122289772</v>
+        <v>122289633</v>
       </c>
       <c r="B266" t="n">
-        <v>78035</v>
+        <v>78651</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -28084,21 +28104,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -28108,10 +28128,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>473001</v>
+        <v>472766</v>
       </c>
       <c r="R266" t="n">
-        <v>6815720</v>
+        <v>6815686</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28170,7 +28190,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122289705</v>
+        <v>122289655</v>
       </c>
       <c r="B267" t="n">
         <v>78651</v>
@@ -28210,10 +28230,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>473019</v>
+        <v>472766</v>
       </c>
       <c r="R267" t="n">
-        <v>6815163</v>
+        <v>6815363</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28272,10 +28292,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122289709</v>
+        <v>122289772</v>
       </c>
       <c r="B268" t="n">
-        <v>78651</v>
+        <v>78035</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28288,21 +28308,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -28312,10 +28332,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>472986</v>
+        <v>473001</v>
       </c>
       <c r="R268" t="n">
-        <v>6815203</v>
+        <v>6815720</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28374,7 +28394,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122289768</v>
+        <v>122289705</v>
       </c>
       <c r="B269" t="n">
         <v>78651</v>
@@ -28414,10 +28434,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>472877</v>
+        <v>473019</v>
       </c>
       <c r="R269" t="n">
-        <v>6815103</v>
+        <v>6815163</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28476,7 +28496,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122289708</v>
+        <v>122289709</v>
       </c>
       <c r="B270" t="n">
         <v>78651</v>
@@ -28516,10 +28536,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>473000</v>
+        <v>472986</v>
       </c>
       <c r="R270" t="n">
-        <v>6815193</v>
+        <v>6815203</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28578,7 +28598,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122289688</v>
+        <v>122289768</v>
       </c>
       <c r="B271" t="n">
         <v>78651</v>
@@ -28618,10 +28638,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>472911</v>
+        <v>472877</v>
       </c>
       <c r="R271" t="n">
-        <v>6815063</v>
+        <v>6815103</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28680,7 +28700,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122289744</v>
+        <v>122289708</v>
       </c>
       <c r="B272" t="n">
         <v>78651</v>
@@ -28720,10 +28740,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>473188</v>
+        <v>473000</v>
       </c>
       <c r="R272" t="n">
-        <v>6815489</v>
+        <v>6815193</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28782,10 +28802,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122289553</v>
+        <v>122289688</v>
       </c>
       <c r="B273" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28798,39 +28818,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>472880</v>
+        <v>472911</v>
       </c>
       <c r="R273" t="n">
-        <v>6815136</v>
+        <v>6815063</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28863,11 +28878,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -28894,10 +28904,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122289583</v>
+        <v>122289744</v>
       </c>
       <c r="B274" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28910,39 +28920,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>472856</v>
+        <v>473188</v>
       </c>
       <c r="R274" t="n">
-        <v>6815150</v>
+        <v>6815489</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28975,11 +28980,6 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD274" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -4837,10 +4837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122289519</v>
+        <v>122289532</v>
       </c>
       <c r="B42" t="n">
-        <v>78685</v>
+        <v>79240</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4853,21 +4853,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473217</v>
+        <v>473191</v>
       </c>
       <c r="R42" t="n">
-        <v>6815515</v>
+        <v>6815504</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4939,10 +4939,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122289505</v>
+        <v>122289598</v>
       </c>
       <c r="B43" t="n">
-        <v>78685</v>
+        <v>78388</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4955,21 +4955,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472846</v>
+        <v>473022</v>
       </c>
       <c r="R43" t="n">
-        <v>6815101</v>
+        <v>6815732</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5041,10 +5041,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122289765</v>
+        <v>122289519</v>
       </c>
       <c r="B44" t="n">
-        <v>90826</v>
+        <v>78685</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5057,21 +5057,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472815</v>
+        <v>473217</v>
       </c>
       <c r="R44" t="n">
-        <v>6815646</v>
+        <v>6815515</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5143,10 +5143,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122289703</v>
+        <v>122289505</v>
       </c>
       <c r="B45" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5159,21 +5159,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473050</v>
+        <v>472846</v>
       </c>
       <c r="R45" t="n">
-        <v>6815176</v>
+        <v>6815101</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122289740</v>
+        <v>122289703</v>
       </c>
       <c r="B46" t="n">
         <v>78651</v>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473153</v>
+        <v>473050</v>
       </c>
       <c r="R46" t="n">
-        <v>6815381</v>
+        <v>6815176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122289748</v>
+        <v>122289740</v>
       </c>
       <c r="B47" t="n">
         <v>78651</v>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473217</v>
+        <v>473153</v>
       </c>
       <c r="R47" t="n">
-        <v>6815515</v>
+        <v>6815381</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122289757</v>
+        <v>122289748</v>
       </c>
       <c r="B48" t="n">
         <v>78651</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473240</v>
+        <v>473217</v>
       </c>
       <c r="R48" t="n">
-        <v>6815680</v>
+        <v>6815515</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122289756</v>
+        <v>122289757</v>
       </c>
       <c r="B49" t="n">
         <v>78651</v>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473239</v>
+        <v>473240</v>
       </c>
       <c r="R49" t="n">
-        <v>6815673</v>
+        <v>6815680</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122289534</v>
+        <v>122289638</v>
       </c>
       <c r="B50" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5669,39 +5669,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472993</v>
+        <v>472871</v>
       </c>
       <c r="R50" t="n">
-        <v>6814991</v>
+        <v>6815512</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5760,10 +5755,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122289578</v>
+        <v>122289652</v>
       </c>
       <c r="B51" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5776,39 +5771,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>472860</v>
+        <v>472813</v>
       </c>
       <c r="R51" t="n">
-        <v>6815679</v>
+        <v>6815369</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5841,11 +5831,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5872,7 +5857,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122289730</v>
+        <v>122289756</v>
       </c>
       <c r="B52" t="n">
         <v>78651</v>
@@ -5912,10 +5897,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>472958</v>
+        <v>473239</v>
       </c>
       <c r="R52" t="n">
-        <v>6815427</v>
+        <v>6815673</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5974,7 +5959,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122289638</v>
+        <v>122289668</v>
       </c>
       <c r="B53" t="n">
         <v>78651</v>
@@ -6014,10 +5999,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>472871</v>
+        <v>472718</v>
       </c>
       <c r="R53" t="n">
-        <v>6815512</v>
+        <v>6815026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6076,10 +6061,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122289652</v>
+        <v>122289534</v>
       </c>
       <c r="B54" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6092,34 +6077,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>472813</v>
+        <v>472993</v>
       </c>
       <c r="R54" t="n">
-        <v>6815369</v>
+        <v>6814991</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6178,10 +6168,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122289668</v>
+        <v>122289578</v>
       </c>
       <c r="B55" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6194,34 +6184,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>472718</v>
+        <v>472860</v>
       </c>
       <c r="R55" t="n">
-        <v>6815026</v>
+        <v>6815679</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6254,6 +6249,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6280,10 +6280,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122289532</v>
+        <v>122289765</v>
       </c>
       <c r="B56" t="n">
-        <v>79240</v>
+        <v>90826</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6296,21 +6296,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473191</v>
+        <v>472815</v>
       </c>
       <c r="R56" t="n">
-        <v>6815504</v>
+        <v>6815646</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122289598</v>
+        <v>122289730</v>
       </c>
       <c r="B57" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6398,21 +6398,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6422,10 +6422,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473022</v>
+        <v>472958</v>
       </c>
       <c r="R57" t="n">
-        <v>6815732</v>
+        <v>6815427</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6484,10 +6484,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122289513</v>
+        <v>122289675</v>
       </c>
       <c r="B58" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6500,21 +6500,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>472966</v>
+        <v>472745</v>
       </c>
       <c r="R58" t="n">
-        <v>6815390</v>
+        <v>6815068</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122289675</v>
+        <v>122289619</v>
       </c>
       <c r="B59" t="n">
         <v>78651</v>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>472745</v>
+        <v>473228</v>
       </c>
       <c r="R59" t="n">
-        <v>6815068</v>
+        <v>6815569</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122289619</v>
+        <v>122289712</v>
       </c>
       <c r="B60" t="n">
         <v>78651</v>
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473228</v>
+        <v>472971</v>
       </c>
       <c r="R60" t="n">
-        <v>6815569</v>
+        <v>6815298</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122289712</v>
+        <v>122289613</v>
       </c>
       <c r="B61" t="n">
-        <v>78651</v>
+        <v>78387</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6806,21 +6806,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>472971</v>
+        <v>473014</v>
       </c>
       <c r="R61" t="n">
-        <v>6815298</v>
+        <v>6815496</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122289613</v>
+        <v>122289485</v>
       </c>
       <c r="B62" t="n">
-        <v>78387</v>
+        <v>79269</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6908,21 +6908,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122289485</v>
+        <v>122289562</v>
       </c>
       <c r="B63" t="n">
-        <v>79269</v>
+        <v>57379</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7010,34 +7010,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473014</v>
+        <v>472869</v>
       </c>
       <c r="R63" t="n">
-        <v>6815496</v>
+        <v>6815446</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7070,6 +7075,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7096,7 +7106,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122289562</v>
+        <v>122289563</v>
       </c>
       <c r="B64" t="n">
         <v>57379</v>
@@ -7141,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>472869</v>
+        <v>472874</v>
       </c>
       <c r="R64" t="n">
-        <v>6815446</v>
+        <v>6815282</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7208,10 +7218,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122289563</v>
+        <v>122289513</v>
       </c>
       <c r="B65" t="n">
-        <v>57379</v>
+        <v>78685</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7224,39 +7234,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>472874</v>
+        <v>472966</v>
       </c>
       <c r="R65" t="n">
-        <v>6815282</v>
+        <v>6815390</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7289,11 +7294,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7422,10 +7422,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122289608</v>
+        <v>122289716</v>
       </c>
       <c r="B67" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7438,21 +7438,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472951</v>
+        <v>472966</v>
       </c>
       <c r="R67" t="n">
-        <v>6815418</v>
+        <v>6815380</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122289607</v>
+        <v>122289572</v>
       </c>
       <c r="B68" t="n">
-        <v>78388</v>
+        <v>57379</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7540,34 +7540,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472871</v>
+        <v>472916</v>
       </c>
       <c r="R68" t="n">
-        <v>6815157</v>
+        <v>6815362</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7600,6 +7605,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7626,10 +7636,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122289716</v>
+        <v>122289615</v>
       </c>
       <c r="B69" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7642,34 +7652,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472966</v>
+        <v>472712</v>
       </c>
       <c r="R69" t="n">
-        <v>6815380</v>
+        <v>6815141</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7702,6 +7717,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7728,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289676</v>
+        <v>122289769</v>
       </c>
       <c r="B70" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7744,34 +7764,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472759</v>
+        <v>472842</v>
       </c>
       <c r="R70" t="n">
-        <v>6815052</v>
+        <v>6815605</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7804,6 +7829,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7830,7 +7860,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289572</v>
+        <v>122289560</v>
       </c>
       <c r="B71" t="n">
         <v>57379</v>
@@ -7875,10 +7905,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472916</v>
+        <v>472880</v>
       </c>
       <c r="R71" t="n">
-        <v>6815362</v>
+        <v>6815442</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7942,10 +7972,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122289615</v>
+        <v>122289676</v>
       </c>
       <c r="B72" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7958,39 +7988,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472712</v>
+        <v>472759</v>
       </c>
       <c r="R72" t="n">
-        <v>6815141</v>
+        <v>6815052</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8023,11 +8048,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8054,10 +8074,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122289769</v>
+        <v>122289608</v>
       </c>
       <c r="B73" t="n">
-        <v>57379</v>
+        <v>78388</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8070,39 +8090,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472842</v>
+        <v>472951</v>
       </c>
       <c r="R73" t="n">
-        <v>6815605</v>
+        <v>6815418</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8135,11 +8150,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8166,10 +8176,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289560</v>
+        <v>122289607</v>
       </c>
       <c r="B74" t="n">
-        <v>57379</v>
+        <v>78388</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8182,39 +8192,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472880</v>
+        <v>472871</v>
       </c>
       <c r="R74" t="n">
-        <v>6815442</v>
+        <v>6815157</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8247,11 +8252,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8278,10 +8278,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122289650</v>
+        <v>122289576</v>
       </c>
       <c r="B75" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8294,34 +8294,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472845</v>
+        <v>473233</v>
       </c>
       <c r="R75" t="n">
-        <v>6815328</v>
+        <v>6815571</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8354,6 +8359,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8380,10 +8390,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122289477</v>
+        <v>122289650</v>
       </c>
       <c r="B76" t="n">
-        <v>79269</v>
+        <v>78651</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8396,21 +8406,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8420,10 +8430,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472716</v>
+        <v>472845</v>
       </c>
       <c r="R76" t="n">
-        <v>6815299</v>
+        <v>6815328</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8482,10 +8492,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122289729</v>
+        <v>122289477</v>
       </c>
       <c r="B77" t="n">
-        <v>78651</v>
+        <v>79269</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8498,21 +8508,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8522,10 +8532,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>472957</v>
+        <v>472716</v>
       </c>
       <c r="R77" t="n">
-        <v>6815421</v>
+        <v>6815299</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8584,7 +8594,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122289656</v>
+        <v>122289729</v>
       </c>
       <c r="B78" t="n">
         <v>78651</v>
@@ -8624,10 +8634,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472748</v>
+        <v>472957</v>
       </c>
       <c r="R78" t="n">
-        <v>6815374</v>
+        <v>6815421</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8686,7 +8696,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122289660</v>
+        <v>122289656</v>
       </c>
       <c r="B79" t="n">
         <v>78651</v>
@@ -8726,10 +8736,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>472716</v>
+        <v>472748</v>
       </c>
       <c r="R79" t="n">
-        <v>6815316</v>
+        <v>6815374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8788,7 +8798,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122289737</v>
+        <v>122289660</v>
       </c>
       <c r="B80" t="n">
         <v>78651</v>
@@ -8828,10 +8838,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>473035</v>
+        <v>472716</v>
       </c>
       <c r="R80" t="n">
-        <v>6815416</v>
+        <v>6815316</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8890,10 +8900,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122289491</v>
+        <v>122289737</v>
       </c>
       <c r="B81" t="n">
-        <v>74752</v>
+        <v>78651</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8906,21 +8916,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8930,10 +8940,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>472841</v>
+        <v>473035</v>
       </c>
       <c r="R81" t="n">
-        <v>6815128</v>
+        <v>6815416</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8992,10 +9002,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122289576</v>
+        <v>122289491</v>
       </c>
       <c r="B82" t="n">
-        <v>57379</v>
+        <v>74752</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9008,39 +9018,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>473233</v>
+        <v>472841</v>
       </c>
       <c r="R82" t="n">
-        <v>6815571</v>
+        <v>6815128</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9073,11 +9078,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11271,10 +11271,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122289617</v>
+        <v>122289582</v>
       </c>
       <c r="B104" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11287,34 +11287,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472731</v>
+        <v>472813</v>
       </c>
       <c r="R104" t="n">
-        <v>6815383</v>
+        <v>6815369</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11347,6 +11352,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11373,10 +11383,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122289754</v>
+        <v>122289584</v>
       </c>
       <c r="B105" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11389,34 +11399,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>473240</v>
+        <v>473037</v>
       </c>
       <c r="R105" t="n">
-        <v>6815620</v>
+        <v>6815020</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11449,6 +11464,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11475,10 +11495,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122289642</v>
+        <v>122289579</v>
       </c>
       <c r="B106" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11491,34 +11511,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472875</v>
+        <v>472828</v>
       </c>
       <c r="R106" t="n">
-        <v>6815470</v>
+        <v>6815624</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11551,6 +11576,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11577,10 +11607,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122289746</v>
+        <v>122289566</v>
       </c>
       <c r="B107" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11593,34 +11623,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>473192</v>
+        <v>472846</v>
       </c>
       <c r="R107" t="n">
-        <v>6815502</v>
+        <v>6815099</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,6 +11688,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11679,10 +11719,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122289665</v>
+        <v>122289589</v>
       </c>
       <c r="B108" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11695,34 +11735,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472722</v>
+        <v>472928</v>
       </c>
       <c r="R108" t="n">
-        <v>6815109</v>
+        <v>6815346</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,6 +11800,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11781,10 +11831,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122289684</v>
+        <v>122289516</v>
       </c>
       <c r="B109" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11797,21 +11847,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11821,10 +11871,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472882</v>
+        <v>473107</v>
       </c>
       <c r="R109" t="n">
-        <v>6815139</v>
+        <v>6815366</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11883,10 +11933,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122289582</v>
+        <v>122289520</v>
       </c>
       <c r="B110" t="n">
-        <v>57379</v>
+        <v>78685</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11899,39 +11949,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>472813</v>
+        <v>473245</v>
       </c>
       <c r="R110" t="n">
-        <v>6815369</v>
+        <v>6815602</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11964,11 +12009,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11995,10 +12035,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122289584</v>
+        <v>122289617</v>
       </c>
       <c r="B111" t="n">
-        <v>57379</v>
+        <v>90826</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12011,39 +12051,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>473037</v>
+        <v>472731</v>
       </c>
       <c r="R111" t="n">
-        <v>6815020</v>
+        <v>6815383</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12076,11 +12111,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12107,10 +12137,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122289579</v>
+        <v>122289754</v>
       </c>
       <c r="B112" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12123,39 +12153,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>472828</v>
+        <v>473240</v>
       </c>
       <c r="R112" t="n">
-        <v>6815624</v>
+        <v>6815620</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12188,11 +12213,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12219,10 +12239,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122289566</v>
+        <v>122289642</v>
       </c>
       <c r="B113" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12235,39 +12255,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>472846</v>
+        <v>472875</v>
       </c>
       <c r="R113" t="n">
-        <v>6815099</v>
+        <v>6815470</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12300,11 +12315,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12331,10 +12341,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122289589</v>
+        <v>122289746</v>
       </c>
       <c r="B114" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12347,39 +12357,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>472928</v>
+        <v>473192</v>
       </c>
       <c r="R114" t="n">
-        <v>6815346</v>
+        <v>6815502</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12412,11 +12417,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12443,10 +12443,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122289531</v>
+        <v>122289665</v>
       </c>
       <c r="B115" t="n">
-        <v>79240</v>
+        <v>78651</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12459,21 +12459,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12483,10 +12483,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>473013</v>
+        <v>472722</v>
       </c>
       <c r="R115" t="n">
-        <v>6815498</v>
+        <v>6815109</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12545,10 +12545,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122289516</v>
+        <v>122289684</v>
       </c>
       <c r="B116" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12561,21 +12561,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12585,10 +12585,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>473107</v>
+        <v>472882</v>
       </c>
       <c r="R116" t="n">
-        <v>6815366</v>
+        <v>6815139</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12647,10 +12647,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122289520</v>
+        <v>122289531</v>
       </c>
       <c r="B117" t="n">
-        <v>78685</v>
+        <v>79240</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12663,21 +12663,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12687,10 +12687,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>473245</v>
+        <v>473013</v>
       </c>
       <c r="R117" t="n">
-        <v>6815602</v>
+        <v>6815498</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12749,10 +12749,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122289567</v>
+        <v>122289717</v>
       </c>
       <c r="B118" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12765,39 +12765,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>472851</v>
+        <v>472949</v>
       </c>
       <c r="R118" t="n">
-        <v>6815154</v>
+        <v>6815365</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12830,11 +12825,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12861,10 +12851,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122289588</v>
+        <v>122289750</v>
       </c>
       <c r="B119" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12877,39 +12867,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>472971</v>
+        <v>473232</v>
       </c>
       <c r="R119" t="n">
-        <v>6815298</v>
+        <v>6815538</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12942,11 +12927,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12973,10 +12953,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122289580</v>
+        <v>122289657</v>
       </c>
       <c r="B120" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12989,39 +12969,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>472862</v>
+        <v>472730</v>
       </c>
       <c r="R120" t="n">
-        <v>6815472</v>
+        <v>6815383</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13054,11 +13029,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13085,10 +13055,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122289517</v>
+        <v>122289622</v>
       </c>
       <c r="B121" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13101,21 +13071,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13125,10 +13095,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>473149</v>
+        <v>472955</v>
       </c>
       <c r="R121" t="n">
-        <v>6815391</v>
+        <v>6815658</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13187,10 +13157,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122289521</v>
+        <v>122289567</v>
       </c>
       <c r="B122" t="n">
-        <v>78685</v>
+        <v>57379</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13203,34 +13173,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>473236</v>
+        <v>472851</v>
       </c>
       <c r="R122" t="n">
-        <v>6815621</v>
+        <v>6815154</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13263,6 +13238,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13289,10 +13269,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122289750</v>
+        <v>122289517</v>
       </c>
       <c r="B123" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13305,21 +13285,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13329,10 +13309,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>473232</v>
+        <v>473149</v>
       </c>
       <c r="R123" t="n">
-        <v>6815538</v>
+        <v>6815391</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13391,10 +13371,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122289549</v>
+        <v>122289521</v>
       </c>
       <c r="B124" t="n">
-        <v>79733</v>
+        <v>78685</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13407,21 +13387,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13431,10 +13411,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>472766</v>
+        <v>473236</v>
       </c>
       <c r="R124" t="n">
-        <v>6815366</v>
+        <v>6815621</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13493,10 +13473,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122289717</v>
+        <v>122289549</v>
       </c>
       <c r="B125" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13509,21 +13489,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13533,10 +13513,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>472949</v>
+        <v>472766</v>
       </c>
       <c r="R125" t="n">
-        <v>6815365</v>
+        <v>6815366</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13697,10 +13677,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122289657</v>
+        <v>122289588</v>
       </c>
       <c r="B127" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13713,34 +13693,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>472730</v>
+        <v>472971</v>
       </c>
       <c r="R127" t="n">
-        <v>6815383</v>
+        <v>6815298</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13773,6 +13758,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13799,10 +13789,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122289622</v>
+        <v>122289580</v>
       </c>
       <c r="B128" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13815,34 +13805,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>472955</v>
+        <v>472862</v>
       </c>
       <c r="R128" t="n">
-        <v>6815658</v>
+        <v>6815472</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13875,6 +13870,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -22395,10 +22395,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289616</v>
+        <v>122289649</v>
       </c>
       <c r="B211" t="n">
-        <v>90826</v>
+        <v>78651</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22411,21 +22411,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22435,10 +22435,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>473244</v>
+        <v>472853</v>
       </c>
       <c r="R211" t="n">
-        <v>6815667</v>
+        <v>6815291</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22497,7 +22497,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289669</v>
+        <v>122289689</v>
       </c>
       <c r="B212" t="n">
         <v>78651</v>
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>472718</v>
+        <v>472954</v>
       </c>
       <c r="R212" t="n">
         <v>6815041</v>
@@ -22599,10 +22599,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289666</v>
+        <v>122289492</v>
       </c>
       <c r="B213" t="n">
-        <v>78651</v>
+        <v>74752</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22615,21 +22615,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22639,10 +22639,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>472737</v>
+        <v>472897</v>
       </c>
       <c r="R213" t="n">
-        <v>6815084</v>
+        <v>6815078</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22701,7 +22701,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289662</v>
+        <v>122289711</v>
       </c>
       <c r="B214" t="n">
         <v>78651</v>
@@ -22741,10 +22741,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>472697</v>
+        <v>472976</v>
       </c>
       <c r="R214" t="n">
-        <v>6815151</v>
+        <v>6815272</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22803,10 +22803,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289649</v>
+        <v>122289616</v>
       </c>
       <c r="B215" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22819,21 +22819,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22843,10 +22843,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>472853</v>
+        <v>473244</v>
       </c>
       <c r="R215" t="n">
-        <v>6815291</v>
+        <v>6815667</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22905,7 +22905,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289689</v>
+        <v>122289669</v>
       </c>
       <c r="B216" t="n">
         <v>78651</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>472954</v>
+        <v>472718</v>
       </c>
       <c r="R216" t="n">
         <v>6815041</v>
@@ -23007,10 +23007,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289492</v>
+        <v>122289666</v>
       </c>
       <c r="B217" t="n">
-        <v>74752</v>
+        <v>78651</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23023,21 +23023,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23047,10 +23047,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>472897</v>
+        <v>472737</v>
       </c>
       <c r="R217" t="n">
-        <v>6815078</v>
+        <v>6815084</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23109,7 +23109,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122289667</v>
+        <v>122289662</v>
       </c>
       <c r="B218" t="n">
         <v>78651</v>
@@ -23149,10 +23149,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>472741</v>
+        <v>472697</v>
       </c>
       <c r="R218" t="n">
-        <v>6815075</v>
+        <v>6815151</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23211,7 +23211,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289753</v>
+        <v>122289667</v>
       </c>
       <c r="B219" t="n">
         <v>78651</v>
@@ -23251,10 +23251,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>473242</v>
+        <v>472741</v>
       </c>
       <c r="R219" t="n">
-        <v>6815602</v>
+        <v>6815075</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23313,10 +23313,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289557</v>
+        <v>122289753</v>
       </c>
       <c r="B220" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23329,39 +23329,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>473230</v>
+        <v>473242</v>
       </c>
       <c r="R220" t="n">
-        <v>6815520</v>
+        <v>6815602</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23394,11 +23389,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23425,10 +23415,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289711</v>
+        <v>122289488</v>
       </c>
       <c r="B221" t="n">
-        <v>78651</v>
+        <v>79269</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23441,21 +23431,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23465,10 +23455,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>472976</v>
+        <v>473234</v>
       </c>
       <c r="R221" t="n">
-        <v>6815272</v>
+        <v>6815734</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23527,10 +23517,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289488</v>
+        <v>122289495</v>
       </c>
       <c r="B222" t="n">
-        <v>79269</v>
+        <v>74752</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23543,21 +23533,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23567,10 +23557,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>473234</v>
+        <v>473212</v>
       </c>
       <c r="R222" t="n">
-        <v>6815734</v>
+        <v>6815464</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23629,10 +23619,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289495</v>
+        <v>122289557</v>
       </c>
       <c r="B223" t="n">
-        <v>74752</v>
+        <v>57379</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23645,34 +23635,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>473212</v>
+        <v>473230</v>
       </c>
       <c r="R223" t="n">
-        <v>6815464</v>
+        <v>6815520</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23705,6 +23700,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD223" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122289669</v>
+        <v>122289571</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,29 +1044,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472718</v>
+        <v>472895</v>
       </c>
       <c r="R5" t="n">
-        <v>6815041</v>
+        <v>6815359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,6 +1104,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122289658</v>
+        <v>122289669</v>
       </c>
       <c r="B6" t="n">
         <v>78652</v>
@@ -1160,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472721</v>
+        <v>472718</v>
       </c>
       <c r="R6" t="n">
-        <v>6815373</v>
+        <v>6815041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122289645</v>
+        <v>122289658</v>
       </c>
       <c r="B7" t="n">
         <v>78652</v>
@@ -1257,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472889</v>
+        <v>472721</v>
       </c>
       <c r="R7" t="n">
-        <v>6815359</v>
+        <v>6815373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122289712</v>
+        <v>122289645</v>
       </c>
       <c r="B8" t="n">
         <v>78652</v>
@@ -1354,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472971</v>
+        <v>472889</v>
       </c>
       <c r="R8" t="n">
-        <v>6815298</v>
+        <v>6815359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1426,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122289667</v>
+        <v>122289712</v>
       </c>
       <c r="B9" t="n">
         <v>78652</v>
@@ -1451,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472741</v>
+        <v>472971</v>
       </c>
       <c r="R9" t="n">
-        <v>6815075</v>
+        <v>6815298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122289659</v>
+        <v>122289667</v>
       </c>
       <c r="B10" t="n">
         <v>78652</v>
@@ -1548,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472724</v>
+        <v>472741</v>
       </c>
       <c r="R10" t="n">
-        <v>6815345</v>
+        <v>6815075</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122289673</v>
+        <v>122289659</v>
       </c>
       <c r="B11" t="n">
         <v>78652</v>
@@ -1645,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472729</v>
+        <v>472724</v>
       </c>
       <c r="R11" t="n">
-        <v>6815062</v>
+        <v>6815345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,7 +1717,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122289704</v>
+        <v>122289673</v>
       </c>
       <c r="B12" t="n">
         <v>78652</v>
@@ -1742,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473036</v>
+        <v>472729</v>
       </c>
       <c r="R12" t="n">
-        <v>6815177</v>
+        <v>6815062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122289714</v>
+        <v>122289704</v>
       </c>
       <c r="B13" t="n">
         <v>78652</v>
@@ -1839,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472966</v>
+        <v>473036</v>
       </c>
       <c r="R13" t="n">
-        <v>6815345</v>
+        <v>6815177</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,7 +1911,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122289768</v>
+        <v>122289714</v>
       </c>
       <c r="B14" t="n">
         <v>78652</v>
@@ -1936,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472877</v>
+        <v>472966</v>
       </c>
       <c r="R14" t="n">
-        <v>6815103</v>
+        <v>6815345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +2008,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122289736</v>
+        <v>122289768</v>
       </c>
       <c r="B15" t="n">
         <v>78652</v>
@@ -2033,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473027</v>
+        <v>472877</v>
       </c>
       <c r="R15" t="n">
-        <v>6815426</v>
+        <v>6815103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,10 +2105,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122289507</v>
+        <v>122289736</v>
       </c>
       <c r="B16" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,16 +2121,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2130,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473043</v>
+        <v>473027</v>
       </c>
       <c r="R16" t="n">
-        <v>6815153</v>
+        <v>6815426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,7 +2202,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122289500</v>
+        <v>122289507</v>
       </c>
       <c r="B17" t="n">
         <v>78686</v>
@@ -2227,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472769</v>
+        <v>473043</v>
       </c>
       <c r="R17" t="n">
-        <v>6815363</v>
+        <v>6815153</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2289,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122289571</v>
+        <v>122289500</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2305,34 +2315,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472895</v>
+        <v>472769</v>
       </c>
       <c r="R18" t="n">
-        <v>6815359</v>
+        <v>6815363</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,11 +2370,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3473,10 +3473,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289699</v>
+        <v>122289767</v>
       </c>
       <c r="B30" t="n">
-        <v>78652</v>
+        <v>90831</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473050</v>
+        <v>472819</v>
       </c>
       <c r="R30" t="n">
-        <v>6815098</v>
+        <v>6815624</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289700</v>
+        <v>122289717</v>
       </c>
       <c r="B31" t="n">
         <v>78652</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473049</v>
+        <v>472949</v>
       </c>
       <c r="R31" t="n">
-        <v>6815133</v>
+        <v>6815365</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122289665</v>
+        <v>122289698</v>
       </c>
       <c r="B32" t="n">
         <v>78652</v>
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472722</v>
+        <v>473037</v>
       </c>
       <c r="R32" t="n">
-        <v>6815109</v>
+        <v>6815086</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3764,10 +3764,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289767</v>
+        <v>122289762</v>
       </c>
       <c r="B33" t="n">
-        <v>90831</v>
+        <v>78652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472819</v>
+        <v>473222</v>
       </c>
       <c r="R33" t="n">
-        <v>6815624</v>
+        <v>6815741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122289717</v>
+        <v>122289702</v>
       </c>
       <c r="B34" t="n">
         <v>78652</v>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472949</v>
+        <v>473044</v>
       </c>
       <c r="R34" t="n">
-        <v>6815365</v>
+        <v>6815169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122289698</v>
+        <v>122289641</v>
       </c>
       <c r="B35" t="n">
         <v>78652</v>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473037</v>
+        <v>472882</v>
       </c>
       <c r="R35" t="n">
-        <v>6815086</v>
+        <v>6815476</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122289762</v>
+        <v>122289655</v>
       </c>
       <c r="B36" t="n">
         <v>78652</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473222</v>
+        <v>472766</v>
       </c>
       <c r="R36" t="n">
-        <v>6815741</v>
+        <v>6815363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122289702</v>
+        <v>122289699</v>
       </c>
       <c r="B37" t="n">
         <v>78652</v>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473044</v>
+        <v>473050</v>
       </c>
       <c r="R37" t="n">
-        <v>6815169</v>
+        <v>6815098</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122289641</v>
+        <v>122289700</v>
       </c>
       <c r="B38" t="n">
         <v>78652</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472882</v>
+        <v>473049</v>
       </c>
       <c r="R38" t="n">
-        <v>6815476</v>
+        <v>6815133</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122289655</v>
+        <v>122289665</v>
       </c>
       <c r="B39" t="n">
         <v>78652</v>
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472766</v>
+        <v>472722</v>
       </c>
       <c r="R39" t="n">
-        <v>6815363</v>
+        <v>6815109</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,10 +4637,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122289713</v>
+        <v>122289553</v>
       </c>
       <c r="B42" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4653,29 +4653,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472952</v>
+        <v>472880</v>
       </c>
       <c r="R42" t="n">
-        <v>6815339</v>
+        <v>6815136</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4708,6 +4713,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4734,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122289676</v>
+        <v>122289537</v>
       </c>
       <c r="B43" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4750,29 +4760,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472759</v>
+        <v>472724</v>
       </c>
       <c r="R43" t="n">
-        <v>6815052</v>
+        <v>6815093</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4831,10 +4846,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122289630</v>
+        <v>122289520</v>
       </c>
       <c r="B44" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4847,16 +4862,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4866,10 +4881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473038</v>
+        <v>473245</v>
       </c>
       <c r="R44" t="n">
-        <v>6815393</v>
+        <v>6815602</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4928,7 +4943,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122289663</v>
+        <v>122289713</v>
       </c>
       <c r="B45" t="n">
         <v>78652</v>
@@ -4963,10 +4978,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472719</v>
+        <v>472952</v>
       </c>
       <c r="R45" t="n">
-        <v>6815128</v>
+        <v>6815339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5025,7 +5040,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122289657</v>
+        <v>122289676</v>
       </c>
       <c r="B46" t="n">
         <v>78652</v>
@@ -5060,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472730</v>
+        <v>472759</v>
       </c>
       <c r="R46" t="n">
-        <v>6815383</v>
+        <v>6815052</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5122,7 +5137,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122289741</v>
+        <v>122289630</v>
       </c>
       <c r="B47" t="n">
         <v>78652</v>
@@ -5157,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473161</v>
+        <v>473038</v>
       </c>
       <c r="R47" t="n">
-        <v>6815418</v>
+        <v>6815393</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5219,7 +5234,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122289622</v>
+        <v>122289663</v>
       </c>
       <c r="B48" t="n">
         <v>78652</v>
@@ -5254,10 +5269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472955</v>
+        <v>472719</v>
       </c>
       <c r="R48" t="n">
-        <v>6815658</v>
+        <v>6815128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5316,10 +5331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122289520</v>
+        <v>122289657</v>
       </c>
       <c r="B49" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5332,16 +5347,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5351,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473245</v>
+        <v>472730</v>
       </c>
       <c r="R49" t="n">
-        <v>6815602</v>
+        <v>6815383</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5413,10 +5428,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122289553</v>
+        <v>122289741</v>
       </c>
       <c r="B50" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5429,34 +5444,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472880</v>
+        <v>473161</v>
       </c>
       <c r="R50" t="n">
-        <v>6815136</v>
+        <v>6815418</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5489,11 +5499,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5520,10 +5525,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122289537</v>
+        <v>122289622</v>
       </c>
       <c r="B51" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5536,34 +5541,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>472724</v>
+        <v>472955</v>
       </c>
       <c r="R51" t="n">
-        <v>6815093</v>
+        <v>6815658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7485,10 +7485,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289549</v>
+        <v>122289609</v>
       </c>
       <c r="B71" t="n">
-        <v>79734</v>
+        <v>80609</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7501,16 +7501,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472766</v>
+        <v>472975</v>
       </c>
       <c r="R71" t="n">
-        <v>6815366</v>
+        <v>6815664</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7582,10 +7582,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122289609</v>
+        <v>122289549</v>
       </c>
       <c r="B72" t="n">
-        <v>80609</v>
+        <v>79734</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7598,16 +7598,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472975</v>
+        <v>472766</v>
       </c>
       <c r="R72" t="n">
-        <v>6815664</v>
+        <v>6815366</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122289648</v>
+        <v>122289578</v>
       </c>
       <c r="B73" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7695,29 +7695,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472874</v>
+        <v>472860</v>
       </c>
       <c r="R73" t="n">
-        <v>6815282</v>
+        <v>6815679</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7750,6 +7755,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7776,7 +7786,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289637</v>
+        <v>122289648</v>
       </c>
       <c r="B74" t="n">
         <v>78652</v>
@@ -7811,10 +7821,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472863</v>
+        <v>472874</v>
       </c>
       <c r="R74" t="n">
-        <v>6815525</v>
+        <v>6815282</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7873,7 +7883,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122289742</v>
+        <v>122289637</v>
       </c>
       <c r="B75" t="n">
         <v>78652</v>
@@ -7908,10 +7918,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>473186</v>
+        <v>472863</v>
       </c>
       <c r="R75" t="n">
-        <v>6815462</v>
+        <v>6815525</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7970,7 +7980,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122289674</v>
+        <v>122289742</v>
       </c>
       <c r="B76" t="n">
         <v>78652</v>
@@ -8005,10 +8015,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472736</v>
+        <v>473186</v>
       </c>
       <c r="R76" t="n">
-        <v>6815067</v>
+        <v>6815462</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8067,7 +8077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122289632</v>
+        <v>122289674</v>
       </c>
       <c r="B77" t="n">
         <v>78652</v>
@@ -8102,10 +8112,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>472754</v>
+        <v>472736</v>
       </c>
       <c r="R77" t="n">
-        <v>6815718</v>
+        <v>6815067</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8164,10 +8174,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122289578</v>
+        <v>122289632</v>
       </c>
       <c r="B78" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8180,34 +8190,29 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472860</v>
+        <v>472754</v>
       </c>
       <c r="R78" t="n">
-        <v>6815679</v>
+        <v>6815718</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8240,11 +8245,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10231,10 +10231,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122289653</v>
+        <v>122289607</v>
       </c>
       <c r="B99" t="n">
-        <v>78652</v>
+        <v>78389</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10247,16 +10247,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>472794</v>
+        <v>472871</v>
       </c>
       <c r="R99" t="n">
-        <v>6815364</v>
+        <v>6815157</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10328,10 +10328,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122289611</v>
+        <v>122289653</v>
       </c>
       <c r="B100" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10344,16 +10344,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472749</v>
+        <v>472794</v>
       </c>
       <c r="R100" t="n">
-        <v>6815725</v>
+        <v>6815364</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122289476</v>
+        <v>122289611</v>
       </c>
       <c r="B101" t="n">
-        <v>79270</v>
+        <v>78388</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10441,16 +10441,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>472813</v>
+        <v>472749</v>
       </c>
       <c r="R101" t="n">
-        <v>6815369</v>
+        <v>6815725</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10522,10 +10522,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122289747</v>
+        <v>122289476</v>
       </c>
       <c r="B102" t="n">
-        <v>78652</v>
+        <v>79270</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10538,16 +10538,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>473203</v>
+        <v>472813</v>
       </c>
       <c r="R102" t="n">
-        <v>6815521</v>
+        <v>6815369</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122289743</v>
+        <v>122289747</v>
       </c>
       <c r="B103" t="n">
         <v>78652</v>
@@ -10654,10 +10654,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>473207</v>
+        <v>473203</v>
       </c>
       <c r="R103" t="n">
-        <v>6815471</v>
+        <v>6815521</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10716,7 +10716,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122289682</v>
+        <v>122289743</v>
       </c>
       <c r="B104" t="n">
         <v>78652</v>
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472846</v>
+        <v>473207</v>
       </c>
       <c r="R104" t="n">
-        <v>6815101</v>
+        <v>6815471</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10813,7 +10813,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122289734</v>
+        <v>122289682</v>
       </c>
       <c r="B105" t="n">
         <v>78652</v>
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>473018</v>
+        <v>472846</v>
       </c>
       <c r="R105" t="n">
-        <v>6815464</v>
+        <v>6815101</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10910,7 +10910,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122289660</v>
+        <v>122289734</v>
       </c>
       <c r="B106" t="n">
         <v>78652</v>
@@ -10945,10 +10945,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472716</v>
+        <v>473018</v>
       </c>
       <c r="R106" t="n">
-        <v>6815316</v>
+        <v>6815464</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11007,7 +11007,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122289693</v>
+        <v>122289660</v>
       </c>
       <c r="B107" t="n">
         <v>78652</v>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>473002</v>
+        <v>472716</v>
       </c>
       <c r="R107" t="n">
-        <v>6814987</v>
+        <v>6815316</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122289678</v>
+        <v>122289693</v>
       </c>
       <c r="B108" t="n">
         <v>78652</v>
@@ -11139,10 +11139,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472765</v>
+        <v>473002</v>
       </c>
       <c r="R108" t="n">
-        <v>6815044</v>
+        <v>6814987</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11201,7 +11201,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122289684</v>
+        <v>122289678</v>
       </c>
       <c r="B109" t="n">
         <v>78652</v>
@@ -11236,10 +11236,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472882</v>
+        <v>472765</v>
       </c>
       <c r="R109" t="n">
-        <v>6815139</v>
+        <v>6815044</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11298,7 +11298,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122289726</v>
+        <v>122289684</v>
       </c>
       <c r="B110" t="n">
         <v>78652</v>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>472934</v>
+        <v>472882</v>
       </c>
       <c r="R110" t="n">
-        <v>6815384</v>
+        <v>6815139</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122289519</v>
+        <v>122289726</v>
       </c>
       <c r="B111" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11411,16 +11411,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>473217</v>
+        <v>472934</v>
       </c>
       <c r="R111" t="n">
-        <v>6815515</v>
+        <v>6815384</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11492,10 +11492,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122289557</v>
+        <v>122289519</v>
       </c>
       <c r="B112" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11508,34 +11508,29 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>473230</v>
+        <v>473217</v>
       </c>
       <c r="R112" t="n">
-        <v>6815520</v>
+        <v>6815515</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11568,11 +11563,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11599,7 +11589,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122289586</v>
+        <v>122289557</v>
       </c>
       <c r="B113" t="n">
         <v>57379</v>
@@ -11630,7 +11620,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -11639,10 +11629,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>473036</v>
+        <v>473230</v>
       </c>
       <c r="R113" t="n">
-        <v>6815173</v>
+        <v>6815520</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11679,7 +11669,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11706,7 +11696,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122289588</v>
+        <v>122289586</v>
       </c>
       <c r="B114" t="n">
         <v>57379</v>
@@ -11746,10 +11736,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>472971</v>
+        <v>473036</v>
       </c>
       <c r="R114" t="n">
-        <v>6815298</v>
+        <v>6815173</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11813,10 +11803,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122289607</v>
+        <v>122289588</v>
       </c>
       <c r="B115" t="n">
-        <v>78389</v>
+        <v>57379</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -11829,29 +11819,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>472871</v>
+        <v>472971</v>
       </c>
       <c r="R115" t="n">
-        <v>6815157</v>
+        <v>6815298</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11884,6 +11879,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16281,10 +16281,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122289596</v>
+        <v>122289769</v>
       </c>
       <c r="B160" t="n">
-        <v>78389</v>
+        <v>57379</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16297,29 +16297,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>473223</v>
+        <v>472842</v>
       </c>
       <c r="R160" t="n">
-        <v>6815621</v>
+        <v>6815605</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16352,6 +16357,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16378,7 +16388,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122289769</v>
+        <v>122289575</v>
       </c>
       <c r="B161" t="n">
         <v>57379</v>
@@ -16418,10 +16428,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>472842</v>
+        <v>473231</v>
       </c>
       <c r="R161" t="n">
-        <v>6815605</v>
+        <v>6815546</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16485,7 +16495,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122289575</v>
+        <v>122289589</v>
       </c>
       <c r="B162" t="n">
         <v>57379</v>
@@ -16516,7 +16526,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -16525,10 +16535,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>473231</v>
+        <v>472928</v>
       </c>
       <c r="R162" t="n">
-        <v>6815546</v>
+        <v>6815346</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16565,7 +16575,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16592,10 +16602,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122289589</v>
+        <v>122289706</v>
       </c>
       <c r="B163" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -16608,34 +16618,29 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>472928</v>
+        <v>473015</v>
       </c>
       <c r="R163" t="n">
-        <v>6815346</v>
+        <v>6815193</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16668,11 +16673,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16699,7 +16699,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122289706</v>
+        <v>122289750</v>
       </c>
       <c r="B164" t="n">
         <v>78652</v>
@@ -16734,10 +16734,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>473015</v>
+        <v>473232</v>
       </c>
       <c r="R164" t="n">
-        <v>6815193</v>
+        <v>6815538</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16796,7 +16796,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122289750</v>
+        <v>122289695</v>
       </c>
       <c r="B165" t="n">
         <v>78652</v>
@@ -16831,10 +16831,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>473232</v>
+        <v>473035</v>
       </c>
       <c r="R165" t="n">
-        <v>6815538</v>
+        <v>6814991</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16893,10 +16893,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122289695</v>
+        <v>122289772</v>
       </c>
       <c r="B166" t="n">
-        <v>78652</v>
+        <v>78036</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -16909,16 +16909,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16928,10 +16928,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>473035</v>
+        <v>473001</v>
       </c>
       <c r="R166" t="n">
-        <v>6814991</v>
+        <v>6815720</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16990,10 +16990,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122289772</v>
+        <v>122289636</v>
       </c>
       <c r="B167" t="n">
-        <v>78036</v>
+        <v>78652</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17006,16 +17006,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17025,10 +17025,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>473001</v>
+        <v>472843</v>
       </c>
       <c r="R167" t="n">
-        <v>6815720</v>
+        <v>6815598</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17087,7 +17087,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122289636</v>
+        <v>122289688</v>
       </c>
       <c r="B168" t="n">
         <v>78652</v>
@@ -17122,10 +17122,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>472843</v>
+        <v>472911</v>
       </c>
       <c r="R168" t="n">
-        <v>6815598</v>
+        <v>6815063</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17184,10 +17184,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122289688</v>
+        <v>122289501</v>
       </c>
       <c r="B169" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17200,16 +17200,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17219,10 +17219,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>472911</v>
+        <v>472722</v>
       </c>
       <c r="R169" t="n">
-        <v>6815063</v>
+        <v>6815373</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17281,10 +17281,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122289501</v>
+        <v>122289596</v>
       </c>
       <c r="B170" t="n">
-        <v>78686</v>
+        <v>78389</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17297,16 +17297,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17316,10 +17316,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>472722</v>
+        <v>473223</v>
       </c>
       <c r="R170" t="n">
-        <v>6815373</v>
+        <v>6815621</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17378,10 +17378,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122289498</v>
+        <v>122289771</v>
       </c>
       <c r="B171" t="n">
-        <v>78686</v>
+        <v>78297</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17394,16 +17394,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17413,10 +17413,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>472863</v>
+        <v>473227</v>
       </c>
       <c r="R171" t="n">
-        <v>6815525</v>
+        <v>6815737</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17475,10 +17475,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122289771</v>
+        <v>122289498</v>
       </c>
       <c r="B172" t="n">
-        <v>78297</v>
+        <v>78686</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -17491,16 +17491,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17510,10 +17510,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>473227</v>
+        <v>472863</v>
       </c>
       <c r="R172" t="n">
-        <v>6815737</v>
+        <v>6815525</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17572,10 +17572,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122289707</v>
+        <v>122289572</v>
       </c>
       <c r="B173" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -17588,29 +17588,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>473010</v>
+        <v>472916</v>
       </c>
       <c r="R173" t="n">
-        <v>6815184</v>
+        <v>6815362</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17643,6 +17648,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -17669,10 +17679,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122289616</v>
+        <v>122289577</v>
       </c>
       <c r="B174" t="n">
-        <v>90831</v>
+        <v>57379</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -17685,29 +17695,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>473244</v>
+        <v>472922</v>
       </c>
       <c r="R174" t="n">
-        <v>6815667</v>
+        <v>6815653</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17740,6 +17755,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -17766,10 +17786,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122289638</v>
+        <v>122289533</v>
       </c>
       <c r="B175" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -17782,29 +17802,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>472871</v>
+        <v>473021</v>
       </c>
       <c r="R175" t="n">
-        <v>6815512</v>
+        <v>6815478</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17863,10 +17888,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122289644</v>
+        <v>122289560</v>
       </c>
       <c r="B176" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -17879,29 +17904,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>472872</v>
+        <v>472880</v>
       </c>
       <c r="R176" t="n">
-        <v>6815410</v>
+        <v>6815442</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -17934,6 +17964,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -17960,7 +17995,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122289572</v>
+        <v>122289580</v>
       </c>
       <c r="B177" t="n">
         <v>57379</v>
@@ -17991,7 +18026,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -18000,10 +18035,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>472916</v>
+        <v>472862</v>
       </c>
       <c r="R177" t="n">
-        <v>6815362</v>
+        <v>6815472</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18040,7 +18075,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18067,10 +18102,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122289577</v>
+        <v>122289707</v>
       </c>
       <c r="B178" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18083,34 +18118,29 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>472922</v>
+        <v>473010</v>
       </c>
       <c r="R178" t="n">
-        <v>6815653</v>
+        <v>6815184</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18143,11 +18173,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18174,10 +18199,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122289533</v>
+        <v>122289616</v>
       </c>
       <c r="B179" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18190,34 +18215,29 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>473021</v>
+        <v>473244</v>
       </c>
       <c r="R179" t="n">
-        <v>6815478</v>
+        <v>6815667</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18276,10 +18296,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122289560</v>
+        <v>122289638</v>
       </c>
       <c r="B180" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18292,34 +18312,29 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>472880</v>
+        <v>472871</v>
       </c>
       <c r="R180" t="n">
-        <v>6815442</v>
+        <v>6815512</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18352,11 +18367,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18383,10 +18393,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122289580</v>
+        <v>122289644</v>
       </c>
       <c r="B181" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18399,34 +18409,29 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>472862</v>
+        <v>472872</v>
       </c>
       <c r="R181" t="n">
-        <v>6815472</v>
+        <v>6815410</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18459,11 +18464,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18490,10 +18490,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122289528</v>
+        <v>122289587</v>
       </c>
       <c r="B182" t="n">
-        <v>79241</v>
+        <v>57379</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -18506,29 +18506,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>473019</v>
+        <v>473000</v>
       </c>
       <c r="R182" t="n">
-        <v>6815730</v>
+        <v>6815184</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18561,6 +18566,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18587,10 +18597,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289517</v>
+        <v>122289619</v>
       </c>
       <c r="B183" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -18603,16 +18613,16 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18622,10 +18632,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>473149</v>
+        <v>473228</v>
       </c>
       <c r="R183" t="n">
-        <v>6815391</v>
+        <v>6815569</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18684,10 +18694,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289506</v>
+        <v>122289738</v>
       </c>
       <c r="B184" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -18700,16 +18710,16 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18719,10 +18729,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>473050</v>
+        <v>473045</v>
       </c>
       <c r="R184" t="n">
-        <v>6815098</v>
+        <v>6815390</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18781,7 +18791,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122289619</v>
+        <v>122289670</v>
       </c>
       <c r="B185" t="n">
         <v>78652</v>
@@ -18816,10 +18826,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>473228</v>
+        <v>472698</v>
       </c>
       <c r="R185" t="n">
-        <v>6815569</v>
+        <v>6815034</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18878,7 +18888,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289738</v>
+        <v>122289680</v>
       </c>
       <c r="B186" t="n">
         <v>78652</v>
@@ -18913,10 +18923,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>473045</v>
+        <v>472808</v>
       </c>
       <c r="R186" t="n">
-        <v>6815390</v>
+        <v>6815067</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18975,10 +18985,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289670</v>
+        <v>122289485</v>
       </c>
       <c r="B187" t="n">
-        <v>78652</v>
+        <v>79270</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -18991,16 +19001,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19010,10 +19020,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>472698</v>
+        <v>473014</v>
       </c>
       <c r="R187" t="n">
-        <v>6815034</v>
+        <v>6815496</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19072,10 +19082,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289680</v>
+        <v>122289517</v>
       </c>
       <c r="B188" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19088,16 +19098,16 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19107,10 +19117,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>472808</v>
+        <v>473149</v>
       </c>
       <c r="R188" t="n">
-        <v>6815067</v>
+        <v>6815391</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19169,10 +19179,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122289485</v>
+        <v>122289506</v>
       </c>
       <c r="B189" t="n">
-        <v>79270</v>
+        <v>78686</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19185,16 +19195,16 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19204,10 +19214,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>473014</v>
+        <v>473050</v>
       </c>
       <c r="R189" t="n">
-        <v>6815496</v>
+        <v>6815098</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19266,10 +19276,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289587</v>
+        <v>122289528</v>
       </c>
       <c r="B190" t="n">
-        <v>57379</v>
+        <v>79241</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19282,34 +19292,29 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>473000</v>
+        <v>473019</v>
       </c>
       <c r="R190" t="n">
-        <v>6815184</v>
+        <v>6815730</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19342,11 +19347,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20644,10 +20644,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122289512</v>
+        <v>122289671</v>
       </c>
       <c r="B204" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -20660,16 +20660,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20679,10 +20679,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>472977</v>
+        <v>472713</v>
       </c>
       <c r="R204" t="n">
-        <v>6815273</v>
+        <v>6815067</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20741,10 +20741,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122289513</v>
+        <v>122289735</v>
       </c>
       <c r="B205" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -20757,16 +20757,16 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20776,10 +20776,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>472966</v>
+        <v>473015</v>
       </c>
       <c r="R205" t="n">
-        <v>6815390</v>
+        <v>6815443</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20838,10 +20838,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122289525</v>
+        <v>122289487</v>
       </c>
       <c r="B206" t="n">
-        <v>95758</v>
+        <v>79270</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -20854,16 +20854,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -20873,10 +20873,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>472724</v>
+        <v>473192</v>
       </c>
       <c r="R206" t="n">
-        <v>6815100</v>
+        <v>6815503</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -20935,10 +20935,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122289594</v>
+        <v>122289621</v>
       </c>
       <c r="B207" t="n">
-        <v>74748</v>
+        <v>78652</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -20951,16 +20951,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -20970,10 +20970,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>472834</v>
+        <v>473076</v>
       </c>
       <c r="R207" t="n">
-        <v>6815612</v>
+        <v>6815660</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21032,10 +21032,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122289526</v>
+        <v>122289757</v>
       </c>
       <c r="B208" t="n">
-        <v>79241</v>
+        <v>78652</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21048,16 +21048,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21067,10 +21067,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>473224</v>
+        <v>473240</v>
       </c>
       <c r="R208" t="n">
-        <v>6815616</v>
+        <v>6815680</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21129,10 +21129,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122289671</v>
+        <v>122289480</v>
       </c>
       <c r="B209" t="n">
-        <v>78652</v>
+        <v>79270</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -21145,16 +21145,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21164,10 +21164,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>472713</v>
+        <v>472742</v>
       </c>
       <c r="R209" t="n">
-        <v>6815067</v>
+        <v>6815075</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21226,10 +21226,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122289735</v>
+        <v>122289512</v>
       </c>
       <c r="B210" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -21242,16 +21242,16 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21261,10 +21261,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>473015</v>
+        <v>472977</v>
       </c>
       <c r="R210" t="n">
-        <v>6815443</v>
+        <v>6815273</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21323,10 +21323,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289487</v>
+        <v>122289513</v>
       </c>
       <c r="B211" t="n">
-        <v>79270</v>
+        <v>78686</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -21339,16 +21339,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21358,10 +21358,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>473192</v>
+        <v>472966</v>
       </c>
       <c r="R211" t="n">
-        <v>6815503</v>
+        <v>6815390</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21420,10 +21420,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289621</v>
+        <v>122289525</v>
       </c>
       <c r="B212" t="n">
-        <v>78652</v>
+        <v>95758</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -21436,16 +21436,16 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21455,10 +21455,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>473076</v>
+        <v>472724</v>
       </c>
       <c r="R212" t="n">
-        <v>6815660</v>
+        <v>6815100</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21517,10 +21517,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289757</v>
+        <v>122289594</v>
       </c>
       <c r="B213" t="n">
-        <v>78652</v>
+        <v>74748</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -21533,16 +21533,16 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21552,10 +21552,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>473240</v>
+        <v>472834</v>
       </c>
       <c r="R213" t="n">
-        <v>6815680</v>
+        <v>6815612</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21614,10 +21614,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289480</v>
+        <v>122289568</v>
       </c>
       <c r="B214" t="n">
-        <v>79270</v>
+        <v>57379</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -21630,29 +21630,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>472742</v>
+        <v>472863</v>
       </c>
       <c r="R214" t="n">
-        <v>6815075</v>
+        <v>6815149</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21685,6 +21690,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -21711,7 +21721,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289568</v>
+        <v>122289555</v>
       </c>
       <c r="B215" t="n">
         <v>57379</v>
@@ -21751,10 +21761,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>472863</v>
+        <v>473055</v>
       </c>
       <c r="R215" t="n">
-        <v>6815149</v>
+        <v>6815710</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21791,7 +21801,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -21818,7 +21828,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289555</v>
+        <v>122289590</v>
       </c>
       <c r="B216" t="n">
         <v>57379</v>
@@ -21849,7 +21859,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -21858,10 +21868,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>473055</v>
+        <v>472945</v>
       </c>
       <c r="R216" t="n">
-        <v>6815710</v>
+        <v>6815381</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -21898,7 +21908,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Äldre rnghack (tall)</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -21925,10 +21935,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289590</v>
+        <v>122289526</v>
       </c>
       <c r="B217" t="n">
-        <v>57379</v>
+        <v>79241</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -21941,34 +21951,29 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>472945</v>
+        <v>473224</v>
       </c>
       <c r="R217" t="n">
-        <v>6815381</v>
+        <v>6815616</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22001,11 +22006,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -22032,10 +22032,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122289592</v>
+        <v>122289773</v>
       </c>
       <c r="B218" t="n">
-        <v>57379</v>
+        <v>78036</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22048,34 +22048,29 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>473038</v>
+        <v>473042</v>
       </c>
       <c r="R218" t="n">
-        <v>6815393</v>
+        <v>6815081</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22134,10 +22129,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289574</v>
+        <v>122289689</v>
       </c>
       <c r="B219" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -22150,34 +22145,29 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>473230</v>
+        <v>472954</v>
       </c>
       <c r="R219" t="n">
-        <v>6815538</v>
+        <v>6815041</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22210,11 +22200,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -22241,10 +22226,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289565</v>
+        <v>122289634</v>
       </c>
       <c r="B220" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -22257,34 +22242,29 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>472697</v>
+        <v>472785</v>
       </c>
       <c r="R220" t="n">
-        <v>6815151</v>
+        <v>6815675</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22317,11 +22297,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -22348,10 +22323,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289585</v>
+        <v>122289701</v>
       </c>
       <c r="B221" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -22364,34 +22339,29 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>473030</v>
+        <v>473043</v>
       </c>
       <c r="R221" t="n">
-        <v>6815053</v>
+        <v>6815159</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22424,11 +22394,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -22455,10 +22420,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289773</v>
+        <v>122289727</v>
       </c>
       <c r="B222" t="n">
-        <v>78036</v>
+        <v>78652</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -22471,16 +22436,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22490,10 +22455,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>473042</v>
+        <v>472922</v>
       </c>
       <c r="R222" t="n">
-        <v>6815081</v>
+        <v>6815393</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22552,7 +22517,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289689</v>
+        <v>122289709</v>
       </c>
       <c r="B223" t="n">
         <v>78652</v>
@@ -22587,10 +22552,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>472954</v>
+        <v>472986</v>
       </c>
       <c r="R223" t="n">
-        <v>6815041</v>
+        <v>6815203</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22649,7 +22614,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122289634</v>
+        <v>122289711</v>
       </c>
       <c r="B224" t="n">
         <v>78652</v>
@@ -22684,10 +22649,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>472785</v>
+        <v>472976</v>
       </c>
       <c r="R224" t="n">
-        <v>6815675</v>
+        <v>6815272</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22746,10 +22711,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122289701</v>
+        <v>122289488</v>
       </c>
       <c r="B225" t="n">
-        <v>78652</v>
+        <v>79270</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -22762,16 +22727,16 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22781,10 +22746,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>473043</v>
+        <v>473234</v>
       </c>
       <c r="R225" t="n">
-        <v>6815159</v>
+        <v>6815734</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22843,7 +22808,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122289727</v>
+        <v>122289696</v>
       </c>
       <c r="B226" t="n">
         <v>78652</v>
@@ -22878,10 +22843,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>472922</v>
+        <v>473033</v>
       </c>
       <c r="R226" t="n">
-        <v>6815393</v>
+        <v>6815029</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -22940,10 +22905,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122289709</v>
+        <v>122289592</v>
       </c>
       <c r="B227" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -22956,29 +22921,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>472986</v>
+        <v>473038</v>
       </c>
       <c r="R227" t="n">
-        <v>6815203</v>
+        <v>6815393</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23037,10 +23007,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122289711</v>
+        <v>122289574</v>
       </c>
       <c r="B228" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23053,29 +23023,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>472976</v>
+        <v>473230</v>
       </c>
       <c r="R228" t="n">
-        <v>6815272</v>
+        <v>6815538</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23108,6 +23083,11 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -23134,10 +23114,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122289488</v>
+        <v>122289565</v>
       </c>
       <c r="B229" t="n">
-        <v>79270</v>
+        <v>57379</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -23150,29 +23130,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>473234</v>
+        <v>472697</v>
       </c>
       <c r="R229" t="n">
-        <v>6815734</v>
+        <v>6815151</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23205,6 +23190,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -23231,10 +23221,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122289696</v>
+        <v>122289585</v>
       </c>
       <c r="B230" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -23247,29 +23237,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>473033</v>
+        <v>473030</v>
       </c>
       <c r="R230" t="n">
-        <v>6815029</v>
+        <v>6815053</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23302,6 +23297,11 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -23328,10 +23328,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>122289511</v>
+        <v>122289690</v>
       </c>
       <c r="B231" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -23344,16 +23344,16 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23363,10 +23363,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>472998</v>
+        <v>472957</v>
       </c>
       <c r="R231" t="n">
-        <v>6815243</v>
+        <v>6815023</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23425,10 +23425,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>122289514</v>
+        <v>122289649</v>
       </c>
       <c r="B232" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -23441,16 +23441,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23460,10 +23460,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>472965</v>
+        <v>472853</v>
       </c>
       <c r="R232" t="n">
-        <v>6815434</v>
+        <v>6815291</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23522,10 +23522,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>122289603</v>
+        <v>122289753</v>
       </c>
       <c r="B233" t="n">
-        <v>78389</v>
+        <v>78652</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -23538,16 +23538,16 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23557,10 +23557,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>472794</v>
+        <v>473242</v>
       </c>
       <c r="R233" t="n">
-        <v>6815363</v>
+        <v>6815602</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23619,7 +23619,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>122289690</v>
+        <v>122289647</v>
       </c>
       <c r="B234" t="n">
         <v>78652</v>
@@ -23654,10 +23654,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>472957</v>
+        <v>472878</v>
       </c>
       <c r="R234" t="n">
-        <v>6815023</v>
+        <v>6815322</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23716,7 +23716,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>122289649</v>
+        <v>122289733</v>
       </c>
       <c r="B235" t="n">
         <v>78652</v>
@@ -23751,10 +23751,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>472853</v>
+        <v>472993</v>
       </c>
       <c r="R235" t="n">
-        <v>6815291</v>
+        <v>6815490</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23813,10 +23813,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>122289753</v>
+        <v>122289547</v>
       </c>
       <c r="B236" t="n">
-        <v>78652</v>
+        <v>79734</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -23829,16 +23829,16 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23848,10 +23848,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>473242</v>
+        <v>472833</v>
       </c>
       <c r="R236" t="n">
-        <v>6815602</v>
+        <v>6815619</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -23910,10 +23910,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>122289647</v>
+        <v>122289581</v>
       </c>
       <c r="B237" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -23926,29 +23926,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>472878</v>
+        <v>472821</v>
       </c>
       <c r="R237" t="n">
-        <v>6815322</v>
+        <v>6815364</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -23981,6 +23986,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -24007,10 +24017,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122289733</v>
+        <v>122289570</v>
       </c>
       <c r="B238" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -24023,29 +24033,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>472993</v>
+        <v>473034</v>
       </c>
       <c r="R238" t="n">
-        <v>6815490</v>
+        <v>6815167</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24078,6 +24093,11 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -24104,10 +24124,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122289547</v>
+        <v>122289511</v>
       </c>
       <c r="B239" t="n">
-        <v>79734</v>
+        <v>78686</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -24120,16 +24140,16 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24139,10 +24159,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>472833</v>
+        <v>472998</v>
       </c>
       <c r="R239" t="n">
-        <v>6815619</v>
+        <v>6815243</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24201,10 +24221,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122289581</v>
+        <v>122289514</v>
       </c>
       <c r="B240" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -24217,34 +24237,29 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>472821</v>
+        <v>472965</v>
       </c>
       <c r="R240" t="n">
-        <v>6815364</v>
+        <v>6815434</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24277,11 +24292,6 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -24308,10 +24318,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>122289570</v>
+        <v>122289603</v>
       </c>
       <c r="B241" t="n">
-        <v>57379</v>
+        <v>78389</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -24324,34 +24334,29 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>473034</v>
+        <v>472794</v>
       </c>
       <c r="R241" t="n">
-        <v>6815167</v>
+        <v>6815363</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24384,11 +24389,6 @@
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -24609,10 +24609,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122289546</v>
+        <v>122289615</v>
       </c>
       <c r="B244" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -24640,7 +24640,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -24649,10 +24649,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>472731</v>
+        <v>472712</v>
       </c>
       <c r="R244" t="n">
-        <v>6815088</v>
+        <v>6815141</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24685,6 +24685,11 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -24711,7 +24716,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122289615</v>
+        <v>122289535</v>
       </c>
       <c r="B245" t="n">
         <v>57379</v>
@@ -24742,7 +24747,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -24751,10 +24756,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>472712</v>
+        <v>472732</v>
       </c>
       <c r="R245" t="n">
-        <v>6815141</v>
+        <v>6815380</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -24787,11 +24792,6 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -24818,10 +24818,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122289535</v>
+        <v>122289546</v>
       </c>
       <c r="B246" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -24834,11 +24834,11 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -24849,7 +24849,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -24858,10 +24858,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>472732</v>
+        <v>472731</v>
       </c>
       <c r="R246" t="n">
-        <v>6815380</v>
+        <v>6815088</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24920,10 +24920,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122289650</v>
+        <v>122289540</v>
       </c>
       <c r="B247" t="n">
-        <v>78652</v>
+        <v>57532</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -24936,16 +24936,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -24955,10 +24955,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>472845</v>
+        <v>473035</v>
       </c>
       <c r="R247" t="n">
-        <v>6815328</v>
+        <v>6815416</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25017,7 +25017,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122289754</v>
+        <v>122289650</v>
       </c>
       <c r="B248" t="n">
         <v>78652</v>
@@ -25052,10 +25052,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>473240</v>
+        <v>472845</v>
       </c>
       <c r="R248" t="n">
-        <v>6815620</v>
+        <v>6815328</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25114,7 +25114,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122289633</v>
+        <v>122289754</v>
       </c>
       <c r="B249" t="n">
         <v>78652</v>
@@ -25149,10 +25149,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>472766</v>
+        <v>473240</v>
       </c>
       <c r="R249" t="n">
-        <v>6815686</v>
+        <v>6815620</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25211,7 +25211,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122289672</v>
+        <v>122289633</v>
       </c>
       <c r="B250" t="n">
         <v>78652</v>
@@ -25246,10 +25246,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>472720</v>
+        <v>472766</v>
       </c>
       <c r="R250" t="n">
-        <v>6815067</v>
+        <v>6815686</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25308,10 +25308,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122289612</v>
+        <v>122289672</v>
       </c>
       <c r="B251" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -25324,16 +25324,16 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25343,10 +25343,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>472742</v>
+        <v>472720</v>
       </c>
       <c r="R251" t="n">
-        <v>6815075</v>
+        <v>6815067</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25405,10 +25405,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122289628</v>
+        <v>122289612</v>
       </c>
       <c r="B252" t="n">
-        <v>78652</v>
+        <v>78388</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -25421,16 +25421,16 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25440,10 +25440,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>472851</v>
+        <v>472742</v>
       </c>
       <c r="R252" t="n">
-        <v>6815729</v>
+        <v>6815075</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25502,7 +25502,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289716</v>
+        <v>122289628</v>
       </c>
       <c r="B253" t="n">
         <v>78652</v>
@@ -25537,10 +25537,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>472966</v>
+        <v>472851</v>
       </c>
       <c r="R253" t="n">
-        <v>6815380</v>
+        <v>6815729</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25599,7 +25599,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289728</v>
+        <v>122289716</v>
       </c>
       <c r="B254" t="n">
         <v>78652</v>
@@ -25634,10 +25634,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>472936</v>
+        <v>472966</v>
       </c>
       <c r="R254" t="n">
-        <v>6815401</v>
+        <v>6815380</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25696,10 +25696,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289483</v>
+        <v>122289728</v>
       </c>
       <c r="B255" t="n">
-        <v>79270</v>
+        <v>78652</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -25712,16 +25712,16 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25731,10 +25731,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>472999</v>
+        <v>472936</v>
       </c>
       <c r="R255" t="n">
-        <v>6815197</v>
+        <v>6815401</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -25793,10 +25793,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289765</v>
+        <v>122289483</v>
       </c>
       <c r="B256" t="n">
-        <v>90831</v>
+        <v>79270</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -25809,16 +25809,16 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -25828,10 +25828,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>472815</v>
+        <v>472999</v>
       </c>
       <c r="R256" t="n">
-        <v>6815646</v>
+        <v>6815197</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -25890,10 +25890,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289664</v>
+        <v>122289765</v>
       </c>
       <c r="B257" t="n">
-        <v>78652</v>
+        <v>90831</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -25906,16 +25906,16 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -25925,10 +25925,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>472722</v>
+        <v>472815</v>
       </c>
       <c r="R257" t="n">
-        <v>6815115</v>
+        <v>6815646</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -25987,7 +25987,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289752</v>
+        <v>122289664</v>
       </c>
       <c r="B258" t="n">
         <v>78652</v>
@@ -26022,10 +26022,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>473224</v>
+        <v>472722</v>
       </c>
       <c r="R258" t="n">
-        <v>6815578</v>
+        <v>6815115</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26084,7 +26084,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289737</v>
+        <v>122289752</v>
       </c>
       <c r="B259" t="n">
         <v>78652</v>
@@ -26119,10 +26119,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>473035</v>
+        <v>473224</v>
       </c>
       <c r="R259" t="n">
-        <v>6815416</v>
+        <v>6815578</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26181,7 +26181,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122289668</v>
+        <v>122289737</v>
       </c>
       <c r="B260" t="n">
         <v>78652</v>
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>472718</v>
+        <v>473035</v>
       </c>
       <c r="R260" t="n">
-        <v>6815026</v>
+        <v>6815416</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26278,10 +26278,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122289618</v>
+        <v>122289668</v>
       </c>
       <c r="B261" t="n">
-        <v>90831</v>
+        <v>78652</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -26294,16 +26294,16 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26313,10 +26313,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>473257</v>
+        <v>472718</v>
       </c>
       <c r="R261" t="n">
-        <v>6815716</v>
+        <v>6815026</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26375,10 +26375,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122289540</v>
+        <v>122289618</v>
       </c>
       <c r="B262" t="n">
-        <v>57532</v>
+        <v>90831</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -26391,16 +26391,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26410,10 +26410,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>473035</v>
+        <v>473257</v>
       </c>
       <c r="R262" t="n">
-        <v>6815416</v>
+        <v>6815716</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122289571</v>
+        <v>122289669</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,34 +1044,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472895</v>
+        <v>472718</v>
       </c>
       <c r="R5" t="n">
-        <v>6815359</v>
+        <v>6815041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,11 +1099,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122289669</v>
+        <v>122289658</v>
       </c>
       <c r="B6" t="n">
         <v>78652</v>
@@ -1170,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472718</v>
+        <v>472721</v>
       </c>
       <c r="R6" t="n">
-        <v>6815041</v>
+        <v>6815373</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122289658</v>
+        <v>122289645</v>
       </c>
       <c r="B7" t="n">
         <v>78652</v>
@@ -1267,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472721</v>
+        <v>472889</v>
       </c>
       <c r="R7" t="n">
-        <v>6815373</v>
+        <v>6815359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122289645</v>
+        <v>122289712</v>
       </c>
       <c r="B8" t="n">
         <v>78652</v>
@@ -1364,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472889</v>
+        <v>472971</v>
       </c>
       <c r="R8" t="n">
-        <v>6815359</v>
+        <v>6815298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122289712</v>
+        <v>122289667</v>
       </c>
       <c r="B9" t="n">
         <v>78652</v>
@@ -1461,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472971</v>
+        <v>472741</v>
       </c>
       <c r="R9" t="n">
-        <v>6815298</v>
+        <v>6815075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122289667</v>
+        <v>122289659</v>
       </c>
       <c r="B10" t="n">
         <v>78652</v>
@@ -1558,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472741</v>
+        <v>472724</v>
       </c>
       <c r="R10" t="n">
-        <v>6815075</v>
+        <v>6815345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1610,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122289659</v>
+        <v>122289673</v>
       </c>
       <c r="B11" t="n">
         <v>78652</v>
@@ -1655,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472724</v>
+        <v>472729</v>
       </c>
       <c r="R11" t="n">
-        <v>6815345</v>
+        <v>6815062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1707,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122289673</v>
+        <v>122289704</v>
       </c>
       <c r="B12" t="n">
         <v>78652</v>
@@ -1752,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472729</v>
+        <v>473036</v>
       </c>
       <c r="R12" t="n">
-        <v>6815062</v>
+        <v>6815177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1804,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122289704</v>
+        <v>122289714</v>
       </c>
       <c r="B13" t="n">
         <v>78652</v>
@@ -1849,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473036</v>
+        <v>472966</v>
       </c>
       <c r="R13" t="n">
-        <v>6815177</v>
+        <v>6815345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1901,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122289714</v>
+        <v>122289768</v>
       </c>
       <c r="B14" t="n">
         <v>78652</v>
@@ -1946,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472966</v>
+        <v>472877</v>
       </c>
       <c r="R14" t="n">
-        <v>6815345</v>
+        <v>6815103</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +1998,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122289768</v>
+        <v>122289736</v>
       </c>
       <c r="B15" t="n">
         <v>78652</v>
@@ -2043,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472877</v>
+        <v>473027</v>
       </c>
       <c r="R15" t="n">
-        <v>6815103</v>
+        <v>6815426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122289736</v>
+        <v>122289507</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2121,16 +2111,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473027</v>
+        <v>473043</v>
       </c>
       <c r="R16" t="n">
-        <v>6815426</v>
+        <v>6815153</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2192,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122289507</v>
+        <v>122289500</v>
       </c>
       <c r="B17" t="n">
         <v>78686</v>
@@ -2237,10 +2227,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473043</v>
+        <v>472769</v>
       </c>
       <c r="R17" t="n">
-        <v>6815153</v>
+        <v>6815363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122289500</v>
+        <v>122289571</v>
       </c>
       <c r="B18" t="n">
-        <v>78686</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2315,29 +2305,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472769</v>
+        <v>472895</v>
       </c>
       <c r="R18" t="n">
-        <v>6815363</v>
+        <v>6815359</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,6 +2365,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3473,10 +3473,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289767</v>
+        <v>122289699</v>
       </c>
       <c r="B30" t="n">
-        <v>90831</v>
+        <v>78652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472819</v>
+        <v>473050</v>
       </c>
       <c r="R30" t="n">
-        <v>6815624</v>
+        <v>6815098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289717</v>
+        <v>122289700</v>
       </c>
       <c r="B31" t="n">
         <v>78652</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472949</v>
+        <v>473049</v>
       </c>
       <c r="R31" t="n">
-        <v>6815365</v>
+        <v>6815133</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122289698</v>
+        <v>122289665</v>
       </c>
       <c r="B32" t="n">
         <v>78652</v>
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473037</v>
+        <v>472722</v>
       </c>
       <c r="R32" t="n">
-        <v>6815086</v>
+        <v>6815109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3764,10 +3764,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289762</v>
+        <v>122289767</v>
       </c>
       <c r="B33" t="n">
-        <v>78652</v>
+        <v>90831</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473222</v>
+        <v>472819</v>
       </c>
       <c r="R33" t="n">
-        <v>6815741</v>
+        <v>6815624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122289702</v>
+        <v>122289717</v>
       </c>
       <c r="B34" t="n">
         <v>78652</v>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473044</v>
+        <v>472949</v>
       </c>
       <c r="R34" t="n">
-        <v>6815169</v>
+        <v>6815365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122289641</v>
+        <v>122289698</v>
       </c>
       <c r="B35" t="n">
         <v>78652</v>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472882</v>
+        <v>473037</v>
       </c>
       <c r="R35" t="n">
-        <v>6815476</v>
+        <v>6815086</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122289655</v>
+        <v>122289762</v>
       </c>
       <c r="B36" t="n">
         <v>78652</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472766</v>
+        <v>473222</v>
       </c>
       <c r="R36" t="n">
-        <v>6815363</v>
+        <v>6815741</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122289699</v>
+        <v>122289702</v>
       </c>
       <c r="B37" t="n">
         <v>78652</v>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473050</v>
+        <v>473044</v>
       </c>
       <c r="R37" t="n">
-        <v>6815098</v>
+        <v>6815169</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122289700</v>
+        <v>122289641</v>
       </c>
       <c r="B38" t="n">
         <v>78652</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473049</v>
+        <v>472882</v>
       </c>
       <c r="R38" t="n">
-        <v>6815133</v>
+        <v>6815476</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122289665</v>
+        <v>122289655</v>
       </c>
       <c r="B39" t="n">
         <v>78652</v>
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472722</v>
+        <v>472766</v>
       </c>
       <c r="R39" t="n">
-        <v>6815109</v>
+        <v>6815363</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,10 +4637,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122289553</v>
+        <v>122289713</v>
       </c>
       <c r="B42" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4653,34 +4653,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472880</v>
+        <v>472952</v>
       </c>
       <c r="R42" t="n">
-        <v>6815136</v>
+        <v>6815339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4713,11 +4708,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4744,10 +4734,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122289537</v>
+        <v>122289676</v>
       </c>
       <c r="B43" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4760,34 +4750,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472724</v>
+        <v>472759</v>
       </c>
       <c r="R43" t="n">
-        <v>6815093</v>
+        <v>6815052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4846,10 +4831,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122289520</v>
+        <v>122289630</v>
       </c>
       <c r="B44" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4862,16 +4847,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4881,10 +4866,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473245</v>
+        <v>473038</v>
       </c>
       <c r="R44" t="n">
-        <v>6815602</v>
+        <v>6815393</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4943,7 +4928,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122289713</v>
+        <v>122289663</v>
       </c>
       <c r="B45" t="n">
         <v>78652</v>
@@ -4978,10 +4963,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472952</v>
+        <v>472719</v>
       </c>
       <c r="R45" t="n">
-        <v>6815339</v>
+        <v>6815128</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5040,7 +5025,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122289676</v>
+        <v>122289657</v>
       </c>
       <c r="B46" t="n">
         <v>78652</v>
@@ -5075,10 +5060,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472759</v>
+        <v>472730</v>
       </c>
       <c r="R46" t="n">
-        <v>6815052</v>
+        <v>6815383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5137,7 +5122,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122289630</v>
+        <v>122289741</v>
       </c>
       <c r="B47" t="n">
         <v>78652</v>
@@ -5172,10 +5157,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473038</v>
+        <v>473161</v>
       </c>
       <c r="R47" t="n">
-        <v>6815393</v>
+        <v>6815418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5234,7 +5219,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122289663</v>
+        <v>122289622</v>
       </c>
       <c r="B48" t="n">
         <v>78652</v>
@@ -5269,10 +5254,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472719</v>
+        <v>472955</v>
       </c>
       <c r="R48" t="n">
-        <v>6815128</v>
+        <v>6815658</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5331,10 +5316,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122289657</v>
+        <v>122289520</v>
       </c>
       <c r="B49" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5347,16 +5332,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5351,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472730</v>
+        <v>473245</v>
       </c>
       <c r="R49" t="n">
-        <v>6815383</v>
+        <v>6815602</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5428,10 +5413,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122289741</v>
+        <v>122289553</v>
       </c>
       <c r="B50" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5444,29 +5429,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473161</v>
+        <v>472880</v>
       </c>
       <c r="R50" t="n">
-        <v>6815418</v>
+        <v>6815136</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,6 +5489,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5525,10 +5520,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122289622</v>
+        <v>122289537</v>
       </c>
       <c r="B51" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5541,29 +5536,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>472955</v>
+        <v>472724</v>
       </c>
       <c r="R51" t="n">
-        <v>6815658</v>
+        <v>6815093</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7485,10 +7485,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289609</v>
+        <v>122289549</v>
       </c>
       <c r="B71" t="n">
-        <v>80609</v>
+        <v>79734</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7501,16 +7501,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472975</v>
+        <v>472766</v>
       </c>
       <c r="R71" t="n">
-        <v>6815664</v>
+        <v>6815366</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7582,10 +7582,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122289549</v>
+        <v>122289609</v>
       </c>
       <c r="B72" t="n">
-        <v>79734</v>
+        <v>80609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7598,16 +7598,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472766</v>
+        <v>472975</v>
       </c>
       <c r="R72" t="n">
-        <v>6815366</v>
+        <v>6815664</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122289578</v>
+        <v>122289648</v>
       </c>
       <c r="B73" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7695,34 +7695,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472860</v>
+        <v>472874</v>
       </c>
       <c r="R73" t="n">
-        <v>6815679</v>
+        <v>6815282</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7755,11 +7750,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7786,7 +7776,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289648</v>
+        <v>122289637</v>
       </c>
       <c r="B74" t="n">
         <v>78652</v>
@@ -7821,10 +7811,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472874</v>
+        <v>472863</v>
       </c>
       <c r="R74" t="n">
-        <v>6815282</v>
+        <v>6815525</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,7 +7873,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122289637</v>
+        <v>122289742</v>
       </c>
       <c r="B75" t="n">
         <v>78652</v>
@@ -7918,10 +7908,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472863</v>
+        <v>473186</v>
       </c>
       <c r="R75" t="n">
-        <v>6815525</v>
+        <v>6815462</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7980,7 +7970,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122289742</v>
+        <v>122289674</v>
       </c>
       <c r="B76" t="n">
         <v>78652</v>
@@ -8015,10 +8005,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>473186</v>
+        <v>472736</v>
       </c>
       <c r="R76" t="n">
-        <v>6815462</v>
+        <v>6815067</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8077,7 +8067,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122289674</v>
+        <v>122289632</v>
       </c>
       <c r="B77" t="n">
         <v>78652</v>
@@ -8112,10 +8102,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>472736</v>
+        <v>472754</v>
       </c>
       <c r="R77" t="n">
-        <v>6815067</v>
+        <v>6815718</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8174,10 +8164,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122289632</v>
+        <v>122289578</v>
       </c>
       <c r="B78" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8190,29 +8180,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472754</v>
+        <v>472860</v>
       </c>
       <c r="R78" t="n">
-        <v>6815718</v>
+        <v>6815679</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8245,6 +8240,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8368,10 +8368,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122289770</v>
+        <v>122289550</v>
       </c>
       <c r="B80" t="n">
-        <v>78297</v>
+        <v>79734</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8384,16 +8384,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>473114</v>
+        <v>473037</v>
       </c>
       <c r="R80" t="n">
-        <v>6815360</v>
+        <v>6815182</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8465,10 +8465,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122289685</v>
+        <v>122289569</v>
       </c>
       <c r="B81" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8481,29 +8481,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>472881</v>
+        <v>473043</v>
       </c>
       <c r="R81" t="n">
-        <v>6815128</v>
+        <v>6815180</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8536,6 +8541,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8562,10 +8572,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122289482</v>
+        <v>122289591</v>
       </c>
       <c r="B82" t="n">
-        <v>79270</v>
+        <v>57379</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8578,29 +8588,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>472988</v>
+        <v>473243</v>
       </c>
       <c r="R82" t="n">
-        <v>6815002</v>
+        <v>6815620</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8633,6 +8648,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8659,10 +8679,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122289666</v>
+        <v>122289770</v>
       </c>
       <c r="B83" t="n">
-        <v>78652</v>
+        <v>78297</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8675,16 +8695,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8694,10 +8714,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>472737</v>
+        <v>473114</v>
       </c>
       <c r="R83" t="n">
-        <v>6815084</v>
+        <v>6815360</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8756,7 +8776,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122289748</v>
+        <v>122289685</v>
       </c>
       <c r="B84" t="n">
         <v>78652</v>
@@ -8791,10 +8811,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>473217</v>
+        <v>472881</v>
       </c>
       <c r="R84" t="n">
-        <v>6815515</v>
+        <v>6815128</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8853,10 +8873,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122289687</v>
+        <v>122289482</v>
       </c>
       <c r="B85" t="n">
-        <v>78652</v>
+        <v>79270</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -8869,16 +8889,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8888,10 +8908,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>472899</v>
+        <v>472988</v>
       </c>
       <c r="R85" t="n">
-        <v>6815079</v>
+        <v>6815002</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8950,7 +8970,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122289723</v>
+        <v>122289666</v>
       </c>
       <c r="B86" t="n">
         <v>78652</v>
@@ -8985,10 +9005,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>472901</v>
+        <v>472737</v>
       </c>
       <c r="R86" t="n">
-        <v>6815361</v>
+        <v>6815084</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9047,7 +9067,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122289639</v>
+        <v>122289748</v>
       </c>
       <c r="B87" t="n">
         <v>78652</v>
@@ -9082,10 +9102,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>472869</v>
+        <v>473217</v>
       </c>
       <c r="R87" t="n">
-        <v>6815500</v>
+        <v>6815515</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9144,7 +9164,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122289697</v>
+        <v>122289687</v>
       </c>
       <c r="B88" t="n">
         <v>78652</v>
@@ -9179,10 +9199,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>473033</v>
+        <v>472899</v>
       </c>
       <c r="R88" t="n">
-        <v>6815058</v>
+        <v>6815079</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9241,7 +9261,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122289719</v>
+        <v>122289723</v>
       </c>
       <c r="B89" t="n">
         <v>78652</v>
@@ -9276,10 +9296,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>472906</v>
+        <v>472901</v>
       </c>
       <c r="R89" t="n">
-        <v>6815327</v>
+        <v>6815361</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9338,10 +9358,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122289610</v>
+        <v>122289639</v>
       </c>
       <c r="B90" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9354,16 +9374,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9373,10 +9393,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>473044</v>
+        <v>472869</v>
       </c>
       <c r="R90" t="n">
-        <v>6815721</v>
+        <v>6815500</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9435,10 +9455,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122289481</v>
+        <v>122289697</v>
       </c>
       <c r="B91" t="n">
-        <v>79270</v>
+        <v>78652</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9451,16 +9471,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9470,10 +9490,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>472871</v>
+        <v>473033</v>
       </c>
       <c r="R91" t="n">
-        <v>6815157</v>
+        <v>6815058</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9532,10 +9552,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122289516</v>
+        <v>122289719</v>
       </c>
       <c r="B92" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9548,16 +9568,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9567,10 +9587,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>473107</v>
+        <v>472906</v>
       </c>
       <c r="R92" t="n">
-        <v>6815366</v>
+        <v>6815327</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9629,10 +9649,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122289510</v>
+        <v>122289610</v>
       </c>
       <c r="B93" t="n">
-        <v>78686</v>
+        <v>78388</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9645,16 +9665,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9664,10 +9684,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>472986</v>
+        <v>473044</v>
       </c>
       <c r="R93" t="n">
-        <v>6815203</v>
+        <v>6815721</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9726,10 +9746,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122289515</v>
+        <v>122289481</v>
       </c>
       <c r="B94" t="n">
-        <v>78686</v>
+        <v>79270</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -9742,16 +9762,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9761,10 +9781,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>473035</v>
+        <v>472871</v>
       </c>
       <c r="R94" t="n">
-        <v>6815416</v>
+        <v>6815157</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9823,10 +9843,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122289550</v>
+        <v>122289516</v>
       </c>
       <c r="B95" t="n">
-        <v>79734</v>
+        <v>78686</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -9839,16 +9859,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9858,10 +9878,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>473037</v>
+        <v>473107</v>
       </c>
       <c r="R95" t="n">
-        <v>6815182</v>
+        <v>6815366</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9920,10 +9940,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122289569</v>
+        <v>122289510</v>
       </c>
       <c r="B96" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -9936,34 +9956,29 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>473043</v>
+        <v>472986</v>
       </c>
       <c r="R96" t="n">
-        <v>6815180</v>
+        <v>6815203</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9996,11 +10011,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10027,10 +10037,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122289591</v>
+        <v>122289515</v>
       </c>
       <c r="B97" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10043,34 +10053,29 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>473243</v>
+        <v>473035</v>
       </c>
       <c r="R97" t="n">
-        <v>6815620</v>
+        <v>6815416</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10103,11 +10108,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -18490,10 +18490,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122289587</v>
+        <v>122289528</v>
       </c>
       <c r="B182" t="n">
-        <v>57379</v>
+        <v>79241</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -18506,34 +18506,29 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>473000</v>
+        <v>473019</v>
       </c>
       <c r="R182" t="n">
-        <v>6815184</v>
+        <v>6815730</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18566,11 +18561,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18597,10 +18587,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289619</v>
+        <v>122289517</v>
       </c>
       <c r="B183" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -18613,16 +18603,16 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18632,10 +18622,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>473228</v>
+        <v>473149</v>
       </c>
       <c r="R183" t="n">
-        <v>6815569</v>
+        <v>6815391</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18694,10 +18684,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289738</v>
+        <v>122289506</v>
       </c>
       <c r="B184" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -18710,16 +18700,16 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18729,10 +18719,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>473045</v>
+        <v>473050</v>
       </c>
       <c r="R184" t="n">
-        <v>6815390</v>
+        <v>6815098</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18791,7 +18781,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122289670</v>
+        <v>122289619</v>
       </c>
       <c r="B185" t="n">
         <v>78652</v>
@@ -18826,10 +18816,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>472698</v>
+        <v>473228</v>
       </c>
       <c r="R185" t="n">
-        <v>6815034</v>
+        <v>6815569</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18888,7 +18878,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289680</v>
+        <v>122289738</v>
       </c>
       <c r="B186" t="n">
         <v>78652</v>
@@ -18923,10 +18913,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>472808</v>
+        <v>473045</v>
       </c>
       <c r="R186" t="n">
-        <v>6815067</v>
+        <v>6815390</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18985,10 +18975,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289485</v>
+        <v>122289670</v>
       </c>
       <c r="B187" t="n">
-        <v>79270</v>
+        <v>78652</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19001,16 +18991,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19020,10 +19010,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>473014</v>
+        <v>472698</v>
       </c>
       <c r="R187" t="n">
-        <v>6815496</v>
+        <v>6815034</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19082,10 +19072,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289517</v>
+        <v>122289680</v>
       </c>
       <c r="B188" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19098,16 +19088,16 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19117,10 +19107,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>473149</v>
+        <v>472808</v>
       </c>
       <c r="R188" t="n">
-        <v>6815391</v>
+        <v>6815067</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19179,10 +19169,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122289506</v>
+        <v>122289485</v>
       </c>
       <c r="B189" t="n">
-        <v>78686</v>
+        <v>79270</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19195,16 +19185,16 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19214,10 +19204,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>473050</v>
+        <v>473014</v>
       </c>
       <c r="R189" t="n">
-        <v>6815098</v>
+        <v>6815496</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19276,10 +19266,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289528</v>
+        <v>122289587</v>
       </c>
       <c r="B190" t="n">
-        <v>79241</v>
+        <v>57379</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19292,29 +19282,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>473019</v>
+        <v>473000</v>
       </c>
       <c r="R190" t="n">
-        <v>6815730</v>
+        <v>6815184</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19347,6 +19342,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19373,10 +19373,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122289497</v>
+        <v>122289755</v>
       </c>
       <c r="B191" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -19389,16 +19389,16 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19408,10 +19408,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>472959</v>
+        <v>473241</v>
       </c>
       <c r="R191" t="n">
-        <v>6815656</v>
+        <v>6815645</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19470,7 +19470,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122289755</v>
+        <v>122289721</v>
       </c>
       <c r="B192" t="n">
         <v>78652</v>
@@ -19505,10 +19505,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>473241</v>
+        <v>472897</v>
       </c>
       <c r="R192" t="n">
-        <v>6815645</v>
+        <v>6815355</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19567,7 +19567,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122289721</v>
+        <v>122289662</v>
       </c>
       <c r="B193" t="n">
         <v>78652</v>
@@ -19602,10 +19602,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>472897</v>
+        <v>472697</v>
       </c>
       <c r="R193" t="n">
-        <v>6815355</v>
+        <v>6815151</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19664,10 +19664,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122289662</v>
+        <v>122289477</v>
       </c>
       <c r="B194" t="n">
-        <v>78652</v>
+        <v>79270</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -19680,16 +19680,16 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19699,10 +19699,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>472697</v>
+        <v>472716</v>
       </c>
       <c r="R194" t="n">
-        <v>6815151</v>
+        <v>6815299</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19761,10 +19761,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122289477</v>
+        <v>122289492</v>
       </c>
       <c r="B195" t="n">
-        <v>79270</v>
+        <v>74753</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -19777,16 +19777,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19796,10 +19796,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>472716</v>
+        <v>472897</v>
       </c>
       <c r="R195" t="n">
-        <v>6815299</v>
+        <v>6815078</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19858,7 +19858,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122289492</v>
+        <v>122289493</v>
       </c>
       <c r="B196" t="n">
         <v>74753</v>
@@ -19893,10 +19893,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>472897</v>
+        <v>473003</v>
       </c>
       <c r="R196" t="n">
-        <v>6815078</v>
+        <v>6814987</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -19955,10 +19955,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122289493</v>
+        <v>122289652</v>
       </c>
       <c r="B197" t="n">
-        <v>74753</v>
+        <v>78652</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -19971,16 +19971,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>473003</v>
+        <v>472813</v>
       </c>
       <c r="R197" t="n">
-        <v>6814987</v>
+        <v>6815369</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20052,7 +20052,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122289652</v>
+        <v>122289692</v>
       </c>
       <c r="B198" t="n">
         <v>78652</v>
@@ -20087,10 +20087,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>472813</v>
+        <v>472970</v>
       </c>
       <c r="R198" t="n">
-        <v>6815369</v>
+        <v>6814989</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20149,7 +20149,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122289692</v>
+        <v>122289745</v>
       </c>
       <c r="B199" t="n">
         <v>78652</v>
@@ -20184,10 +20184,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>472970</v>
+        <v>473190</v>
       </c>
       <c r="R199" t="n">
-        <v>6814989</v>
+        <v>6815498</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20246,7 +20246,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122289745</v>
+        <v>122289708</v>
       </c>
       <c r="B200" t="n">
         <v>78652</v>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>473190</v>
+        <v>473000</v>
       </c>
       <c r="R200" t="n">
-        <v>6815498</v>
+        <v>6815193</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20343,10 +20343,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122289708</v>
+        <v>122289495</v>
       </c>
       <c r="B201" t="n">
-        <v>78652</v>
+        <v>74753</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -20359,16 +20359,16 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>473000</v>
+        <v>473212</v>
       </c>
       <c r="R201" t="n">
-        <v>6815193</v>
+        <v>6815464</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20440,10 +20440,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122289495</v>
+        <v>122289559</v>
       </c>
       <c r="B202" t="n">
-        <v>74753</v>
+        <v>57379</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -20456,29 +20456,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>473212</v>
+        <v>472934</v>
       </c>
       <c r="R202" t="n">
-        <v>6815464</v>
+        <v>6815651</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20511,6 +20516,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20537,10 +20547,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122289559</v>
+        <v>122289497</v>
       </c>
       <c r="B203" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -20553,34 +20563,29 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>472934</v>
+        <v>472959</v>
       </c>
       <c r="R203" t="n">
-        <v>6815651</v>
+        <v>6815656</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20613,11 +20618,6 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -20644,10 +20644,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122289671</v>
+        <v>122289512</v>
       </c>
       <c r="B204" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -20660,16 +20660,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20679,10 +20679,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>472713</v>
+        <v>472977</v>
       </c>
       <c r="R204" t="n">
-        <v>6815067</v>
+        <v>6815273</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20741,10 +20741,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122289735</v>
+        <v>122289513</v>
       </c>
       <c r="B205" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -20757,16 +20757,16 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20776,10 +20776,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>473015</v>
+        <v>472966</v>
       </c>
       <c r="R205" t="n">
-        <v>6815443</v>
+        <v>6815390</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20838,10 +20838,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122289487</v>
+        <v>122289525</v>
       </c>
       <c r="B206" t="n">
-        <v>79270</v>
+        <v>95758</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -20854,16 +20854,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -20873,10 +20873,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>473192</v>
+        <v>472724</v>
       </c>
       <c r="R206" t="n">
-        <v>6815503</v>
+        <v>6815100</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -20935,10 +20935,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122289621</v>
+        <v>122289594</v>
       </c>
       <c r="B207" t="n">
-        <v>78652</v>
+        <v>74748</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -20951,16 +20951,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -20970,10 +20970,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>473076</v>
+        <v>472834</v>
       </c>
       <c r="R207" t="n">
-        <v>6815660</v>
+        <v>6815612</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21032,10 +21032,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122289757</v>
+        <v>122289526</v>
       </c>
       <c r="B208" t="n">
-        <v>78652</v>
+        <v>79241</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21048,16 +21048,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21067,10 +21067,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>473240</v>
+        <v>473224</v>
       </c>
       <c r="R208" t="n">
-        <v>6815680</v>
+        <v>6815616</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21129,10 +21129,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122289480</v>
+        <v>122289671</v>
       </c>
       <c r="B209" t="n">
-        <v>79270</v>
+        <v>78652</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -21145,16 +21145,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21164,10 +21164,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>472742</v>
+        <v>472713</v>
       </c>
       <c r="R209" t="n">
-        <v>6815075</v>
+        <v>6815067</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21226,10 +21226,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122289512</v>
+        <v>122289735</v>
       </c>
       <c r="B210" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -21242,16 +21242,16 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21261,10 +21261,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>472977</v>
+        <v>473015</v>
       </c>
       <c r="R210" t="n">
-        <v>6815273</v>
+        <v>6815443</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21323,10 +21323,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289513</v>
+        <v>122289487</v>
       </c>
       <c r="B211" t="n">
-        <v>78686</v>
+        <v>79270</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -21339,16 +21339,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21358,10 +21358,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>472966</v>
+        <v>473192</v>
       </c>
       <c r="R211" t="n">
-        <v>6815390</v>
+        <v>6815503</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21420,10 +21420,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289525</v>
+        <v>122289621</v>
       </c>
       <c r="B212" t="n">
-        <v>95758</v>
+        <v>78652</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -21436,16 +21436,16 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21455,10 +21455,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>472724</v>
+        <v>473076</v>
       </c>
       <c r="R212" t="n">
-        <v>6815100</v>
+        <v>6815660</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21517,10 +21517,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289594</v>
+        <v>122289757</v>
       </c>
       <c r="B213" t="n">
-        <v>74748</v>
+        <v>78652</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -21533,16 +21533,16 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21552,10 +21552,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>472834</v>
+        <v>473240</v>
       </c>
       <c r="R213" t="n">
-        <v>6815612</v>
+        <v>6815680</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21614,10 +21614,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289568</v>
+        <v>122289480</v>
       </c>
       <c r="B214" t="n">
-        <v>57379</v>
+        <v>79270</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -21630,34 +21630,29 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>472863</v>
+        <v>472742</v>
       </c>
       <c r="R214" t="n">
-        <v>6815149</v>
+        <v>6815075</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21690,11 +21685,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -21721,7 +21711,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289555</v>
+        <v>122289568</v>
       </c>
       <c r="B215" t="n">
         <v>57379</v>
@@ -21761,10 +21751,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>473055</v>
+        <v>472863</v>
       </c>
       <c r="R215" t="n">
-        <v>6815710</v>
+        <v>6815149</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21801,7 +21791,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Äldre rnghack (tall)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -21828,7 +21818,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289590</v>
+        <v>122289555</v>
       </c>
       <c r="B216" t="n">
         <v>57379</v>
@@ -21859,7 +21849,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -21868,10 +21858,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>472945</v>
+        <v>473055</v>
       </c>
       <c r="R216" t="n">
-        <v>6815381</v>
+        <v>6815710</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -21908,7 +21898,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -21935,10 +21925,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289526</v>
+        <v>122289590</v>
       </c>
       <c r="B217" t="n">
-        <v>79241</v>
+        <v>57379</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -21951,29 +21941,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>473224</v>
+        <v>472945</v>
       </c>
       <c r="R217" t="n">
-        <v>6815616</v>
+        <v>6815381</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22006,6 +22001,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -22032,10 +22032,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122289773</v>
+        <v>122289592</v>
       </c>
       <c r="B218" t="n">
-        <v>78036</v>
+        <v>57379</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22048,29 +22048,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>473042</v>
+        <v>473038</v>
       </c>
       <c r="R218" t="n">
-        <v>6815081</v>
+        <v>6815393</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22129,10 +22134,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289689</v>
+        <v>122289574</v>
       </c>
       <c r="B219" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -22145,29 +22150,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>472954</v>
+        <v>473230</v>
       </c>
       <c r="R219" t="n">
-        <v>6815041</v>
+        <v>6815538</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22200,6 +22210,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -22226,10 +22241,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289634</v>
+        <v>122289565</v>
       </c>
       <c r="B220" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -22242,29 +22257,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>472785</v>
+        <v>472697</v>
       </c>
       <c r="R220" t="n">
-        <v>6815675</v>
+        <v>6815151</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22297,6 +22317,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -22323,10 +22348,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289701</v>
+        <v>122289585</v>
       </c>
       <c r="B221" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -22339,29 +22364,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>473043</v>
+        <v>473030</v>
       </c>
       <c r="R221" t="n">
-        <v>6815159</v>
+        <v>6815053</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22394,6 +22424,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -22420,10 +22455,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289727</v>
+        <v>122289773</v>
       </c>
       <c r="B222" t="n">
-        <v>78652</v>
+        <v>78036</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -22436,16 +22471,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22455,10 +22490,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>472922</v>
+        <v>473042</v>
       </c>
       <c r="R222" t="n">
-        <v>6815393</v>
+        <v>6815081</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22517,7 +22552,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289709</v>
+        <v>122289689</v>
       </c>
       <c r="B223" t="n">
         <v>78652</v>
@@ -22552,10 +22587,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>472986</v>
+        <v>472954</v>
       </c>
       <c r="R223" t="n">
-        <v>6815203</v>
+        <v>6815041</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22614,7 +22649,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122289711</v>
+        <v>122289634</v>
       </c>
       <c r="B224" t="n">
         <v>78652</v>
@@ -22649,10 +22684,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>472976</v>
+        <v>472785</v>
       </c>
       <c r="R224" t="n">
-        <v>6815272</v>
+        <v>6815675</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22711,10 +22746,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122289488</v>
+        <v>122289701</v>
       </c>
       <c r="B225" t="n">
-        <v>79270</v>
+        <v>78652</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -22727,16 +22762,16 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22746,10 +22781,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>473234</v>
+        <v>473043</v>
       </c>
       <c r="R225" t="n">
-        <v>6815734</v>
+        <v>6815159</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22808,7 +22843,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122289696</v>
+        <v>122289727</v>
       </c>
       <c r="B226" t="n">
         <v>78652</v>
@@ -22843,10 +22878,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>473033</v>
+        <v>472922</v>
       </c>
       <c r="R226" t="n">
-        <v>6815029</v>
+        <v>6815393</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -22905,10 +22940,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122289592</v>
+        <v>122289709</v>
       </c>
       <c r="B227" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -22921,34 +22956,29 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>473038</v>
+        <v>472986</v>
       </c>
       <c r="R227" t="n">
-        <v>6815393</v>
+        <v>6815203</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23007,10 +23037,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122289574</v>
+        <v>122289711</v>
       </c>
       <c r="B228" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23023,34 +23053,29 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>473230</v>
+        <v>472976</v>
       </c>
       <c r="R228" t="n">
-        <v>6815538</v>
+        <v>6815272</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23083,11 +23108,6 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -23114,10 +23134,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122289565</v>
+        <v>122289488</v>
       </c>
       <c r="B229" t="n">
-        <v>57379</v>
+        <v>79270</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -23130,34 +23150,29 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>472697</v>
+        <v>473234</v>
       </c>
       <c r="R229" t="n">
-        <v>6815151</v>
+        <v>6815734</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23190,11 +23205,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -23221,10 +23231,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122289585</v>
+        <v>122289696</v>
       </c>
       <c r="B230" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -23237,34 +23247,29 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>473030</v>
+        <v>473033</v>
       </c>
       <c r="R230" t="n">
-        <v>6815053</v>
+        <v>6815029</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23297,11 +23302,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -23813,10 +23813,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>122289547</v>
+        <v>122289511</v>
       </c>
       <c r="B236" t="n">
-        <v>79734</v>
+        <v>78686</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -23829,16 +23829,16 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23848,10 +23848,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>472833</v>
+        <v>472998</v>
       </c>
       <c r="R236" t="n">
-        <v>6815619</v>
+        <v>6815243</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -23910,10 +23910,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>122289581</v>
+        <v>122289514</v>
       </c>
       <c r="B237" t="n">
-        <v>57379</v>
+        <v>78686</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -23926,34 +23926,29 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>472821</v>
+        <v>472965</v>
       </c>
       <c r="R237" t="n">
-        <v>6815364</v>
+        <v>6815434</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -23986,11 +23981,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -24017,7 +24007,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122289570</v>
+        <v>122289581</v>
       </c>
       <c r="B238" t="n">
         <v>57379</v>
@@ -24048,7 +24038,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -24057,10 +24047,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>473034</v>
+        <v>472821</v>
       </c>
       <c r="R238" t="n">
-        <v>6815167</v>
+        <v>6815364</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24097,7 +24087,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -24124,10 +24114,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122289511</v>
+        <v>122289570</v>
       </c>
       <c r="B239" t="n">
-        <v>78686</v>
+        <v>57379</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -24140,29 +24130,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>472998</v>
+        <v>473034</v>
       </c>
       <c r="R239" t="n">
-        <v>6815243</v>
+        <v>6815167</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24195,6 +24190,11 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -24221,10 +24221,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122289514</v>
+        <v>122289547</v>
       </c>
       <c r="B240" t="n">
-        <v>78686</v>
+        <v>79734</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -24237,16 +24237,16 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24256,10 +24256,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>472965</v>
+        <v>472833</v>
       </c>
       <c r="R240" t="n">
-        <v>6815434</v>
+        <v>6815619</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -2695,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122289498</v>
+        <v>122289723</v>
       </c>
       <c r="B21" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472863</v>
+        <v>472901</v>
       </c>
       <c r="R21" t="n">
-        <v>6815525</v>
+        <v>6815361</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122289510</v>
+        <v>122289648</v>
       </c>
       <c r="B22" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472986</v>
+        <v>472874</v>
       </c>
       <c r="R22" t="n">
-        <v>6815203</v>
+        <v>6815282</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122289521</v>
+        <v>122289706</v>
       </c>
       <c r="B23" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473236</v>
+        <v>473015</v>
       </c>
       <c r="R23" t="n">
-        <v>6815621</v>
+        <v>6815193</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122289501</v>
+        <v>122289733</v>
       </c>
       <c r="B24" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472722</v>
+        <v>472993</v>
       </c>
       <c r="R24" t="n">
-        <v>6815373</v>
+        <v>6815490</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122289723</v>
+        <v>122289674</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472901</v>
+        <v>472736</v>
       </c>
       <c r="R25" t="n">
-        <v>6815361</v>
+        <v>6815067</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122289648</v>
+        <v>122289664</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472874</v>
+        <v>472722</v>
       </c>
       <c r="R26" t="n">
-        <v>6815282</v>
+        <v>6815115</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122289706</v>
+        <v>122289640</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473015</v>
+        <v>472893</v>
       </c>
       <c r="R27" t="n">
-        <v>6815193</v>
+        <v>6815451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122289733</v>
+        <v>122289741</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472993</v>
+        <v>473161</v>
       </c>
       <c r="R28" t="n">
-        <v>6815490</v>
+        <v>6815418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122289674</v>
+        <v>122289773</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472736</v>
+        <v>473042</v>
       </c>
       <c r="R29" t="n">
-        <v>6815067</v>
+        <v>6815081</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289664</v>
+        <v>122289494</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3629,21 +3629,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472722</v>
+        <v>473044</v>
       </c>
       <c r="R30" t="n">
-        <v>6815115</v>
+        <v>6815169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289640</v>
+        <v>122289477</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3731,21 +3731,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472893</v>
+        <v>472716</v>
       </c>
       <c r="R31" t="n">
-        <v>6815451</v>
+        <v>6815299</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289576</v>
+        <v>122289498</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
+        <v>78690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,39 +3945,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473233</v>
+        <v>472863</v>
       </c>
       <c r="R33" t="n">
-        <v>6815571</v>
+        <v>6815525</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,11 +4005,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4041,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122289565</v>
+        <v>122289510</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
+        <v>78690</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4057,39 +4047,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472697</v>
+        <v>472986</v>
       </c>
       <c r="R34" t="n">
-        <v>6815151</v>
+        <v>6815203</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4122,11 +4107,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122289600</v>
+        <v>122289521</v>
       </c>
       <c r="B35" t="n">
-        <v>78393</v>
+        <v>78690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4169,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472822</v>
+        <v>473236</v>
       </c>
       <c r="R35" t="n">
-        <v>6815541</v>
+        <v>6815621</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122289741</v>
+        <v>122289501</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4271,21 +4251,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4275,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473161</v>
+        <v>472722</v>
       </c>
       <c r="R36" t="n">
-        <v>6815418</v>
+        <v>6815373</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,10 +4337,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122289773</v>
+        <v>122289576</v>
       </c>
       <c r="B37" t="n">
-        <v>78040</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4373,34 +4353,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473042</v>
+        <v>473233</v>
       </c>
       <c r="R37" t="n">
-        <v>6815081</v>
+        <v>6815571</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4433,6 +4418,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4459,10 +4449,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122289494</v>
+        <v>122289565</v>
       </c>
       <c r="B38" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4475,34 +4465,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473044</v>
+        <v>472697</v>
       </c>
       <c r="R38" t="n">
-        <v>6815169</v>
+        <v>6815151</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4535,6 +4530,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4561,10 +4561,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122289477</v>
+        <v>122289600</v>
       </c>
       <c r="B39" t="n">
-        <v>79274</v>
+        <v>78393</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472716</v>
+        <v>472822</v>
       </c>
       <c r="R39" t="n">
-        <v>6815299</v>
+        <v>6815541</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5999,10 +5999,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122289699</v>
+        <v>122289560</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6015,34 +6015,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473050</v>
+        <v>472880</v>
       </c>
       <c r="R53" t="n">
-        <v>6815098</v>
+        <v>6815442</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6075,6 +6080,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6101,10 +6111,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122289696</v>
+        <v>122289564</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6117,34 +6127,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473033</v>
+        <v>472724</v>
       </c>
       <c r="R54" t="n">
-        <v>6815029</v>
+        <v>6815345</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6177,6 +6192,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6203,10 +6223,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122289689</v>
+        <v>122289476</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6219,21 +6239,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6243,10 +6263,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>472954</v>
+        <v>472813</v>
       </c>
       <c r="R55" t="n">
-        <v>6815041</v>
+        <v>6815369</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6305,7 +6325,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122289753</v>
+        <v>122289699</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6345,10 +6365,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473242</v>
+        <v>473050</v>
       </c>
       <c r="R56" t="n">
-        <v>6815602</v>
+        <v>6815098</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6407,7 +6427,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122289738</v>
+        <v>122289696</v>
       </c>
       <c r="B57" t="n">
         <v>78656</v>
@@ -6447,10 +6467,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473045</v>
+        <v>473033</v>
       </c>
       <c r="R57" t="n">
-        <v>6815390</v>
+        <v>6815029</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6509,10 +6529,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122289525</v>
+        <v>122289689</v>
       </c>
       <c r="B58" t="n">
-        <v>95784</v>
+        <v>78656</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6525,21 +6545,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6549,10 +6569,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>472724</v>
+        <v>472954</v>
       </c>
       <c r="R58" t="n">
-        <v>6815100</v>
+        <v>6815041</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6611,10 +6631,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122289476</v>
+        <v>122289753</v>
       </c>
       <c r="B59" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6627,21 +6647,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6651,10 +6671,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>472813</v>
+        <v>473242</v>
       </c>
       <c r="R59" t="n">
-        <v>6815369</v>
+        <v>6815602</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6713,10 +6733,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122289564</v>
+        <v>122289738</v>
       </c>
       <c r="B60" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6729,39 +6749,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>472724</v>
+        <v>473045</v>
       </c>
       <c r="R60" t="n">
-        <v>6815345</v>
+        <v>6815390</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6794,11 +6809,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6825,10 +6835,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122289599</v>
+        <v>122289525</v>
       </c>
       <c r="B61" t="n">
-        <v>78393</v>
+        <v>95784</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6841,21 +6851,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6865,10 +6875,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>472912</v>
+        <v>472724</v>
       </c>
       <c r="R61" t="n">
-        <v>6815662</v>
+        <v>6815100</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6927,10 +6937,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122289560</v>
+        <v>122289599</v>
       </c>
       <c r="B62" t="n">
-        <v>57383</v>
+        <v>78393</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6943,39 +6953,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>472880</v>
+        <v>472912</v>
       </c>
       <c r="R62" t="n">
-        <v>6815442</v>
+        <v>6815662</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7008,11 +7013,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7039,10 +7039,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122289493</v>
+        <v>122289518</v>
       </c>
       <c r="B63" t="n">
-        <v>74757</v>
+        <v>78690</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473003</v>
+        <v>473192</v>
       </c>
       <c r="R63" t="n">
-        <v>6814987</v>
+        <v>6815502</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7141,10 +7141,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122289557</v>
+        <v>122289504</v>
       </c>
       <c r="B64" t="n">
-        <v>57383</v>
+        <v>78690</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7157,39 +7157,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473230</v>
+        <v>472835</v>
       </c>
       <c r="R64" t="n">
-        <v>6815520</v>
+        <v>6815089</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7222,11 +7217,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7253,10 +7243,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122289518</v>
+        <v>122289609</v>
       </c>
       <c r="B65" t="n">
-        <v>78690</v>
+        <v>80613</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7269,21 +7259,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7293,10 +7283,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473192</v>
+        <v>472975</v>
       </c>
       <c r="R65" t="n">
-        <v>6815502</v>
+        <v>6815664</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7355,10 +7345,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122289504</v>
+        <v>122289716</v>
       </c>
       <c r="B66" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7371,21 +7361,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7395,10 +7385,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472835</v>
+        <v>472966</v>
       </c>
       <c r="R66" t="n">
-        <v>6815089</v>
+        <v>6815380</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7457,7 +7447,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122289716</v>
+        <v>122289678</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7497,10 +7487,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472966</v>
+        <v>472765</v>
       </c>
       <c r="R67" t="n">
-        <v>6815380</v>
+        <v>6815044</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7559,7 +7549,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122289678</v>
+        <v>122289743</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7599,10 +7589,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472765</v>
+        <v>473207</v>
       </c>
       <c r="R68" t="n">
-        <v>6815044</v>
+        <v>6815471</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7661,7 +7651,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122289743</v>
+        <v>122289728</v>
       </c>
       <c r="B69" t="n">
         <v>78656</v>
@@ -7701,10 +7691,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>473207</v>
+        <v>472936</v>
       </c>
       <c r="R69" t="n">
-        <v>6815471</v>
+        <v>6815401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7763,7 +7753,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289728</v>
+        <v>122289751</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -7803,10 +7793,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472936</v>
+        <v>473230</v>
       </c>
       <c r="R70" t="n">
-        <v>6815401</v>
+        <v>6815539</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7865,7 +7855,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289751</v>
+        <v>122289735</v>
       </c>
       <c r="B71" t="n">
         <v>78656</v>
@@ -7905,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>473230</v>
+        <v>473015</v>
       </c>
       <c r="R71" t="n">
-        <v>6815539</v>
+        <v>6815443</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7967,7 +7957,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122289735</v>
+        <v>122289746</v>
       </c>
       <c r="B72" t="n">
         <v>78656</v>
@@ -8007,10 +7997,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>473015</v>
+        <v>473192</v>
       </c>
       <c r="R72" t="n">
-        <v>6815443</v>
+        <v>6815502</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8069,7 +8059,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122289746</v>
+        <v>122289721</v>
       </c>
       <c r="B73" t="n">
         <v>78656</v>
@@ -8109,10 +8099,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>473192</v>
+        <v>472897</v>
       </c>
       <c r="R73" t="n">
-        <v>6815502</v>
+        <v>6815355</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8171,7 +8161,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122289721</v>
+        <v>122289656</v>
       </c>
       <c r="B74" t="n">
         <v>78656</v>
@@ -8211,10 +8201,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472897</v>
+        <v>472748</v>
       </c>
       <c r="R74" t="n">
-        <v>6815355</v>
+        <v>6815374</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8273,10 +8263,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122289656</v>
+        <v>122289493</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8289,21 +8279,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8313,10 +8303,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472748</v>
+        <v>473003</v>
       </c>
       <c r="R75" t="n">
-        <v>6815374</v>
+        <v>6814987</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8375,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122289609</v>
+        <v>122289557</v>
       </c>
       <c r="B76" t="n">
-        <v>80613</v>
+        <v>57383</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8391,34 +8381,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472975</v>
+        <v>473230</v>
       </c>
       <c r="R76" t="n">
-        <v>6815664</v>
+        <v>6815520</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8451,6 +8446,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -14269,10 +14269,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122289568</v>
+        <v>122289692</v>
       </c>
       <c r="B133" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14285,39 +14285,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>472863</v>
+        <v>472970</v>
       </c>
       <c r="R133" t="n">
-        <v>6815149</v>
+        <v>6814989</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14350,11 +14345,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14381,7 +14371,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122289692</v>
+        <v>122289712</v>
       </c>
       <c r="B134" t="n">
         <v>78656</v>
@@ -14421,10 +14411,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>472970</v>
+        <v>472971</v>
       </c>
       <c r="R134" t="n">
-        <v>6814989</v>
+        <v>6815298</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14483,7 +14473,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122289712</v>
+        <v>122289649</v>
       </c>
       <c r="B135" t="n">
         <v>78656</v>
@@ -14523,10 +14513,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>472971</v>
+        <v>472853</v>
       </c>
       <c r="R135" t="n">
-        <v>6815298</v>
+        <v>6815291</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14585,7 +14575,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122289649</v>
+        <v>122289681</v>
       </c>
       <c r="B136" t="n">
         <v>78656</v>
@@ -14625,10 +14615,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>472853</v>
+        <v>472834</v>
       </c>
       <c r="R136" t="n">
-        <v>6815291</v>
+        <v>6815094</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14687,7 +14677,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122289681</v>
+        <v>122289737</v>
       </c>
       <c r="B137" t="n">
         <v>78656</v>
@@ -14727,10 +14717,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>472834</v>
+        <v>473035</v>
       </c>
       <c r="R137" t="n">
-        <v>6815094</v>
+        <v>6815416</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14789,7 +14779,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122289737</v>
+        <v>122289662</v>
       </c>
       <c r="B138" t="n">
         <v>78656</v>
@@ -14829,10 +14819,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>473035</v>
+        <v>472697</v>
       </c>
       <c r="R138" t="n">
-        <v>6815416</v>
+        <v>6815151</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14891,7 +14881,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122289662</v>
+        <v>122289652</v>
       </c>
       <c r="B139" t="n">
         <v>78656</v>
@@ -14931,10 +14921,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>472697</v>
+        <v>472813</v>
       </c>
       <c r="R139" t="n">
-        <v>6815151</v>
+        <v>6815369</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14993,10 +14983,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122289652</v>
+        <v>122289546</v>
       </c>
       <c r="B140" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15009,34 +14999,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>472813</v>
+        <v>472731</v>
       </c>
       <c r="R140" t="n">
-        <v>6815369</v>
+        <v>6815088</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15095,10 +15090,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122289546</v>
+        <v>122289568</v>
       </c>
       <c r="B141" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15111,16 +15106,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15131,7 +15126,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15140,10 +15135,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>472731</v>
+        <v>472863</v>
       </c>
       <c r="R141" t="n">
-        <v>6815088</v>
+        <v>6815149</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15176,6 +15171,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15202,10 +15202,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122289586</v>
+        <v>122289516</v>
       </c>
       <c r="B142" t="n">
-        <v>57383</v>
+        <v>78690</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15218,39 +15218,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>473036</v>
+        <v>473107</v>
       </c>
       <c r="R142" t="n">
-        <v>6815173</v>
+        <v>6815366</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15283,11 +15278,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15314,10 +15304,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122289562</v>
+        <v>122289502</v>
       </c>
       <c r="B143" t="n">
-        <v>57383</v>
+        <v>78690</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15330,39 +15320,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>472869</v>
+        <v>472693</v>
       </c>
       <c r="R143" t="n">
-        <v>6815446</v>
+        <v>6815202</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15395,11 +15380,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15426,10 +15406,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122289573</v>
+        <v>122289749</v>
       </c>
       <c r="B144" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15442,39 +15422,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>473154</v>
+        <v>473236</v>
       </c>
       <c r="R144" t="n">
-        <v>6815410</v>
+        <v>6815526</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15507,11 +15482,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15538,10 +15508,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122289601</v>
+        <v>122289551</v>
       </c>
       <c r="B145" t="n">
-        <v>78393</v>
+        <v>79641</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15550,25 +15520,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15578,10 +15548,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>472894</v>
+        <v>472884</v>
       </c>
       <c r="R145" t="n">
-        <v>6815448</v>
+        <v>6815478</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15640,10 +15610,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122289605</v>
+        <v>122289658</v>
       </c>
       <c r="B146" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15656,21 +15626,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15680,10 +15650,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>472715</v>
+        <v>472721</v>
       </c>
       <c r="R146" t="n">
-        <v>6815304</v>
+        <v>6815373</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15742,7 +15712,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122289749</v>
+        <v>122289727</v>
       </c>
       <c r="B147" t="n">
         <v>78656</v>
@@ -15782,10 +15752,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>473236</v>
+        <v>472922</v>
       </c>
       <c r="R147" t="n">
-        <v>6815526</v>
+        <v>6815393</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15844,10 +15814,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122289551</v>
+        <v>122289688</v>
       </c>
       <c r="B148" t="n">
-        <v>79641</v>
+        <v>78656</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15856,25 +15826,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15884,10 +15854,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>472884</v>
+        <v>472911</v>
       </c>
       <c r="R148" t="n">
-        <v>6815478</v>
+        <v>6815063</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15946,10 +15916,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122289516</v>
+        <v>122289731</v>
       </c>
       <c r="B149" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15962,21 +15932,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15986,10 +15956,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>473107</v>
+        <v>472971</v>
       </c>
       <c r="R149" t="n">
-        <v>6815366</v>
+        <v>6815445</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16048,10 +16018,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122289502</v>
+        <v>122289693</v>
       </c>
       <c r="B150" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16064,21 +16034,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16088,10 +16058,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>472693</v>
+        <v>473002</v>
       </c>
       <c r="R150" t="n">
-        <v>6815202</v>
+        <v>6814987</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16150,7 +16120,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122289658</v>
+        <v>122289659</v>
       </c>
       <c r="B151" t="n">
         <v>78656</v>
@@ -16190,10 +16160,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>472721</v>
+        <v>472724</v>
       </c>
       <c r="R151" t="n">
-        <v>6815373</v>
+        <v>6815345</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16252,10 +16222,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122289727</v>
+        <v>122289586</v>
       </c>
       <c r="B152" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16268,34 +16238,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>472922</v>
+        <v>473036</v>
       </c>
       <c r="R152" t="n">
-        <v>6815393</v>
+        <v>6815173</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16328,6 +16303,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16354,10 +16334,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122289688</v>
+        <v>122289562</v>
       </c>
       <c r="B153" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16370,34 +16350,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>472911</v>
+        <v>472869</v>
       </c>
       <c r="R153" t="n">
-        <v>6815063</v>
+        <v>6815446</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16430,6 +16415,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16456,10 +16446,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122289731</v>
+        <v>122289573</v>
       </c>
       <c r="B154" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16472,34 +16462,39 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>472971</v>
+        <v>473154</v>
       </c>
       <c r="R154" t="n">
-        <v>6815445</v>
+        <v>6815410</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16532,6 +16527,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16558,10 +16558,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122289693</v>
+        <v>122289601</v>
       </c>
       <c r="B155" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16574,21 +16574,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16598,10 +16598,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>473002</v>
+        <v>472894</v>
       </c>
       <c r="R155" t="n">
-        <v>6814987</v>
+        <v>6815448</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16660,10 +16660,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122289659</v>
+        <v>122289605</v>
       </c>
       <c r="B156" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16676,21 +16676,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16700,10 +16700,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>472724</v>
+        <v>472715</v>
       </c>
       <c r="R156" t="n">
-        <v>6815345</v>
+        <v>6815304</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18322,7 +18322,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122289636</v>
+        <v>122289719</v>
       </c>
       <c r="B172" t="n">
         <v>78656</v>
@@ -18362,10 +18362,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>472843</v>
+        <v>472906</v>
       </c>
       <c r="R172" t="n">
-        <v>6815598</v>
+        <v>6815327</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18424,10 +18424,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122289730</v>
+        <v>122289512</v>
       </c>
       <c r="B173" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18440,21 +18440,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18464,10 +18464,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>472958</v>
+        <v>472977</v>
       </c>
       <c r="R173" t="n">
-        <v>6815427</v>
+        <v>6815273</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18526,7 +18526,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122289666</v>
+        <v>122289636</v>
       </c>
       <c r="B174" t="n">
         <v>78656</v>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>472737</v>
+        <v>472843</v>
       </c>
       <c r="R174" t="n">
-        <v>6815084</v>
+        <v>6815598</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18628,10 +18628,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122289512</v>
+        <v>122289730</v>
       </c>
       <c r="B175" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18644,21 +18644,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18668,10 +18668,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>472977</v>
+        <v>472958</v>
       </c>
       <c r="R175" t="n">
-        <v>6815273</v>
+        <v>6815427</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18730,7 +18730,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122289719</v>
+        <v>122289666</v>
       </c>
       <c r="B176" t="n">
         <v>78656</v>
@@ -18770,10 +18770,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>472906</v>
+        <v>472737</v>
       </c>
       <c r="R176" t="n">
-        <v>6815327</v>
+        <v>6815084</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19342,10 +19342,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122289581</v>
+        <v>122289519</v>
       </c>
       <c r="B182" t="n">
-        <v>57383</v>
+        <v>78690</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19358,39 +19358,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>472821</v>
+        <v>473217</v>
       </c>
       <c r="R182" t="n">
-        <v>6815364</v>
+        <v>6815515</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19423,11 +19418,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19454,10 +19444,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289580</v>
+        <v>122289486</v>
       </c>
       <c r="B183" t="n">
-        <v>57383</v>
+        <v>79274</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19470,39 +19460,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>472862</v>
+        <v>473115</v>
       </c>
       <c r="R183" t="n">
-        <v>6815472</v>
+        <v>6815359</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19535,11 +19520,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19566,10 +19546,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289531</v>
+        <v>122289665</v>
       </c>
       <c r="B184" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19582,21 +19562,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19606,10 +19586,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>473013</v>
+        <v>472722</v>
       </c>
       <c r="R184" t="n">
-        <v>6815498</v>
+        <v>6815109</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19780,10 +19760,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289519</v>
+        <v>122289581</v>
       </c>
       <c r="B186" t="n">
-        <v>78690</v>
+        <v>57383</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19796,34 +19776,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>473217</v>
+        <v>472821</v>
       </c>
       <c r="R186" t="n">
-        <v>6815515</v>
+        <v>6815364</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19856,6 +19841,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19882,10 +19872,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289486</v>
+        <v>122289580</v>
       </c>
       <c r="B187" t="n">
-        <v>79274</v>
+        <v>57383</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19898,34 +19888,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>473115</v>
+        <v>472862</v>
       </c>
       <c r="R187" t="n">
-        <v>6815359</v>
+        <v>6815472</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19958,6 +19953,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19984,10 +19984,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289665</v>
+        <v>122289531</v>
       </c>
       <c r="B188" t="n">
-        <v>78656</v>
+        <v>79245</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20000,21 +20000,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20024,10 +20024,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>472722</v>
+        <v>473013</v>
       </c>
       <c r="R188" t="n">
-        <v>6815109</v>
+        <v>6815498</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20188,10 +20188,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289563</v>
+        <v>122289638</v>
       </c>
       <c r="B190" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20204,39 +20204,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>472874</v>
+        <v>472871</v>
       </c>
       <c r="R190" t="n">
-        <v>6815282</v>
+        <v>6815512</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20269,11 +20264,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20300,10 +20290,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122289608</v>
+        <v>122289703</v>
       </c>
       <c r="B191" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20316,21 +20306,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20340,10 +20330,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>472951</v>
+        <v>473050</v>
       </c>
       <c r="R191" t="n">
-        <v>6815418</v>
+        <v>6815176</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20402,10 +20392,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122289598</v>
+        <v>122289747</v>
       </c>
       <c r="B192" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20418,21 +20408,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20442,10 +20432,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>473022</v>
+        <v>473203</v>
       </c>
       <c r="R192" t="n">
-        <v>6815732</v>
+        <v>6815521</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20504,10 +20494,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122289595</v>
+        <v>122289717</v>
       </c>
       <c r="B193" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20520,21 +20510,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20544,10 +20534,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>472813</v>
+        <v>472949</v>
       </c>
       <c r="R193" t="n">
-        <v>6815369</v>
+        <v>6815365</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20606,7 +20596,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122289638</v>
+        <v>122289695</v>
       </c>
       <c r="B194" t="n">
         <v>78656</v>
@@ -20646,10 +20636,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>472871</v>
+        <v>473035</v>
       </c>
       <c r="R194" t="n">
-        <v>6815512</v>
+        <v>6814991</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20708,7 +20698,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122289703</v>
+        <v>122289694</v>
       </c>
       <c r="B195" t="n">
         <v>78656</v>
@@ -20748,10 +20738,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>473050</v>
+        <v>473042</v>
       </c>
       <c r="R195" t="n">
-        <v>6815176</v>
+        <v>6814969</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20810,7 +20800,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122289747</v>
+        <v>122289630</v>
       </c>
       <c r="B196" t="n">
         <v>78656</v>
@@ -20850,10 +20840,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>473203</v>
+        <v>473038</v>
       </c>
       <c r="R196" t="n">
-        <v>6815521</v>
+        <v>6815393</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20912,7 +20902,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122289717</v>
+        <v>122289633</v>
       </c>
       <c r="B197" t="n">
         <v>78656</v>
@@ -20952,10 +20942,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>472949</v>
+        <v>472766</v>
       </c>
       <c r="R197" t="n">
-        <v>6815365</v>
+        <v>6815686</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21014,7 +21004,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122289695</v>
+        <v>122289705</v>
       </c>
       <c r="B198" t="n">
         <v>78656</v>
@@ -21054,10 +21044,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>473035</v>
+        <v>473019</v>
       </c>
       <c r="R198" t="n">
-        <v>6814991</v>
+        <v>6815163</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21116,7 +21106,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122289694</v>
+        <v>122289622</v>
       </c>
       <c r="B199" t="n">
         <v>78656</v>
@@ -21156,10 +21146,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>473042</v>
+        <v>472955</v>
       </c>
       <c r="R199" t="n">
-        <v>6814969</v>
+        <v>6815658</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21218,7 +21208,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122289630</v>
+        <v>122289732</v>
       </c>
       <c r="B200" t="n">
         <v>78656</v>
@@ -21258,10 +21248,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>473038</v>
+        <v>472971</v>
       </c>
       <c r="R200" t="n">
-        <v>6815393</v>
+        <v>6815467</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21320,7 +21310,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122289622</v>
+        <v>122289657</v>
       </c>
       <c r="B201" t="n">
         <v>78656</v>
@@ -21360,10 +21350,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>472955</v>
+        <v>472730</v>
       </c>
       <c r="R201" t="n">
-        <v>6815658</v>
+        <v>6815383</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21422,10 +21412,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122289732</v>
+        <v>122289608</v>
       </c>
       <c r="B202" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21438,21 +21428,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21462,10 +21452,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>472971</v>
+        <v>472951</v>
       </c>
       <c r="R202" t="n">
-        <v>6815467</v>
+        <v>6815418</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21524,10 +21514,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122289633</v>
+        <v>122289598</v>
       </c>
       <c r="B203" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21540,21 +21530,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21564,10 +21554,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>472766</v>
+        <v>473022</v>
       </c>
       <c r="R203" t="n">
-        <v>6815686</v>
+        <v>6815732</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21626,10 +21616,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122289705</v>
+        <v>122289595</v>
       </c>
       <c r="B204" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21642,21 +21632,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21666,10 +21656,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>473019</v>
+        <v>472813</v>
       </c>
       <c r="R204" t="n">
-        <v>6815163</v>
+        <v>6815369</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21728,10 +21718,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122289657</v>
+        <v>122289563</v>
       </c>
       <c r="B205" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21744,34 +21734,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>472730</v>
+        <v>472874</v>
       </c>
       <c r="R205" t="n">
-        <v>6815383</v>
+        <v>6815282</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21804,6 +21799,11 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24132,10 +24132,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122289520</v>
+        <v>122289641</v>
       </c>
       <c r="B228" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24148,21 +24148,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24172,10 +24172,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>473245</v>
+        <v>472882</v>
       </c>
       <c r="R228" t="n">
-        <v>6815602</v>
+        <v>6815476</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24234,10 +24234,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122289769</v>
+        <v>122289621</v>
       </c>
       <c r="B229" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24250,39 +24250,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>472842</v>
+        <v>473076</v>
       </c>
       <c r="R229" t="n">
-        <v>6815605</v>
+        <v>6815660</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24315,11 +24310,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24346,10 +24336,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122289556</v>
+        <v>122289740</v>
       </c>
       <c r="B230" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24362,39 +24352,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>472995</v>
+        <v>473153</v>
       </c>
       <c r="R230" t="n">
-        <v>6815217</v>
+        <v>6815381</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24427,11 +24412,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24458,10 +24438,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>122289578</v>
+        <v>122289710</v>
       </c>
       <c r="B231" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24474,39 +24454,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>472860</v>
+        <v>472998</v>
       </c>
       <c r="R231" t="n">
-        <v>6815679</v>
+        <v>6815243</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24539,11 +24514,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24570,10 +24540,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>122289569</v>
+        <v>122289680</v>
       </c>
       <c r="B232" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24586,39 +24556,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>473043</v>
+        <v>472808</v>
       </c>
       <c r="R232" t="n">
-        <v>6815180</v>
+        <v>6815067</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24651,11 +24616,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24682,10 +24642,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>122289528</v>
+        <v>122289520</v>
       </c>
       <c r="B233" t="n">
-        <v>79245</v>
+        <v>78690</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24698,21 +24658,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24722,10 +24682,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>473019</v>
+        <v>473245</v>
       </c>
       <c r="R233" t="n">
-        <v>6815730</v>
+        <v>6815602</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24784,10 +24744,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>122289641</v>
+        <v>122289769</v>
       </c>
       <c r="B234" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24800,34 +24760,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>472882</v>
+        <v>472842</v>
       </c>
       <c r="R234" t="n">
-        <v>6815476</v>
+        <v>6815605</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24860,6 +24825,11 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24886,10 +24856,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>122289621</v>
+        <v>122289556</v>
       </c>
       <c r="B235" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24902,34 +24872,39 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>473076</v>
+        <v>472995</v>
       </c>
       <c r="R235" t="n">
-        <v>6815660</v>
+        <v>6815217</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24962,6 +24937,11 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24988,10 +24968,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>122289740</v>
+        <v>122289578</v>
       </c>
       <c r="B236" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25004,34 +24984,39 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>473153</v>
+        <v>472860</v>
       </c>
       <c r="R236" t="n">
-        <v>6815381</v>
+        <v>6815679</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25064,6 +25049,11 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25090,10 +25080,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>122289710</v>
+        <v>122289569</v>
       </c>
       <c r="B237" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25106,34 +25096,39 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>472998</v>
+        <v>473043</v>
       </c>
       <c r="R237" t="n">
-        <v>6815243</v>
+        <v>6815180</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25166,6 +25161,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25192,10 +25192,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122289680</v>
+        <v>122289528</v>
       </c>
       <c r="B238" t="n">
-        <v>78656</v>
+        <v>79245</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25208,21 +25208,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25232,10 +25232,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>472808</v>
+        <v>473019</v>
       </c>
       <c r="R238" t="n">
-        <v>6815067</v>
+        <v>6815730</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25498,10 +25498,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>122289532</v>
+        <v>122289517</v>
       </c>
       <c r="B241" t="n">
-        <v>79245</v>
+        <v>78690</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25514,21 +25514,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25538,10 +25538,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>473191</v>
+        <v>473149</v>
       </c>
       <c r="R241" t="n">
-        <v>6815504</v>
+        <v>6815391</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25600,7 +25600,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122289530</v>
+        <v>122289532</v>
       </c>
       <c r="B242" t="n">
         <v>79245</v>
@@ -25640,10 +25640,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>473042</v>
+        <v>473191</v>
       </c>
       <c r="R242" t="n">
-        <v>6815081</v>
+        <v>6815504</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25702,10 +25702,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122289517</v>
+        <v>122289530</v>
       </c>
       <c r="B243" t="n">
-        <v>78690</v>
+        <v>79245</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25718,21 +25718,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25742,10 +25742,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>473149</v>
+        <v>473042</v>
       </c>
       <c r="R243" t="n">
-        <v>6815391</v>
+        <v>6815081</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25804,10 +25804,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122289668</v>
+        <v>122289590</v>
       </c>
       <c r="B244" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25820,34 +25820,39 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>472718</v>
+        <v>472945</v>
       </c>
       <c r="R244" t="n">
-        <v>6815026</v>
+        <v>6815381</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25880,6 +25885,11 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25906,10 +25916,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122289632</v>
+        <v>122289577</v>
       </c>
       <c r="B245" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25922,34 +25932,39 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>472754</v>
+        <v>472922</v>
       </c>
       <c r="R245" t="n">
-        <v>6815718</v>
+        <v>6815653</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25982,6 +25997,11 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26008,10 +26028,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122289708</v>
+        <v>122289485</v>
       </c>
       <c r="B246" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -26024,21 +26044,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -26048,10 +26068,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>473000</v>
+        <v>473014</v>
       </c>
       <c r="R246" t="n">
-        <v>6815193</v>
+        <v>6815496</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26110,10 +26130,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122289748</v>
+        <v>122289474</v>
       </c>
       <c r="B247" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -26126,21 +26146,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -26150,10 +26170,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>473217</v>
+        <v>473224</v>
       </c>
       <c r="R247" t="n">
-        <v>6815515</v>
+        <v>6815618</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26212,10 +26232,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122289663</v>
+        <v>122289774</v>
       </c>
       <c r="B248" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26228,21 +26248,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -26252,10 +26272,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>472719</v>
+        <v>473192</v>
       </c>
       <c r="R248" t="n">
-        <v>6815128</v>
+        <v>6815503</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26314,10 +26334,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122289667</v>
+        <v>122289491</v>
       </c>
       <c r="B249" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26330,21 +26350,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -26354,10 +26374,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>472741</v>
+        <v>472841</v>
       </c>
       <c r="R249" t="n">
-        <v>6815075</v>
+        <v>6815128</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26416,7 +26436,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122289684</v>
+        <v>122289668</v>
       </c>
       <c r="B250" t="n">
         <v>78656</v>
@@ -26456,10 +26476,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>472882</v>
+        <v>472718</v>
       </c>
       <c r="R250" t="n">
-        <v>6815139</v>
+        <v>6815026</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26518,7 +26538,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122289755</v>
+        <v>122289632</v>
       </c>
       <c r="B251" t="n">
         <v>78656</v>
@@ -26558,10 +26578,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>473241</v>
+        <v>472754</v>
       </c>
       <c r="R251" t="n">
-        <v>6815645</v>
+        <v>6815718</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26620,10 +26640,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122289485</v>
+        <v>122289708</v>
       </c>
       <c r="B252" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26636,21 +26656,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26660,10 +26680,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>473014</v>
+        <v>473000</v>
       </c>
       <c r="R252" t="n">
-        <v>6815496</v>
+        <v>6815193</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26722,10 +26742,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289474</v>
+        <v>122289748</v>
       </c>
       <c r="B253" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26738,21 +26758,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26762,10 +26782,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>473224</v>
+        <v>473217</v>
       </c>
       <c r="R253" t="n">
-        <v>6815618</v>
+        <v>6815515</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26824,10 +26844,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289774</v>
+        <v>122289663</v>
       </c>
       <c r="B254" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26840,21 +26860,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26864,10 +26884,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>473192</v>
+        <v>472719</v>
       </c>
       <c r="R254" t="n">
-        <v>6815503</v>
+        <v>6815128</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26926,10 +26946,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289491</v>
+        <v>122289667</v>
       </c>
       <c r="B255" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26942,21 +26962,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26966,10 +26986,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>472841</v>
+        <v>472741</v>
       </c>
       <c r="R255" t="n">
-        <v>6815128</v>
+        <v>6815075</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27028,10 +27048,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289590</v>
+        <v>122289684</v>
       </c>
       <c r="B256" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27044,39 +27064,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>472945</v>
+        <v>472882</v>
       </c>
       <c r="R256" t="n">
-        <v>6815381</v>
+        <v>6815139</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27109,11 +27124,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27140,10 +27150,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289577</v>
+        <v>122289755</v>
       </c>
       <c r="B257" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27156,39 +27166,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>472922</v>
+        <v>473241</v>
       </c>
       <c r="R257" t="n">
-        <v>6815653</v>
+        <v>6815645</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27221,11 +27226,6 @@
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27252,10 +27252,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289503</v>
+        <v>122289770</v>
       </c>
       <c r="B258" t="n">
-        <v>78690</v>
+        <v>78301</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27268,21 +27268,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27292,10 +27292,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>472704</v>
+        <v>473114</v>
       </c>
       <c r="R258" t="n">
-        <v>6815035</v>
+        <v>6815360</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27354,10 +27354,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289509</v>
+        <v>122289715</v>
       </c>
       <c r="B259" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27370,21 +27370,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27394,10 +27394,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>473014</v>
+        <v>472966</v>
       </c>
       <c r="R259" t="n">
-        <v>6815194</v>
+        <v>6815390</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27456,10 +27456,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122289589</v>
+        <v>122289651</v>
       </c>
       <c r="B260" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27472,39 +27472,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>472928</v>
+        <v>472821</v>
       </c>
       <c r="R260" t="n">
-        <v>6815346</v>
+        <v>6815364</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27537,11 +27532,6 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27568,10 +27558,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122289591</v>
+        <v>122289687</v>
       </c>
       <c r="B261" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27584,39 +27574,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>473243</v>
+        <v>472899</v>
       </c>
       <c r="R261" t="n">
-        <v>6815620</v>
+        <v>6815079</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27649,11 +27634,6 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27680,10 +27660,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122289770</v>
+        <v>122289671</v>
       </c>
       <c r="B262" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27696,21 +27676,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27720,10 +27700,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>473114</v>
+        <v>472713</v>
       </c>
       <c r="R262" t="n">
-        <v>6815360</v>
+        <v>6815067</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27782,10 +27762,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122289715</v>
+        <v>122289618</v>
       </c>
       <c r="B263" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27798,21 +27778,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -27822,10 +27802,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>472966</v>
+        <v>473257</v>
       </c>
       <c r="R263" t="n">
-        <v>6815390</v>
+        <v>6815716</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27884,7 +27864,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122289651</v>
+        <v>122289624</v>
       </c>
       <c r="B264" t="n">
         <v>78656</v>
@@ -27924,10 +27904,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>472821</v>
+        <v>472913</v>
       </c>
       <c r="R264" t="n">
-        <v>6815364</v>
+        <v>6815662</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27986,7 +27966,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122289687</v>
+        <v>122289690</v>
       </c>
       <c r="B265" t="n">
         <v>78656</v>
@@ -28026,10 +28006,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>472899</v>
+        <v>472957</v>
       </c>
       <c r="R265" t="n">
-        <v>6815079</v>
+        <v>6815023</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28088,7 +28068,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122289671</v>
+        <v>122289634</v>
       </c>
       <c r="B266" t="n">
         <v>78656</v>
@@ -28128,10 +28108,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>472713</v>
+        <v>472785</v>
       </c>
       <c r="R266" t="n">
-        <v>6815067</v>
+        <v>6815675</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28190,10 +28170,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122289618</v>
+        <v>122289750</v>
       </c>
       <c r="B267" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28206,21 +28186,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -28230,10 +28210,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>473257</v>
+        <v>473232</v>
       </c>
       <c r="R267" t="n">
-        <v>6815716</v>
+        <v>6815538</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28292,7 +28272,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122289624</v>
+        <v>122289629</v>
       </c>
       <c r="B268" t="n">
         <v>78656</v>
@@ -28332,10 +28312,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>472913</v>
+        <v>472833</v>
       </c>
       <c r="R268" t="n">
-        <v>6815662</v>
+        <v>6815744</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28394,10 +28374,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122289690</v>
+        <v>122289503</v>
       </c>
       <c r="B269" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28410,21 +28390,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28434,10 +28414,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>472957</v>
+        <v>472704</v>
       </c>
       <c r="R269" t="n">
-        <v>6815023</v>
+        <v>6815035</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28496,10 +28476,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122289634</v>
+        <v>122289509</v>
       </c>
       <c r="B270" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28512,21 +28492,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28536,10 +28516,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>472785</v>
+        <v>473014</v>
       </c>
       <c r="R270" t="n">
-        <v>6815675</v>
+        <v>6815194</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28598,10 +28578,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122289750</v>
+        <v>122289589</v>
       </c>
       <c r="B271" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28614,34 +28594,39 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>473232</v>
+        <v>472928</v>
       </c>
       <c r="R271" t="n">
-        <v>6815538</v>
+        <v>6815346</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28674,6 +28659,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28700,10 +28690,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122289629</v>
+        <v>122289591</v>
       </c>
       <c r="B272" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28716,34 +28706,39 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>472833</v>
+        <v>473243</v>
       </c>
       <c r="R272" t="n">
-        <v>6815744</v>
+        <v>6815620</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28776,6 +28771,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD272" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122289712</v>
+        <v>122289772</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472971</v>
+        <v>473001</v>
       </c>
       <c r="R32" t="n">
-        <v>6815298</v>
+        <v>6815720</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289653</v>
+        <v>122289712</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472794</v>
+        <v>472971</v>
       </c>
       <c r="R33" t="n">
-        <v>6815364</v>
+        <v>6815298</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122289719</v>
+        <v>122289699</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472906</v>
+        <v>473050</v>
       </c>
       <c r="R34" t="n">
-        <v>6815327</v>
+        <v>6815098</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,10 +4128,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122289772</v>
+        <v>122289681</v>
       </c>
       <c r="B35" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473001</v>
+        <v>472834</v>
       </c>
       <c r="R35" t="n">
-        <v>6815720</v>
+        <v>6815094</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122289699</v>
+        <v>122289707</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473050</v>
+        <v>473010</v>
       </c>
       <c r="R36" t="n">
-        <v>6815098</v>
+        <v>6815184</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122289681</v>
+        <v>122289611</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4348,21 +4348,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472834</v>
+        <v>472749</v>
       </c>
       <c r="R37" t="n">
-        <v>6815094</v>
+        <v>6815725</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122289707</v>
+        <v>122289748</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473010</v>
+        <v>473217</v>
       </c>
       <c r="R38" t="n">
-        <v>6815184</v>
+        <v>6815515</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4536,10 +4536,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122289611</v>
+        <v>122289653</v>
       </c>
       <c r="B39" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4552,21 +4552,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472749</v>
+        <v>472794</v>
       </c>
       <c r="R39" t="n">
-        <v>6815725</v>
+        <v>6815364</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122289748</v>
+        <v>122289719</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473217</v>
+        <v>472906</v>
       </c>
       <c r="R40" t="n">
-        <v>6815515</v>
+        <v>6815327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -10259,7 +10259,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122289497</v>
+        <v>122289521</v>
       </c>
       <c r="B94" t="n">
         <v>78690</v>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>472959</v>
+        <v>473236</v>
       </c>
       <c r="R94" t="n">
-        <v>6815656</v>
+        <v>6815621</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10361,10 +10361,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122289521</v>
+        <v>122289547</v>
       </c>
       <c r="B95" t="n">
-        <v>78690</v>
+        <v>79738</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10377,21 +10377,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>473236</v>
+        <v>472833</v>
       </c>
       <c r="R95" t="n">
-        <v>6815621</v>
+        <v>6815619</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10463,10 +10463,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122289547</v>
+        <v>122289572</v>
       </c>
       <c r="B96" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10479,34 +10479,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>472833</v>
+        <v>472916</v>
       </c>
       <c r="R96" t="n">
-        <v>6815619</v>
+        <v>6815362</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10539,6 +10544,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10565,10 +10575,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122289692</v>
+        <v>122289538</v>
       </c>
       <c r="B97" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10581,21 +10591,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10605,10 +10615,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>472970</v>
+        <v>472787</v>
       </c>
       <c r="R97" t="n">
-        <v>6814989</v>
+        <v>6815675</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10667,10 +10677,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122289733</v>
+        <v>122289497</v>
       </c>
       <c r="B98" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10683,21 +10693,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10707,10 +10717,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>472993</v>
+        <v>472959</v>
       </c>
       <c r="R98" t="n">
-        <v>6815490</v>
+        <v>6815656</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10769,7 +10779,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122289625</v>
+        <v>122289692</v>
       </c>
       <c r="B99" t="n">
         <v>78656</v>
@@ -10809,10 +10819,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>472874</v>
+        <v>472970</v>
       </c>
       <c r="R99" t="n">
-        <v>6815658</v>
+        <v>6814989</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10871,7 +10881,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122289738</v>
+        <v>122289716</v>
       </c>
       <c r="B100" t="n">
         <v>78656</v>
@@ -10911,10 +10921,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>473045</v>
+        <v>472966</v>
       </c>
       <c r="R100" t="n">
-        <v>6815390</v>
+        <v>6815380</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10973,7 +10983,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122289694</v>
+        <v>122289733</v>
       </c>
       <c r="B101" t="n">
         <v>78656</v>
@@ -11013,10 +11023,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>473042</v>
+        <v>472993</v>
       </c>
       <c r="R101" t="n">
-        <v>6814969</v>
+        <v>6815490</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11075,7 +11085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122289627</v>
+        <v>122289625</v>
       </c>
       <c r="B102" t="n">
         <v>78656</v>
@@ -11115,10 +11125,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>472837</v>
+        <v>472874</v>
       </c>
       <c r="R102" t="n">
-        <v>6815704</v>
+        <v>6815658</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11177,10 +11187,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122289612</v>
+        <v>122289738</v>
       </c>
       <c r="B103" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11193,21 +11203,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11217,10 +11227,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472742</v>
+        <v>473045</v>
       </c>
       <c r="R103" t="n">
-        <v>6815075</v>
+        <v>6815390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11279,10 +11289,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122289711</v>
+        <v>122289774</v>
       </c>
       <c r="B104" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11295,21 +11305,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11319,10 +11329,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472976</v>
+        <v>473192</v>
       </c>
       <c r="R104" t="n">
-        <v>6815272</v>
+        <v>6815503</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11381,7 +11391,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122289669</v>
+        <v>122289694</v>
       </c>
       <c r="B105" t="n">
         <v>78656</v>
@@ -11421,10 +11431,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472718</v>
+        <v>473042</v>
       </c>
       <c r="R105" t="n">
-        <v>6815041</v>
+        <v>6814969</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11483,10 +11493,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122289572</v>
+        <v>122289627</v>
       </c>
       <c r="B106" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11499,39 +11509,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472916</v>
+        <v>472837</v>
       </c>
       <c r="R106" t="n">
-        <v>6815362</v>
+        <v>6815704</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11564,11 +11569,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11595,10 +11595,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122289538</v>
+        <v>122289612</v>
       </c>
       <c r="B107" t="n">
-        <v>57536</v>
+        <v>78392</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11611,21 +11611,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11635,10 +11635,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>472787</v>
+        <v>472742</v>
       </c>
       <c r="R107" t="n">
-        <v>6815675</v>
+        <v>6815075</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11697,10 +11697,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122289598</v>
+        <v>122289711</v>
       </c>
       <c r="B108" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11713,21 +11713,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11737,10 +11737,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>473022</v>
+        <v>472976</v>
       </c>
       <c r="R108" t="n">
-        <v>6815732</v>
+        <v>6815272</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11799,7 +11799,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122289716</v>
+        <v>122289669</v>
       </c>
       <c r="B109" t="n">
         <v>78656</v>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472966</v>
+        <v>472718</v>
       </c>
       <c r="R109" t="n">
-        <v>6815380</v>
+        <v>6815041</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11901,10 +11901,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122289774</v>
+        <v>122289598</v>
       </c>
       <c r="B110" t="n">
-        <v>78040</v>
+        <v>78393</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11917,21 +11917,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>473192</v>
+        <v>473022</v>
       </c>
       <c r="R110" t="n">
-        <v>6815503</v>
+        <v>6815732</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12941,10 +12941,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122289608</v>
+        <v>122289524</v>
       </c>
       <c r="B120" t="n">
-        <v>78393</v>
+        <v>78690</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12957,21 +12957,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>472951</v>
+        <v>473242</v>
       </c>
       <c r="R120" t="n">
-        <v>6815418</v>
+        <v>6815724</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13043,10 +13043,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122289524</v>
+        <v>122289682</v>
       </c>
       <c r="B121" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13059,21 +13059,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>473242</v>
+        <v>472846</v>
       </c>
       <c r="R121" t="n">
-        <v>6815724</v>
+        <v>6815101</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13145,10 +13145,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122289682</v>
+        <v>122289492</v>
       </c>
       <c r="B122" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13161,21 +13161,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13185,10 +13185,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>472846</v>
+        <v>472897</v>
       </c>
       <c r="R122" t="n">
-        <v>6815101</v>
+        <v>6815078</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13247,10 +13247,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122289492</v>
+        <v>122289619</v>
       </c>
       <c r="B123" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13263,21 +13263,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>472897</v>
+        <v>473228</v>
       </c>
       <c r="R123" t="n">
-        <v>6815078</v>
+        <v>6815569</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13349,7 +13349,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122289619</v>
+        <v>122289628</v>
       </c>
       <c r="B124" t="n">
         <v>78656</v>
@@ -13389,10 +13389,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>473228</v>
+        <v>472851</v>
       </c>
       <c r="R124" t="n">
-        <v>6815569</v>
+        <v>6815729</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13451,7 +13451,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122289628</v>
+        <v>122289621</v>
       </c>
       <c r="B125" t="n">
         <v>78656</v>
@@ -13491,10 +13491,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>472851</v>
+        <v>473076</v>
       </c>
       <c r="R125" t="n">
-        <v>6815729</v>
+        <v>6815660</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122289621</v>
+        <v>122289727</v>
       </c>
       <c r="B126" t="n">
         <v>78656</v>
@@ -13593,10 +13593,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>473076</v>
+        <v>472922</v>
       </c>
       <c r="R126" t="n">
-        <v>6815660</v>
+        <v>6815393</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13655,10 +13655,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122289727</v>
+        <v>122289539</v>
       </c>
       <c r="B127" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13671,21 +13671,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13695,10 +13695,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>472922</v>
+        <v>473229</v>
       </c>
       <c r="R127" t="n">
-        <v>6815393</v>
+        <v>6815569</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13757,10 +13757,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122289539</v>
+        <v>122289608</v>
       </c>
       <c r="B128" t="n">
-        <v>90859</v>
+        <v>78393</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13773,21 +13773,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13797,10 +13797,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>473229</v>
+        <v>472951</v>
       </c>
       <c r="R128" t="n">
-        <v>6815569</v>
+        <v>6815418</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14083,10 +14083,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122289493</v>
+        <v>122289576</v>
       </c>
       <c r="B131" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14099,34 +14099,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>473003</v>
+        <v>473233</v>
       </c>
       <c r="R131" t="n">
-        <v>6814987</v>
+        <v>6815571</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14159,6 +14164,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14185,10 +14195,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122289485</v>
+        <v>122289570</v>
       </c>
       <c r="B132" t="n">
-        <v>79274</v>
+        <v>57383</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14201,34 +14211,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>473014</v>
+        <v>473034</v>
       </c>
       <c r="R132" t="n">
-        <v>6815496</v>
+        <v>6815167</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14261,6 +14276,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14287,10 +14307,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122289664</v>
+        <v>122289528</v>
       </c>
       <c r="B133" t="n">
-        <v>78656</v>
+        <v>79245</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14303,21 +14323,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14327,10 +14347,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>472722</v>
+        <v>473019</v>
       </c>
       <c r="R133" t="n">
-        <v>6815115</v>
+        <v>6815730</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14389,10 +14409,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122289576</v>
+        <v>122289493</v>
       </c>
       <c r="B134" t="n">
-        <v>57383</v>
+        <v>74757</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14405,39 +14425,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>473233</v>
+        <v>473003</v>
       </c>
       <c r="R134" t="n">
-        <v>6815571</v>
+        <v>6814987</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14470,11 +14485,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14501,10 +14511,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122289570</v>
+        <v>122289485</v>
       </c>
       <c r="B135" t="n">
-        <v>57383</v>
+        <v>79274</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14517,39 +14527,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>473034</v>
+        <v>473014</v>
       </c>
       <c r="R135" t="n">
-        <v>6815167</v>
+        <v>6815496</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14582,11 +14587,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14613,10 +14613,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122289516</v>
+        <v>122289737</v>
       </c>
       <c r="B136" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14629,21 +14629,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14653,10 +14653,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>473107</v>
+        <v>473035</v>
       </c>
       <c r="R136" t="n">
-        <v>6815366</v>
+        <v>6815416</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14715,10 +14715,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122289518</v>
+        <v>122289664</v>
       </c>
       <c r="B137" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14731,21 +14731,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>473192</v>
+        <v>472722</v>
       </c>
       <c r="R137" t="n">
-        <v>6815502</v>
+        <v>6815115</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14817,10 +14817,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122289501</v>
+        <v>122289663</v>
       </c>
       <c r="B138" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14833,21 +14833,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14857,10 +14857,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>472722</v>
+        <v>472719</v>
       </c>
       <c r="R138" t="n">
-        <v>6815373</v>
+        <v>6815128</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14919,7 +14919,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122289737</v>
+        <v>122289744</v>
       </c>
       <c r="B139" t="n">
         <v>78656</v>
@@ -14959,10 +14959,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>473035</v>
+        <v>473188</v>
       </c>
       <c r="R139" t="n">
-        <v>6815416</v>
+        <v>6815489</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15021,7 +15021,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122289663</v>
+        <v>122289672</v>
       </c>
       <c r="B140" t="n">
         <v>78656</v>
@@ -15061,10 +15061,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>472719</v>
+        <v>472720</v>
       </c>
       <c r="R140" t="n">
-        <v>6815128</v>
+        <v>6815067</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15123,7 +15123,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122289744</v>
+        <v>122289735</v>
       </c>
       <c r="B141" t="n">
         <v>78656</v>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>473188</v>
+        <v>473015</v>
       </c>
       <c r="R141" t="n">
-        <v>6815489</v>
+        <v>6815443</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15225,7 +15225,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122289672</v>
+        <v>122289657</v>
       </c>
       <c r="B142" t="n">
         <v>78656</v>
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>472720</v>
+        <v>472730</v>
       </c>
       <c r="R142" t="n">
-        <v>6815067</v>
+        <v>6815383</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15327,10 +15327,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122289735</v>
+        <v>122289476</v>
       </c>
       <c r="B143" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15343,21 +15343,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15367,10 +15367,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>473015</v>
+        <v>472813</v>
       </c>
       <c r="R143" t="n">
-        <v>6815443</v>
+        <v>6815369</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15429,10 +15429,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122289657</v>
+        <v>122289516</v>
       </c>
       <c r="B144" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15445,21 +15445,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15469,10 +15469,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>472730</v>
+        <v>473107</v>
       </c>
       <c r="R144" t="n">
-        <v>6815383</v>
+        <v>6815366</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15531,10 +15531,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122289476</v>
+        <v>122289518</v>
       </c>
       <c r="B145" t="n">
-        <v>79274</v>
+        <v>78690</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15547,21 +15547,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15571,10 +15571,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>472813</v>
+        <v>473192</v>
       </c>
       <c r="R145" t="n">
-        <v>6815369</v>
+        <v>6815502</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15633,10 +15633,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122289528</v>
+        <v>122289501</v>
       </c>
       <c r="B146" t="n">
-        <v>79245</v>
+        <v>78690</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>473019</v>
+        <v>472722</v>
       </c>
       <c r="R146" t="n">
-        <v>6815730</v>
+        <v>6815373</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15735,10 +15735,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122289511</v>
+        <v>122289649</v>
       </c>
       <c r="B147" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15751,21 +15751,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15775,10 +15775,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>472998</v>
+        <v>472853</v>
       </c>
       <c r="R147" t="n">
-        <v>6815243</v>
+        <v>6815291</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15837,7 +15837,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122289734</v>
+        <v>122289639</v>
       </c>
       <c r="B148" t="n">
         <v>78656</v>
@@ -15877,10 +15877,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>473018</v>
+        <v>472869</v>
       </c>
       <c r="R148" t="n">
-        <v>6815464</v>
+        <v>6815500</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15939,7 +15939,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122289741</v>
+        <v>122289670</v>
       </c>
       <c r="B149" t="n">
         <v>78656</v>
@@ -15979,10 +15979,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>473161</v>
+        <v>472698</v>
       </c>
       <c r="R149" t="n">
-        <v>6815418</v>
+        <v>6815034</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16041,10 +16041,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122289477</v>
+        <v>122289673</v>
       </c>
       <c r="B150" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16057,21 +16057,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16081,10 +16081,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>472716</v>
+        <v>472729</v>
       </c>
       <c r="R150" t="n">
-        <v>6815299</v>
+        <v>6815062</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122289626</v>
+        <v>122289734</v>
       </c>
       <c r="B151" t="n">
         <v>78656</v>
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>472855</v>
+        <v>473018</v>
       </c>
       <c r="R151" t="n">
-        <v>6815671</v>
+        <v>6815464</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16245,7 +16245,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122289662</v>
+        <v>122289741</v>
       </c>
       <c r="B152" t="n">
         <v>78656</v>
@@ -16285,10 +16285,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>472697</v>
+        <v>473161</v>
       </c>
       <c r="R152" t="n">
-        <v>6815151</v>
+        <v>6815418</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16347,10 +16347,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122289649</v>
+        <v>122289477</v>
       </c>
       <c r="B153" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16363,21 +16363,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16387,10 +16387,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>472853</v>
+        <v>472716</v>
       </c>
       <c r="R153" t="n">
-        <v>6815291</v>
+        <v>6815299</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16449,7 +16449,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122289639</v>
+        <v>122289626</v>
       </c>
       <c r="B154" t="n">
         <v>78656</v>
@@ -16489,10 +16489,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>472869</v>
+        <v>472855</v>
       </c>
       <c r="R154" t="n">
-        <v>6815500</v>
+        <v>6815671</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16551,7 +16551,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122289670</v>
+        <v>122289662</v>
       </c>
       <c r="B155" t="n">
         <v>78656</v>
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>472698</v>
+        <v>472697</v>
       </c>
       <c r="R155" t="n">
-        <v>6815034</v>
+        <v>6815151</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16653,10 +16653,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122289673</v>
+        <v>122289605</v>
       </c>
       <c r="B156" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16669,21 +16669,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16693,10 +16693,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>472729</v>
+        <v>472715</v>
       </c>
       <c r="R156" t="n">
-        <v>6815062</v>
+        <v>6815304</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16755,10 +16755,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122289605</v>
+        <v>122289511</v>
       </c>
       <c r="B157" t="n">
-        <v>78393</v>
+        <v>78690</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16771,21 +16771,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16795,10 +16795,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>472715</v>
+        <v>472998</v>
       </c>
       <c r="R157" t="n">
-        <v>6815304</v>
+        <v>6815243</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -27951,10 +27951,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122289592</v>
+        <v>122289698</v>
       </c>
       <c r="B265" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27967,39 +27967,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>473038</v>
+        <v>473037</v>
       </c>
       <c r="R265" t="n">
-        <v>6815393</v>
+        <v>6815086</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28058,10 +28053,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122289586</v>
+        <v>122289717</v>
       </c>
       <c r="B266" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -28074,39 +28069,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>473036</v>
+        <v>472949</v>
       </c>
       <c r="R266" t="n">
-        <v>6815173</v>
+        <v>6815365</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28139,11 +28129,6 @@
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28170,10 +28155,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122289537</v>
+        <v>122289680</v>
       </c>
       <c r="B267" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28186,39 +28171,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>472724</v>
+        <v>472808</v>
       </c>
       <c r="R267" t="n">
-        <v>6815093</v>
+        <v>6815067</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28277,7 +28257,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122289533</v>
+        <v>122289592</v>
       </c>
       <c r="B268" t="n">
         <v>57383</v>
@@ -28313,7 +28293,7 @@
       <c r="I268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -28322,10 +28302,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>473021</v>
+        <v>473038</v>
       </c>
       <c r="R268" t="n">
-        <v>6815478</v>
+        <v>6815393</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28384,7 +28364,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122289587</v>
+        <v>122289586</v>
       </c>
       <c r="B269" t="n">
         <v>57383</v>
@@ -28429,10 +28409,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>473000</v>
+        <v>473036</v>
       </c>
       <c r="R269" t="n">
-        <v>6815184</v>
+        <v>6815173</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28496,10 +28476,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122289601</v>
+        <v>122289537</v>
       </c>
       <c r="B270" t="n">
-        <v>78393</v>
+        <v>57383</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28512,34 +28492,39 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>472894</v>
+        <v>472724</v>
       </c>
       <c r="R270" t="n">
-        <v>6815448</v>
+        <v>6815093</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28598,10 +28583,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122289529</v>
+        <v>122289533</v>
       </c>
       <c r="B271" t="n">
-        <v>79245</v>
+        <v>57383</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28614,34 +28599,39 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>472881</v>
+        <v>473021</v>
       </c>
       <c r="R271" t="n">
-        <v>6815396</v>
+        <v>6815478</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28700,10 +28690,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122289698</v>
+        <v>122289587</v>
       </c>
       <c r="B272" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28716,34 +28706,39 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>473037</v>
+        <v>473000</v>
       </c>
       <c r="R272" t="n">
-        <v>6815086</v>
+        <v>6815184</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28776,6 +28771,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -28802,10 +28802,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122289717</v>
+        <v>122289601</v>
       </c>
       <c r="B273" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28818,21 +28818,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28842,10 +28842,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>472949</v>
+        <v>472894</v>
       </c>
       <c r="R273" t="n">
-        <v>6815365</v>
+        <v>6815448</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28904,10 +28904,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122289680</v>
+        <v>122289529</v>
       </c>
       <c r="B274" t="n">
-        <v>78656</v>
+        <v>79245</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28920,21 +28920,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28944,10 +28944,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>472808</v>
+        <v>472881</v>
       </c>
       <c r="R274" t="n">
-        <v>6815067</v>
+        <v>6815396</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122289615</v>
+        <v>122289513</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>78691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,39 +1044,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472712</v>
+        <v>472966</v>
       </c>
       <c r="R5" t="n">
-        <v>6815141</v>
+        <v>6815390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,11 +1104,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122289588</v>
+        <v>122289615</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1176,7 +1166,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472971</v>
+        <v>472712</v>
       </c>
       <c r="R6" t="n">
-        <v>6815298</v>
+        <v>6815141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122289513</v>
+        <v>122289588</v>
       </c>
       <c r="B7" t="n">
-        <v>78691</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472966</v>
+        <v>472971</v>
       </c>
       <c r="R7" t="n">
-        <v>6815390</v>
+        <v>6815298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,6 +1323,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2374,10 +2374,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122289533</v>
+        <v>122289594</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>74753</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2390,39 +2390,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473021</v>
+        <v>472834</v>
       </c>
       <c r="R18" t="n">
-        <v>6815478</v>
+        <v>6815612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122289555</v>
+        <v>122289682</v>
       </c>
       <c r="B19" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,39 +2492,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473055</v>
+        <v>472846</v>
       </c>
       <c r="R19" t="n">
-        <v>6815710</v>
+        <v>6815101</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,11 +2552,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,10 +2578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122289535</v>
+        <v>122289748</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,39 +2594,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472732</v>
+        <v>473217</v>
       </c>
       <c r="R20" t="n">
-        <v>6815380</v>
+        <v>6815515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,7 +2680,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122289661</v>
+        <v>122289655</v>
       </c>
       <c r="B21" t="n">
         <v>78657</v>
@@ -2740,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472693</v>
+        <v>472766</v>
       </c>
       <c r="R21" t="n">
-        <v>6815202</v>
+        <v>6815363</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2782,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122289649</v>
+        <v>122289679</v>
       </c>
       <c r="B22" t="n">
         <v>78657</v>
@@ -2842,10 +2822,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472853</v>
+        <v>472779</v>
       </c>
       <c r="R22" t="n">
-        <v>6815291</v>
+        <v>6815051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,10 +2884,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122289682</v>
+        <v>122289477</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2920,21 +2900,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2944,10 +2924,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472846</v>
+        <v>472716</v>
       </c>
       <c r="R23" t="n">
-        <v>6815101</v>
+        <v>6815299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,10 +2986,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122289645</v>
+        <v>122289483</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3022,21 +3002,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3046,10 +3026,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472889</v>
+        <v>472999</v>
       </c>
       <c r="R24" t="n">
-        <v>6815359</v>
+        <v>6815197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3088,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122289621</v>
+        <v>122289656</v>
       </c>
       <c r="B25" t="n">
         <v>78657</v>
@@ -3148,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473076</v>
+        <v>472748</v>
       </c>
       <c r="R25" t="n">
-        <v>6815660</v>
+        <v>6815374</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,10 +3190,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122289748</v>
+        <v>122289550</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>79739</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3226,21 +3206,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3250,10 +3230,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473217</v>
+        <v>473037</v>
       </c>
       <c r="R26" t="n">
-        <v>6815515</v>
+        <v>6815182</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,10 +3292,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122289655</v>
+        <v>122289533</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3328,34 +3308,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472766</v>
+        <v>473021</v>
       </c>
       <c r="R27" t="n">
-        <v>6815363</v>
+        <v>6815478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3414,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122289679</v>
+        <v>122289555</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3430,34 +3415,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472779</v>
+        <v>473055</v>
       </c>
       <c r="R28" t="n">
-        <v>6815051</v>
+        <v>6815710</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3490,6 +3480,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3516,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122289477</v>
+        <v>122289535</v>
       </c>
       <c r="B29" t="n">
-        <v>79275</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3532,34 +3527,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472716</v>
+        <v>472732</v>
       </c>
       <c r="R29" t="n">
-        <v>6815299</v>
+        <v>6815380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289483</v>
+        <v>122289661</v>
       </c>
       <c r="B30" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472999</v>
+        <v>472693</v>
       </c>
       <c r="R30" t="n">
-        <v>6815197</v>
+        <v>6815202</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289656</v>
+        <v>122289649</v>
       </c>
       <c r="B31" t="n">
         <v>78657</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472748</v>
+        <v>472853</v>
       </c>
       <c r="R31" t="n">
-        <v>6815374</v>
+        <v>6815291</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122289594</v>
+        <v>122289645</v>
       </c>
       <c r="B32" t="n">
-        <v>74753</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472834</v>
+        <v>472889</v>
       </c>
       <c r="R32" t="n">
-        <v>6815612</v>
+        <v>6815359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122289550</v>
+        <v>122289621</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473037</v>
+        <v>473076</v>
       </c>
       <c r="R33" t="n">
-        <v>6815182</v>
+        <v>6815660</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -9721,10 +9721,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122289547</v>
+        <v>122289563</v>
       </c>
       <c r="B89" t="n">
-        <v>79739</v>
+        <v>57384</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9737,34 +9737,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>472833</v>
+        <v>472874</v>
       </c>
       <c r="R89" t="n">
-        <v>6815619</v>
+        <v>6815282</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9797,6 +9802,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9823,10 +9833,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122289481</v>
+        <v>122289570</v>
       </c>
       <c r="B90" t="n">
-        <v>79275</v>
+        <v>57384</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9839,34 +9849,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>472871</v>
+        <v>473034</v>
       </c>
       <c r="R90" t="n">
-        <v>6815157</v>
+        <v>6815167</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9899,6 +9914,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9925,7 +9945,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122289563</v>
+        <v>122289559</v>
       </c>
       <c r="B91" t="n">
         <v>57384</v>
@@ -9970,10 +9990,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>472874</v>
+        <v>472934</v>
       </c>
       <c r="R91" t="n">
-        <v>6815282</v>
+        <v>6815651</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10037,10 +10057,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122289570</v>
+        <v>122289547</v>
       </c>
       <c r="B92" t="n">
-        <v>57384</v>
+        <v>79739</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10053,39 +10073,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>473034</v>
+        <v>472833</v>
       </c>
       <c r="R92" t="n">
-        <v>6815167</v>
+        <v>6815619</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10118,11 +10133,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10149,10 +10159,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122289559</v>
+        <v>122289636</v>
       </c>
       <c r="B93" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10165,39 +10175,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>472934</v>
+        <v>472843</v>
       </c>
       <c r="R93" t="n">
-        <v>6815651</v>
+        <v>6815598</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10230,11 +10235,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10261,7 +10261,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122289636</v>
+        <v>122289670</v>
       </c>
       <c r="B94" t="n">
         <v>78657</v>
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>472843</v>
+        <v>472698</v>
       </c>
       <c r="R94" t="n">
-        <v>6815598</v>
+        <v>6815034</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10363,10 +10363,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122289670</v>
+        <v>122289481</v>
       </c>
       <c r="B95" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>472698</v>
+        <v>472871</v>
       </c>
       <c r="R95" t="n">
-        <v>6815034</v>
+        <v>6815157</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13575,10 +13575,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122289501</v>
+        <v>122289568</v>
       </c>
       <c r="B126" t="n">
-        <v>78691</v>
+        <v>57384</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13591,34 +13591,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>472722</v>
+        <v>472863</v>
       </c>
       <c r="R126" t="n">
-        <v>6815373</v>
+        <v>6815149</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13651,6 +13656,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13677,10 +13687,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122289509</v>
+        <v>122289540</v>
       </c>
       <c r="B127" t="n">
-        <v>78691</v>
+        <v>57537</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13693,21 +13703,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13717,10 +13727,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>473014</v>
+        <v>473035</v>
       </c>
       <c r="R127" t="n">
-        <v>6815194</v>
+        <v>6815416</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13779,10 +13789,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122289568</v>
+        <v>122289501</v>
       </c>
       <c r="B128" t="n">
-        <v>57384</v>
+        <v>78691</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13795,39 +13805,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>472863</v>
+        <v>472722</v>
       </c>
       <c r="R128" t="n">
-        <v>6815149</v>
+        <v>6815373</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13860,11 +13865,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13891,10 +13891,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122289632</v>
+        <v>122289509</v>
       </c>
       <c r="B129" t="n">
-        <v>78657</v>
+        <v>78691</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13907,21 +13907,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13931,10 +13931,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>472754</v>
+        <v>473014</v>
       </c>
       <c r="R129" t="n">
-        <v>6815718</v>
+        <v>6815194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122289625</v>
+        <v>122289632</v>
       </c>
       <c r="B130" t="n">
         <v>78657</v>
@@ -14033,10 +14033,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>472874</v>
+        <v>472754</v>
       </c>
       <c r="R130" t="n">
-        <v>6815658</v>
+        <v>6815718</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14095,7 +14095,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122289740</v>
+        <v>122289625</v>
       </c>
       <c r="B131" t="n">
         <v>78657</v>
@@ -14135,10 +14135,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>473153</v>
+        <v>472874</v>
       </c>
       <c r="R131" t="n">
-        <v>6815381</v>
+        <v>6815658</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122289474</v>
+        <v>122289740</v>
       </c>
       <c r="B132" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14213,21 +14213,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14237,10 +14237,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>473224</v>
+        <v>473153</v>
       </c>
       <c r="R132" t="n">
-        <v>6815618</v>
+        <v>6815381</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14299,10 +14299,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122289727</v>
+        <v>122289474</v>
       </c>
       <c r="B133" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14315,21 +14315,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>472922</v>
+        <v>473224</v>
       </c>
       <c r="R133" t="n">
-        <v>6815393</v>
+        <v>6815618</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14401,7 +14401,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122289698</v>
+        <v>122289727</v>
       </c>
       <c r="B134" t="n">
         <v>78657</v>
@@ -14441,10 +14441,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>473037</v>
+        <v>472922</v>
       </c>
       <c r="R134" t="n">
-        <v>6815086</v>
+        <v>6815393</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14503,7 +14503,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122289691</v>
+        <v>122289698</v>
       </c>
       <c r="B135" t="n">
         <v>78657</v>
@@ -14543,10 +14543,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>472974</v>
+        <v>473037</v>
       </c>
       <c r="R135" t="n">
-        <v>6815012</v>
+        <v>6815086</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14605,7 +14605,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122289690</v>
+        <v>122289691</v>
       </c>
       <c r="B136" t="n">
         <v>78657</v>
@@ -14645,10 +14645,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>472957</v>
+        <v>472974</v>
       </c>
       <c r="R136" t="n">
-        <v>6815023</v>
+        <v>6815012</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14707,7 +14707,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122289634</v>
+        <v>122289690</v>
       </c>
       <c r="B137" t="n">
         <v>78657</v>
@@ -14747,10 +14747,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>472785</v>
+        <v>472957</v>
       </c>
       <c r="R137" t="n">
-        <v>6815675</v>
+        <v>6815023</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14809,7 +14809,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122289643</v>
+        <v>122289634</v>
       </c>
       <c r="B138" t="n">
         <v>78657</v>
@@ -14849,10 +14849,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>472856</v>
+        <v>472785</v>
       </c>
       <c r="R138" t="n">
-        <v>6815448</v>
+        <v>6815675</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14911,7 +14911,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122289739</v>
+        <v>122289643</v>
       </c>
       <c r="B139" t="n">
         <v>78657</v>
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>473062</v>
+        <v>472856</v>
       </c>
       <c r="R139" t="n">
-        <v>6815374</v>
+        <v>6815448</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15013,7 +15013,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122289623</v>
+        <v>122289739</v>
       </c>
       <c r="B140" t="n">
         <v>78657</v>
@@ -15053,10 +15053,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>472922</v>
+        <v>473062</v>
       </c>
       <c r="R140" t="n">
-        <v>6815653</v>
+        <v>6815374</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15115,7 +15115,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122289745</v>
+        <v>122289623</v>
       </c>
       <c r="B141" t="n">
         <v>78657</v>
@@ -15155,10 +15155,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>473190</v>
+        <v>472922</v>
       </c>
       <c r="R141" t="n">
-        <v>6815498</v>
+        <v>6815653</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15217,7 +15217,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122289669</v>
+        <v>122289745</v>
       </c>
       <c r="B142" t="n">
         <v>78657</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>472718</v>
+        <v>473190</v>
       </c>
       <c r="R142" t="n">
-        <v>6815041</v>
+        <v>6815498</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15319,10 +15319,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122289540</v>
+        <v>122289669</v>
       </c>
       <c r="B143" t="n">
-        <v>57537</v>
+        <v>78657</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>473035</v>
+        <v>472718</v>
       </c>
       <c r="R143" t="n">
-        <v>6815416</v>
+        <v>6815041</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -20895,10 +20895,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122289524</v>
+        <v>122289562</v>
       </c>
       <c r="B197" t="n">
-        <v>78691</v>
+        <v>57384</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20911,34 +20911,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>473242</v>
+        <v>472869</v>
       </c>
       <c r="R197" t="n">
-        <v>6815724</v>
+        <v>6815446</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20971,6 +20976,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20997,10 +21007,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122289697</v>
+        <v>122289584</v>
       </c>
       <c r="B198" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21013,34 +21023,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>473033</v>
+        <v>473037</v>
       </c>
       <c r="R198" t="n">
-        <v>6815058</v>
+        <v>6815020</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21073,6 +21088,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21099,7 +21119,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122289756</v>
+        <v>122289697</v>
       </c>
       <c r="B199" t="n">
         <v>78657</v>
@@ -21139,10 +21159,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>473239</v>
+        <v>473033</v>
       </c>
       <c r="R199" t="n">
-        <v>6815673</v>
+        <v>6815058</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21201,7 +21221,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122289749</v>
+        <v>122289702</v>
       </c>
       <c r="B200" t="n">
         <v>78657</v>
@@ -21241,10 +21261,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>473236</v>
+        <v>473044</v>
       </c>
       <c r="R200" t="n">
-        <v>6815526</v>
+        <v>6815169</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21303,7 +21323,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122289718</v>
+        <v>122289756</v>
       </c>
       <c r="B201" t="n">
         <v>78657</v>
@@ -21343,10 +21363,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>472942</v>
+        <v>473239</v>
       </c>
       <c r="R201" t="n">
-        <v>6815355</v>
+        <v>6815673</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21405,7 +21425,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122289710</v>
+        <v>122289749</v>
       </c>
       <c r="B202" t="n">
         <v>78657</v>
@@ -21445,10 +21465,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>472998</v>
+        <v>473236</v>
       </c>
       <c r="R202" t="n">
-        <v>6815243</v>
+        <v>6815526</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21507,7 +21527,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122289750</v>
+        <v>122289718</v>
       </c>
       <c r="B203" t="n">
         <v>78657</v>
@@ -21547,10 +21567,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>473232</v>
+        <v>472942</v>
       </c>
       <c r="R203" t="n">
-        <v>6815538</v>
+        <v>6815355</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21609,7 +21629,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122289633</v>
+        <v>122289710</v>
       </c>
       <c r="B204" t="n">
         <v>78657</v>
@@ -21649,10 +21669,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>472766</v>
+        <v>472998</v>
       </c>
       <c r="R204" t="n">
-        <v>6815686</v>
+        <v>6815243</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21711,7 +21731,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122289705</v>
+        <v>122289750</v>
       </c>
       <c r="B205" t="n">
         <v>78657</v>
@@ -21751,10 +21771,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>473019</v>
+        <v>473232</v>
       </c>
       <c r="R205" t="n">
-        <v>6815163</v>
+        <v>6815538</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21813,7 +21833,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122289734</v>
+        <v>122289633</v>
       </c>
       <c r="B206" t="n">
         <v>78657</v>
@@ -21853,10 +21873,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>473018</v>
+        <v>472766</v>
       </c>
       <c r="R206" t="n">
-        <v>6815464</v>
+        <v>6815686</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21915,7 +21935,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122289741</v>
+        <v>122289705</v>
       </c>
       <c r="B207" t="n">
         <v>78657</v>
@@ -21955,10 +21975,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>473161</v>
+        <v>473019</v>
       </c>
       <c r="R207" t="n">
-        <v>6815418</v>
+        <v>6815163</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22017,7 +22037,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122289626</v>
+        <v>122289734</v>
       </c>
       <c r="B208" t="n">
         <v>78657</v>
@@ -22057,10 +22077,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>472855</v>
+        <v>473018</v>
       </c>
       <c r="R208" t="n">
-        <v>6815671</v>
+        <v>6815464</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22119,10 +22139,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122289562</v>
+        <v>122289741</v>
       </c>
       <c r="B209" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22135,39 +22155,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>472869</v>
+        <v>473161</v>
       </c>
       <c r="R209" t="n">
-        <v>6815446</v>
+        <v>6815418</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22200,11 +22215,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22231,10 +22241,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122289584</v>
+        <v>122289626</v>
       </c>
       <c r="B210" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22247,39 +22257,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>473037</v>
+        <v>472855</v>
       </c>
       <c r="R210" t="n">
-        <v>6815020</v>
+        <v>6815671</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22312,11 +22317,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22343,10 +22343,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289702</v>
+        <v>122289524</v>
       </c>
       <c r="B211" t="n">
-        <v>78657</v>
+        <v>78691</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22359,21 +22359,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22383,10 +22383,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>473044</v>
+        <v>473242</v>
       </c>
       <c r="R211" t="n">
-        <v>6815169</v>
+        <v>6815724</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22445,10 +22445,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289523</v>
+        <v>122289771</v>
       </c>
       <c r="B212" t="n">
-        <v>78691</v>
+        <v>78302</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22461,21 +22461,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22485,10 +22485,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>473251</v>
+        <v>473227</v>
       </c>
       <c r="R212" t="n">
-        <v>6815667</v>
+        <v>6815737</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22547,10 +22547,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289771</v>
+        <v>122289703</v>
       </c>
       <c r="B213" t="n">
-        <v>78302</v>
+        <v>78657</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22563,21 +22563,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22587,10 +22587,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>473227</v>
+        <v>473050</v>
       </c>
       <c r="R213" t="n">
-        <v>6815737</v>
+        <v>6815176</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22649,10 +22649,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289586</v>
+        <v>122289673</v>
       </c>
       <c r="B214" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22665,39 +22665,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>473036</v>
+        <v>472729</v>
       </c>
       <c r="R214" t="n">
-        <v>6815173</v>
+        <v>6815062</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22730,11 +22725,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22761,10 +22751,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289537</v>
+        <v>122289629</v>
       </c>
       <c r="B215" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22777,39 +22767,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>472724</v>
+        <v>472833</v>
       </c>
       <c r="R215" t="n">
-        <v>6815093</v>
+        <v>6815744</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22868,10 +22853,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289590</v>
+        <v>122289721</v>
       </c>
       <c r="B216" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22884,39 +22869,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>472945</v>
+        <v>472897</v>
       </c>
       <c r="R216" t="n">
-        <v>6815381</v>
+        <v>6815355</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22949,11 +22929,6 @@
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -22980,10 +22955,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289703</v>
+        <v>122289601</v>
       </c>
       <c r="B217" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22996,21 +22971,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23020,10 +22995,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>473050</v>
+        <v>472894</v>
       </c>
       <c r="R217" t="n">
-        <v>6815176</v>
+        <v>6815448</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23082,10 +23057,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122289673</v>
+        <v>122289603</v>
       </c>
       <c r="B218" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23098,21 +23073,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23122,10 +23097,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>472729</v>
+        <v>472794</v>
       </c>
       <c r="R218" t="n">
-        <v>6815062</v>
+        <v>6815363</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23184,10 +23159,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289629</v>
+        <v>122289523</v>
       </c>
       <c r="B219" t="n">
-        <v>78657</v>
+        <v>78691</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23200,21 +23175,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23224,10 +23199,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>472833</v>
+        <v>473251</v>
       </c>
       <c r="R219" t="n">
-        <v>6815744</v>
+        <v>6815667</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23286,10 +23261,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289721</v>
+        <v>122289586</v>
       </c>
       <c r="B220" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23302,34 +23277,39 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>472897</v>
+        <v>473036</v>
       </c>
       <c r="R220" t="n">
-        <v>6815355</v>
+        <v>6815173</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23362,6 +23342,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23388,10 +23373,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289601</v>
+        <v>122289537</v>
       </c>
       <c r="B221" t="n">
-        <v>78394</v>
+        <v>57384</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23404,34 +23389,39 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>472894</v>
+        <v>472724</v>
       </c>
       <c r="R221" t="n">
-        <v>6815448</v>
+        <v>6815093</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23490,10 +23480,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289603</v>
+        <v>122289590</v>
       </c>
       <c r="B222" t="n">
-        <v>78394</v>
+        <v>57384</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23506,34 +23496,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>472794</v>
+        <v>472945</v>
       </c>
       <c r="R222" t="n">
-        <v>6815363</v>
+        <v>6815381</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23566,6 +23561,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23592,10 +23592,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289723</v>
+        <v>122289548</v>
       </c>
       <c r="B223" t="n">
-        <v>78657</v>
+        <v>79739</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23608,21 +23608,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23632,10 +23632,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>472901</v>
+        <v>472848</v>
       </c>
       <c r="R223" t="n">
-        <v>6815361</v>
+        <v>6815573</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23694,10 +23694,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122289485</v>
+        <v>122289587</v>
       </c>
       <c r="B224" t="n">
-        <v>79275</v>
+        <v>57384</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23710,34 +23710,39 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>473014</v>
+        <v>473000</v>
       </c>
       <c r="R224" t="n">
-        <v>6815496</v>
+        <v>6815184</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23770,6 +23775,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23796,10 +23806,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122289624</v>
+        <v>122289538</v>
       </c>
       <c r="B225" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23812,21 +23822,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23836,10 +23846,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>472913</v>
+        <v>472787</v>
       </c>
       <c r="R225" t="n">
-        <v>6815662</v>
+        <v>6815675</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23898,10 +23908,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122289650</v>
+        <v>122289532</v>
       </c>
       <c r="B226" t="n">
-        <v>78657</v>
+        <v>79246</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23914,21 +23924,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23938,10 +23948,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>472845</v>
+        <v>473191</v>
       </c>
       <c r="R226" t="n">
-        <v>6815328</v>
+        <v>6815504</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24000,10 +24010,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122289714</v>
+        <v>122289600</v>
       </c>
       <c r="B227" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24016,21 +24026,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24040,10 +24050,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>472966</v>
+        <v>472822</v>
       </c>
       <c r="R227" t="n">
-        <v>6815345</v>
+        <v>6815541</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24102,7 +24112,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122289744</v>
+        <v>122289723</v>
       </c>
       <c r="B228" t="n">
         <v>78657</v>
@@ -24142,10 +24152,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>473188</v>
+        <v>472901</v>
       </c>
       <c r="R228" t="n">
-        <v>6815489</v>
+        <v>6815361</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24204,10 +24214,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122289616</v>
+        <v>122289485</v>
       </c>
       <c r="B229" t="n">
-        <v>90852</v>
+        <v>79275</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24220,21 +24230,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24244,10 +24254,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>473244</v>
+        <v>473014</v>
       </c>
       <c r="R229" t="n">
-        <v>6815667</v>
+        <v>6815496</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24306,7 +24316,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122289657</v>
+        <v>122289624</v>
       </c>
       <c r="B230" t="n">
         <v>78657</v>
@@ -24346,10 +24356,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>472730</v>
+        <v>472913</v>
       </c>
       <c r="R230" t="n">
-        <v>6815383</v>
+        <v>6815662</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24408,10 +24418,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>122289532</v>
+        <v>122289650</v>
       </c>
       <c r="B231" t="n">
-        <v>79246</v>
+        <v>78657</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24424,21 +24434,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24448,10 +24458,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>473191</v>
+        <v>472845</v>
       </c>
       <c r="R231" t="n">
-        <v>6815504</v>
+        <v>6815328</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24510,10 +24520,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>122289600</v>
+        <v>122289714</v>
       </c>
       <c r="B232" t="n">
-        <v>78394</v>
+        <v>78657</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24526,21 +24536,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24550,10 +24560,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>472822</v>
+        <v>472966</v>
       </c>
       <c r="R232" t="n">
-        <v>6815541</v>
+        <v>6815345</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24612,10 +24622,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>122289548</v>
+        <v>122289744</v>
       </c>
       <c r="B233" t="n">
-        <v>79739</v>
+        <v>78657</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24628,21 +24638,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24652,10 +24662,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>472848</v>
+        <v>473188</v>
       </c>
       <c r="R233" t="n">
-        <v>6815573</v>
+        <v>6815489</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24714,10 +24724,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>122289587</v>
+        <v>122289616</v>
       </c>
       <c r="B234" t="n">
-        <v>57384</v>
+        <v>90852</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24730,39 +24740,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>473000</v>
+        <v>473244</v>
       </c>
       <c r="R234" t="n">
-        <v>6815184</v>
+        <v>6815667</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24795,11 +24800,6 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24826,10 +24826,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>122289538</v>
+        <v>122289657</v>
       </c>
       <c r="B235" t="n">
-        <v>57537</v>
+        <v>78657</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24842,21 +24842,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24866,10 +24866,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>472787</v>
+        <v>472730</v>
       </c>
       <c r="R235" t="n">
-        <v>6815675</v>
+        <v>6815383</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25662,10 +25662,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122289549</v>
+        <v>122289772</v>
       </c>
       <c r="B243" t="n">
-        <v>79739</v>
+        <v>78041</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25678,21 +25678,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25702,10 +25702,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>472766</v>
+        <v>473001</v>
       </c>
       <c r="R243" t="n">
-        <v>6815366</v>
+        <v>6815720</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25764,10 +25764,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122289596</v>
+        <v>122289641</v>
       </c>
       <c r="B244" t="n">
-        <v>78394</v>
+        <v>78657</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25780,21 +25780,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25804,10 +25804,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>473223</v>
+        <v>472882</v>
       </c>
       <c r="R244" t="n">
-        <v>6815621</v>
+        <v>6815476</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25866,10 +25866,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122289519</v>
+        <v>122289689</v>
       </c>
       <c r="B245" t="n">
-        <v>78691</v>
+        <v>78657</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25882,21 +25882,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25906,10 +25906,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>473217</v>
+        <v>472954</v>
       </c>
       <c r="R245" t="n">
-        <v>6815515</v>
+        <v>6815041</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25968,10 +25968,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122289546</v>
+        <v>122289706</v>
       </c>
       <c r="B246" t="n">
-        <v>57400</v>
+        <v>78657</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25984,39 +25984,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>472731</v>
+        <v>473015</v>
       </c>
       <c r="R246" t="n">
-        <v>6815088</v>
+        <v>6815193</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26075,10 +26070,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122289553</v>
+        <v>122289768</v>
       </c>
       <c r="B247" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -26091,39 +26086,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>472880</v>
+        <v>472877</v>
       </c>
       <c r="R247" t="n">
-        <v>6815136</v>
+        <v>6815103</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26156,11 +26146,6 @@
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26187,10 +26172,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122289569</v>
+        <v>122289628</v>
       </c>
       <c r="B248" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26203,39 +26188,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>473043</v>
+        <v>472851</v>
       </c>
       <c r="R248" t="n">
-        <v>6815180</v>
+        <v>6815729</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26268,11 +26248,6 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26299,10 +26274,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122289772</v>
+        <v>122289622</v>
       </c>
       <c r="B249" t="n">
-        <v>78041</v>
+        <v>78657</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26315,21 +26290,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -26339,10 +26314,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>473001</v>
+        <v>472955</v>
       </c>
       <c r="R249" t="n">
-        <v>6815720</v>
+        <v>6815658</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26401,10 +26376,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122289641</v>
+        <v>122289519</v>
       </c>
       <c r="B250" t="n">
-        <v>78657</v>
+        <v>78691</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26417,21 +26392,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26441,10 +26416,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>472882</v>
+        <v>473217</v>
       </c>
       <c r="R250" t="n">
-        <v>6815476</v>
+        <v>6815515</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26503,10 +26478,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122289689</v>
+        <v>122289549</v>
       </c>
       <c r="B251" t="n">
-        <v>78657</v>
+        <v>79739</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26519,21 +26494,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26543,10 +26518,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>472954</v>
+        <v>472766</v>
       </c>
       <c r="R251" t="n">
-        <v>6815041</v>
+        <v>6815366</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26605,10 +26580,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122289706</v>
+        <v>122289546</v>
       </c>
       <c r="B252" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26621,34 +26596,39 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>473015</v>
+        <v>472731</v>
       </c>
       <c r="R252" t="n">
-        <v>6815193</v>
+        <v>6815088</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26707,10 +26687,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289768</v>
+        <v>122289553</v>
       </c>
       <c r="B253" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26723,34 +26703,39 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>472877</v>
+        <v>472880</v>
       </c>
       <c r="R253" t="n">
-        <v>6815103</v>
+        <v>6815136</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26783,6 +26768,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26809,10 +26799,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289628</v>
+        <v>122289569</v>
       </c>
       <c r="B254" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26825,34 +26815,39 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>472851</v>
+        <v>473043</v>
       </c>
       <c r="R254" t="n">
-        <v>6815729</v>
+        <v>6815180</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26885,6 +26880,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26911,10 +26911,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289622</v>
+        <v>122289596</v>
       </c>
       <c r="B255" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26927,21 +26927,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26951,10 +26951,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>472955</v>
+        <v>473223</v>
       </c>
       <c r="R255" t="n">
-        <v>6815658</v>
+        <v>6815621</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27013,10 +27013,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289696</v>
+        <v>122289558</v>
       </c>
       <c r="B256" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27029,34 +27029,39 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>473033</v>
+        <v>472954</v>
       </c>
       <c r="R256" t="n">
-        <v>6815029</v>
+        <v>6815040</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27089,6 +27094,11 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27115,10 +27125,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289638</v>
+        <v>122289592</v>
       </c>
       <c r="B257" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27131,34 +27141,39 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>472871</v>
+        <v>473038</v>
       </c>
       <c r="R257" t="n">
-        <v>6815512</v>
+        <v>6815393</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27217,10 +27232,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289753</v>
+        <v>122289769</v>
       </c>
       <c r="B258" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27233,34 +27248,39 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>473242</v>
+        <v>472842</v>
       </c>
       <c r="R258" t="n">
-        <v>6815602</v>
+        <v>6815605</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27293,6 +27313,11 @@
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27319,10 +27344,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289619</v>
+        <v>122289579</v>
       </c>
       <c r="B259" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27335,34 +27360,39 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>473228</v>
+        <v>472828</v>
       </c>
       <c r="R259" t="n">
-        <v>6815569</v>
+        <v>6815624</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27395,6 +27425,11 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27421,10 +27456,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122289751</v>
+        <v>122289566</v>
       </c>
       <c r="B260" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27437,34 +27472,39 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>473230</v>
+        <v>472846</v>
       </c>
       <c r="R260" t="n">
-        <v>6815539</v>
+        <v>6815099</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27497,6 +27537,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27523,10 +27568,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122289484</v>
+        <v>122289608</v>
       </c>
       <c r="B261" t="n">
-        <v>79275</v>
+        <v>78394</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27539,21 +27584,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27563,10 +27608,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>472950</v>
+        <v>472951</v>
       </c>
       <c r="R261" t="n">
-        <v>6815417</v>
+        <v>6815418</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27625,7 +27670,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122289731</v>
+        <v>122289696</v>
       </c>
       <c r="B262" t="n">
         <v>78657</v>
@@ -27665,10 +27710,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>472971</v>
+        <v>473033</v>
       </c>
       <c r="R262" t="n">
-        <v>6815445</v>
+        <v>6815029</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27727,10 +27772,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122289551</v>
+        <v>122289638</v>
       </c>
       <c r="B263" t="n">
-        <v>79642</v>
+        <v>78657</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27739,25 +27784,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -27767,10 +27812,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>472884</v>
+        <v>472871</v>
       </c>
       <c r="R263" t="n">
-        <v>6815478</v>
+        <v>6815512</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27829,7 +27874,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122289659</v>
+        <v>122289753</v>
       </c>
       <c r="B264" t="n">
         <v>78657</v>
@@ -27869,10 +27914,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>472724</v>
+        <v>473242</v>
       </c>
       <c r="R264" t="n">
-        <v>6815345</v>
+        <v>6815602</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27931,10 +27976,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122289558</v>
+        <v>122289619</v>
       </c>
       <c r="B265" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27947,39 +27992,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>472954</v>
+        <v>473228</v>
       </c>
       <c r="R265" t="n">
-        <v>6815040</v>
+        <v>6815569</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28012,11 +28052,6 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28043,10 +28078,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122289592</v>
+        <v>122289751</v>
       </c>
       <c r="B266" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -28059,39 +28094,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>473038</v>
+        <v>473230</v>
       </c>
       <c r="R266" t="n">
-        <v>6815393</v>
+        <v>6815539</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28150,10 +28180,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122289769</v>
+        <v>122289484</v>
       </c>
       <c r="B267" t="n">
-        <v>57384</v>
+        <v>79275</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28166,39 +28196,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>472842</v>
+        <v>472950</v>
       </c>
       <c r="R267" t="n">
-        <v>6815605</v>
+        <v>6815417</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28231,11 +28256,6 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28262,10 +28282,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122289579</v>
+        <v>122289731</v>
       </c>
       <c r="B268" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28278,39 +28298,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>472828</v>
+        <v>472971</v>
       </c>
       <c r="R268" t="n">
-        <v>6815624</v>
+        <v>6815445</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28343,11 +28358,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28374,10 +28384,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122289560</v>
+        <v>122289551</v>
       </c>
       <c r="B269" t="n">
-        <v>57384</v>
+        <v>79642</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28386,43 +28396,38 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>472880</v>
+        <v>472884</v>
       </c>
       <c r="R269" t="n">
-        <v>6815442</v>
+        <v>6815478</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28455,11 +28460,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28486,10 +28486,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122289566</v>
+        <v>122289659</v>
       </c>
       <c r="B270" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28502,39 +28502,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>472846</v>
+        <v>472724</v>
       </c>
       <c r="R270" t="n">
-        <v>6815099</v>
+        <v>6815345</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28567,11 +28562,6 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28598,10 +28588,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122289608</v>
+        <v>122289511</v>
       </c>
       <c r="B271" t="n">
-        <v>78394</v>
+        <v>78691</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28614,21 +28604,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28638,10 +28628,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>472951</v>
+        <v>472998</v>
       </c>
       <c r="R271" t="n">
-        <v>6815418</v>
+        <v>6815243</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28700,7 +28690,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122289511</v>
+        <v>122289514</v>
       </c>
       <c r="B272" t="n">
         <v>78691</v>
@@ -28740,10 +28730,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>472998</v>
+        <v>472965</v>
       </c>
       <c r="R272" t="n">
-        <v>6815243</v>
+        <v>6815434</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28802,7 +28792,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122289514</v>
+        <v>122289498</v>
       </c>
       <c r="B273" t="n">
         <v>78691</v>
@@ -28842,10 +28832,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>472965</v>
+        <v>472863</v>
       </c>
       <c r="R273" t="n">
-        <v>6815434</v>
+        <v>6815525</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28904,10 +28894,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122289498</v>
+        <v>122289560</v>
       </c>
       <c r="B274" t="n">
-        <v>78691</v>
+        <v>57384</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28920,34 +28910,39 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>472863</v>
+        <v>472880</v>
       </c>
       <c r="R274" t="n">
-        <v>6815525</v>
+        <v>6815442</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28980,6 +28975,11 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD274" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122289752</v>
+        <v>122289507</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473224</v>
+        <v>473043</v>
       </c>
       <c r="R5" t="n">
-        <v>6815578</v>
+        <v>6815153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122289756</v>
+        <v>122289525</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>95790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473239</v>
+        <v>472724</v>
       </c>
       <c r="R6" t="n">
-        <v>6815673</v>
+        <v>6815100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122289648</v>
+        <v>122289504</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472874</v>
+        <v>472835</v>
       </c>
       <c r="R7" t="n">
-        <v>6815282</v>
+        <v>6815089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122289631</v>
+        <v>122289587</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,34 +1350,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472746</v>
+        <v>473000</v>
       </c>
       <c r="R8" t="n">
-        <v>6815730</v>
+        <v>6815184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,6 +1415,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122289482</v>
+        <v>122289571</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,34 +1462,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472988</v>
+        <v>472895</v>
       </c>
       <c r="R9" t="n">
-        <v>6815002</v>
+        <v>6815359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,6 +1527,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122289653</v>
+        <v>122289590</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,34 +1574,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472794</v>
+        <v>472945</v>
       </c>
       <c r="R10" t="n">
-        <v>6815364</v>
+        <v>6815381</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1639,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,7 +1670,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122289754</v>
+        <v>122289752</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1680,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473240</v>
+        <v>473224</v>
       </c>
       <c r="R11" t="n">
-        <v>6815620</v>
+        <v>6815578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1772,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122289744</v>
+        <v>122289756</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1782,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473188</v>
+        <v>473239</v>
       </c>
       <c r="R12" t="n">
-        <v>6815489</v>
+        <v>6815673</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1874,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122289629</v>
+        <v>122289648</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1884,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472833</v>
+        <v>472874</v>
       </c>
       <c r="R13" t="n">
-        <v>6815744</v>
+        <v>6815282</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122289587</v>
+        <v>122289631</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,39 +1992,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473000</v>
+        <v>472746</v>
       </c>
       <c r="R14" t="n">
-        <v>6815184</v>
+        <v>6815730</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,11 +2052,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122289571</v>
+        <v>122289482</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>79278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,39 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472895</v>
+        <v>472988</v>
       </c>
       <c r="R15" t="n">
-        <v>6815359</v>
+        <v>6815002</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,11 +2154,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122289590</v>
+        <v>122289653</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,39 +2196,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472945</v>
+        <v>472794</v>
       </c>
       <c r="R16" t="n">
-        <v>6815381</v>
+        <v>6815364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,11 +2256,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122289601</v>
+        <v>122289754</v>
       </c>
       <c r="B17" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472894</v>
+        <v>473240</v>
       </c>
       <c r="R17" t="n">
-        <v>6815448</v>
+        <v>6815620</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122289529</v>
+        <v>122289744</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472881</v>
+        <v>473188</v>
       </c>
       <c r="R18" t="n">
-        <v>6815396</v>
+        <v>6815489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122289507</v>
+        <v>122289629</v>
       </c>
       <c r="B19" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473043</v>
+        <v>472833</v>
       </c>
       <c r="R19" t="n">
-        <v>6815153</v>
+        <v>6815744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122289525</v>
+        <v>122289601</v>
       </c>
       <c r="B20" t="n">
-        <v>95790</v>
+        <v>78397</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472724</v>
+        <v>472894</v>
       </c>
       <c r="R20" t="n">
-        <v>6815100</v>
+        <v>6815448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122289504</v>
+        <v>122289529</v>
       </c>
       <c r="B21" t="n">
-        <v>78694</v>
+        <v>79249</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472835</v>
+        <v>472881</v>
       </c>
       <c r="R21" t="n">
-        <v>6815089</v>
+        <v>6815396</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122289486</v>
+        <v>122289597</v>
       </c>
       <c r="B22" t="n">
-        <v>79278</v>
+        <v>78397</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,21 +2808,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473115</v>
+        <v>473041</v>
       </c>
       <c r="R22" t="n">
-        <v>6815359</v>
+        <v>6815720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122289710</v>
+        <v>122289486</v>
       </c>
       <c r="B23" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472998</v>
+        <v>473115</v>
       </c>
       <c r="R23" t="n">
-        <v>6815243</v>
+        <v>6815359</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122289495</v>
+        <v>122289710</v>
       </c>
       <c r="B24" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,21 +3012,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473212</v>
+        <v>472998</v>
       </c>
       <c r="R24" t="n">
-        <v>6815464</v>
+        <v>6815243</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122289494</v>
+        <v>122289495</v>
       </c>
       <c r="B25" t="n">
         <v>74761</v>
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473044</v>
+        <v>473212</v>
       </c>
       <c r="R25" t="n">
-        <v>6815169</v>
+        <v>6815464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122289490</v>
+        <v>122289494</v>
       </c>
       <c r="B26" t="n">
         <v>74761</v>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472713</v>
+        <v>473044</v>
       </c>
       <c r="R26" t="n">
-        <v>6815143</v>
+        <v>6815169</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,10 +3302,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122289627</v>
+        <v>122289490</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3318,21 +3318,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472837</v>
+        <v>472713</v>
       </c>
       <c r="R27" t="n">
-        <v>6815704</v>
+        <v>6815143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122289476</v>
+        <v>122289627</v>
       </c>
       <c r="B28" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472813</v>
+        <v>472837</v>
       </c>
       <c r="R28" t="n">
-        <v>6815369</v>
+        <v>6815704</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122289524</v>
+        <v>122289476</v>
       </c>
       <c r="B29" t="n">
-        <v>78694</v>
+        <v>79278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3522,21 +3522,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473242</v>
+        <v>472813</v>
       </c>
       <c r="R29" t="n">
-        <v>6815724</v>
+        <v>6815369</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289515</v>
+        <v>122289524</v>
       </c>
       <c r="B30" t="n">
         <v>78694</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473035</v>
+        <v>473242</v>
       </c>
       <c r="R30" t="n">
-        <v>6815416</v>
+        <v>6815724</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289597</v>
+        <v>122289515</v>
       </c>
       <c r="B31" t="n">
-        <v>78397</v>
+        <v>78694</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3726,21 +3726,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473041</v>
+        <v>473035</v>
       </c>
       <c r="R31" t="n">
-        <v>6815720</v>
+        <v>6815416</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -7198,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122289621</v>
+        <v>122289556</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7214,34 +7214,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473076</v>
+        <v>472995</v>
       </c>
       <c r="R65" t="n">
-        <v>6815660</v>
+        <v>6815217</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,6 +7279,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7300,10 +7310,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122289691</v>
+        <v>122289566</v>
       </c>
       <c r="B66" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7316,34 +7326,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472974</v>
+        <v>472846</v>
       </c>
       <c r="R66" t="n">
-        <v>6815012</v>
+        <v>6815099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7376,6 +7391,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,10 +7422,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122289643</v>
+        <v>122289603</v>
       </c>
       <c r="B67" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7418,21 +7438,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7442,10 +7462,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472856</v>
+        <v>472794</v>
       </c>
       <c r="R67" t="n">
-        <v>6815448</v>
+        <v>6815363</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7504,10 +7524,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122289551</v>
+        <v>122289621</v>
       </c>
       <c r="B68" t="n">
-        <v>79645</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7516,25 +7536,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7544,10 +7564,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472884</v>
+        <v>473076</v>
       </c>
       <c r="R68" t="n">
-        <v>6815478</v>
+        <v>6815660</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7606,10 +7626,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122289603</v>
+        <v>122289691</v>
       </c>
       <c r="B69" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7622,21 +7642,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7646,10 +7666,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472794</v>
+        <v>472974</v>
       </c>
       <c r="R69" t="n">
-        <v>6815363</v>
+        <v>6815012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7708,10 +7728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289556</v>
+        <v>122289643</v>
       </c>
       <c r="B70" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7724,39 +7744,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472995</v>
+        <v>472856</v>
       </c>
       <c r="R70" t="n">
-        <v>6815217</v>
+        <v>6815448</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7789,11 +7804,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7820,10 +7830,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289566</v>
+        <v>122289551</v>
       </c>
       <c r="B71" t="n">
-        <v>57384</v>
+        <v>79645</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7832,43 +7842,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472846</v>
+        <v>472884</v>
       </c>
       <c r="R71" t="n">
-        <v>6815099</v>
+        <v>6815478</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,11 +7906,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10721,10 +10721,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122289692</v>
+        <v>122289771</v>
       </c>
       <c r="B99" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10737,21 +10737,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>472970</v>
+        <v>473227</v>
       </c>
       <c r="R99" t="n">
-        <v>6814989</v>
+        <v>6815737</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10823,7 +10823,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122289689</v>
+        <v>122289692</v>
       </c>
       <c r="B100" t="n">
         <v>78660</v>
@@ -10863,10 +10863,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472954</v>
+        <v>472970</v>
       </c>
       <c r="R100" t="n">
-        <v>6815041</v>
+        <v>6814989</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10925,7 +10925,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122289737</v>
+        <v>122289689</v>
       </c>
       <c r="B101" t="n">
         <v>78660</v>
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>473035</v>
+        <v>472954</v>
       </c>
       <c r="R101" t="n">
-        <v>6815416</v>
+        <v>6815041</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11027,10 +11027,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122289481</v>
+        <v>122289737</v>
       </c>
       <c r="B102" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11043,21 +11043,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>472871</v>
+        <v>473035</v>
       </c>
       <c r="R102" t="n">
-        <v>6815157</v>
+        <v>6815416</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11129,10 +11129,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122289730</v>
+        <v>122289481</v>
       </c>
       <c r="B103" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11145,21 +11145,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11169,10 +11169,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472958</v>
+        <v>472871</v>
       </c>
       <c r="R103" t="n">
-        <v>6815427</v>
+        <v>6815157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122289650</v>
+        <v>122289730</v>
       </c>
       <c r="B104" t="n">
         <v>78660</v>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472845</v>
+        <v>472958</v>
       </c>
       <c r="R104" t="n">
-        <v>6815328</v>
+        <v>6815427</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11333,7 +11333,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122289718</v>
+        <v>122289650</v>
       </c>
       <c r="B105" t="n">
         <v>78660</v>
@@ -11373,10 +11373,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472942</v>
+        <v>472845</v>
       </c>
       <c r="R105" t="n">
-        <v>6815355</v>
+        <v>6815328</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122289774</v>
+        <v>122289718</v>
       </c>
       <c r="B106" t="n">
-        <v>78044</v>
+        <v>78660</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11451,21 +11451,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>473192</v>
+        <v>472942</v>
       </c>
       <c r="R106" t="n">
-        <v>6815503</v>
+        <v>6815355</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11537,10 +11537,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122289688</v>
+        <v>122289774</v>
       </c>
       <c r="B107" t="n">
-        <v>78660</v>
+        <v>78044</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11553,21 +11553,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11577,10 +11577,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>472911</v>
+        <v>473192</v>
       </c>
       <c r="R107" t="n">
-        <v>6815063</v>
+        <v>6815503</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11639,7 +11639,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122289642</v>
+        <v>122289688</v>
       </c>
       <c r="B108" t="n">
         <v>78660</v>
@@ -11679,10 +11679,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472875</v>
+        <v>472911</v>
       </c>
       <c r="R108" t="n">
-        <v>6815470</v>
+        <v>6815063</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11741,10 +11741,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122289771</v>
+        <v>122289642</v>
       </c>
       <c r="B109" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11757,21 +11757,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>473227</v>
+        <v>472875</v>
       </c>
       <c r="R109" t="n">
-        <v>6815737</v>
+        <v>6815470</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13630,10 +13630,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122289530</v>
+        <v>122289567</v>
       </c>
       <c r="B127" t="n">
-        <v>79249</v>
+        <v>57384</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13646,34 +13646,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>473042</v>
+        <v>472851</v>
       </c>
       <c r="R127" t="n">
-        <v>6815081</v>
+        <v>6815154</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13706,6 +13711,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13732,10 +13742,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122289772</v>
+        <v>122289563</v>
       </c>
       <c r="B128" t="n">
-        <v>78044</v>
+        <v>57384</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13748,34 +13758,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>473001</v>
+        <v>472874</v>
       </c>
       <c r="R128" t="n">
-        <v>6815720</v>
+        <v>6815282</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13808,6 +13823,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13834,10 +13854,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122289699</v>
+        <v>122289553</v>
       </c>
       <c r="B129" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13850,34 +13870,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>473050</v>
+        <v>472880</v>
       </c>
       <c r="R129" t="n">
-        <v>6815098</v>
+        <v>6815136</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13910,6 +13935,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13936,10 +13966,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122289698</v>
+        <v>122289559</v>
       </c>
       <c r="B130" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13952,34 +13982,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>473037</v>
+        <v>472934</v>
       </c>
       <c r="R130" t="n">
-        <v>6815086</v>
+        <v>6815651</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14012,6 +14047,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14038,10 +14078,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122289690</v>
+        <v>122289530</v>
       </c>
       <c r="B131" t="n">
-        <v>78660</v>
+        <v>79249</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14054,21 +14094,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14078,10 +14118,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>472957</v>
+        <v>473042</v>
       </c>
       <c r="R131" t="n">
-        <v>6815023</v>
+        <v>6815081</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14140,10 +14180,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122289644</v>
+        <v>122289772</v>
       </c>
       <c r="B132" t="n">
-        <v>78660</v>
+        <v>78044</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14156,21 +14196,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14180,10 +14220,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>472872</v>
+        <v>473001</v>
       </c>
       <c r="R132" t="n">
-        <v>6815410</v>
+        <v>6815720</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14242,7 +14282,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122289701</v>
+        <v>122289699</v>
       </c>
       <c r="B133" t="n">
         <v>78660</v>
@@ -14282,10 +14322,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>473043</v>
+        <v>473050</v>
       </c>
       <c r="R133" t="n">
-        <v>6815159</v>
+        <v>6815098</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14344,7 +14384,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122289652</v>
+        <v>122289698</v>
       </c>
       <c r="B134" t="n">
         <v>78660</v>
@@ -14384,10 +14424,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>472813</v>
+        <v>473037</v>
       </c>
       <c r="R134" t="n">
-        <v>6815369</v>
+        <v>6815086</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14446,7 +14486,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122289711</v>
+        <v>122289690</v>
       </c>
       <c r="B135" t="n">
         <v>78660</v>
@@ -14486,10 +14526,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>472976</v>
+        <v>472957</v>
       </c>
       <c r="R135" t="n">
-        <v>6815272</v>
+        <v>6815023</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14548,10 +14588,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122289567</v>
+        <v>122289644</v>
       </c>
       <c r="B136" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14564,39 +14604,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>472851</v>
+        <v>472872</v>
       </c>
       <c r="R136" t="n">
-        <v>6815154</v>
+        <v>6815410</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14629,11 +14664,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14660,10 +14690,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122289563</v>
+        <v>122289701</v>
       </c>
       <c r="B137" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14676,39 +14706,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>472874</v>
+        <v>473043</v>
       </c>
       <c r="R137" t="n">
-        <v>6815282</v>
+        <v>6815159</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14741,11 +14766,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14772,10 +14792,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122289553</v>
+        <v>122289652</v>
       </c>
       <c r="B138" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14788,39 +14808,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>472880</v>
+        <v>472813</v>
       </c>
       <c r="R138" t="n">
-        <v>6815136</v>
+        <v>6815369</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14853,11 +14868,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14884,10 +14894,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122289559</v>
+        <v>122289711</v>
       </c>
       <c r="B139" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14900,39 +14910,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>472934</v>
+        <v>472976</v>
       </c>
       <c r="R139" t="n">
-        <v>6815651</v>
+        <v>6815272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14965,11 +14970,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18432,10 +18432,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122289521</v>
+        <v>122289534</v>
       </c>
       <c r="B173" t="n">
-        <v>78694</v>
+        <v>57384</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18448,34 +18448,39 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>473236</v>
+        <v>472993</v>
       </c>
       <c r="R173" t="n">
-        <v>6815621</v>
+        <v>6814991</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18534,10 +18539,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122289531</v>
+        <v>122289560</v>
       </c>
       <c r="B174" t="n">
-        <v>79249</v>
+        <v>57384</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18550,34 +18555,39 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>473013</v>
+        <v>472880</v>
       </c>
       <c r="R174" t="n">
-        <v>6815498</v>
+        <v>6815442</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18610,6 +18620,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19452,10 +19467,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289534</v>
+        <v>122289521</v>
       </c>
       <c r="B183" t="n">
-        <v>57384</v>
+        <v>78694</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19468,39 +19483,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>472993</v>
+        <v>473236</v>
       </c>
       <c r="R183" t="n">
-        <v>6814991</v>
+        <v>6815621</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19559,10 +19569,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289560</v>
+        <v>122289531</v>
       </c>
       <c r="B184" t="n">
-        <v>57384</v>
+        <v>79249</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19575,39 +19585,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>472880</v>
+        <v>473013</v>
       </c>
       <c r="R184" t="n">
-        <v>6815442</v>
+        <v>6815498</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19640,11 +19645,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22373,10 +22373,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289696</v>
+        <v>122289502</v>
       </c>
       <c r="B211" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22389,21 +22389,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22413,10 +22413,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>473033</v>
+        <v>472693</v>
       </c>
       <c r="R211" t="n">
-        <v>6815029</v>
+        <v>6815202</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22475,10 +22475,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289747</v>
+        <v>122289503</v>
       </c>
       <c r="B212" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22491,21 +22491,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22515,10 +22515,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>473203</v>
+        <v>472704</v>
       </c>
       <c r="R212" t="n">
-        <v>6815521</v>
+        <v>6815035</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22577,10 +22577,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289658</v>
+        <v>122289609</v>
       </c>
       <c r="B213" t="n">
-        <v>78660</v>
+        <v>80617</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22593,21 +22593,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22617,10 +22617,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>472721</v>
+        <v>472975</v>
       </c>
       <c r="R213" t="n">
-        <v>6815373</v>
+        <v>6815664</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22679,7 +22679,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289714</v>
+        <v>122289696</v>
       </c>
       <c r="B214" t="n">
         <v>78660</v>
@@ -22719,10 +22719,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>472966</v>
+        <v>473033</v>
       </c>
       <c r="R214" t="n">
-        <v>6815345</v>
+        <v>6815029</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22781,10 +22781,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289502</v>
+        <v>122289747</v>
       </c>
       <c r="B215" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22797,21 +22797,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22821,10 +22821,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>472693</v>
+        <v>473203</v>
       </c>
       <c r="R215" t="n">
-        <v>6815202</v>
+        <v>6815521</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22883,10 +22883,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289503</v>
+        <v>122289658</v>
       </c>
       <c r="B216" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22899,21 +22899,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22923,10 +22923,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>472704</v>
+        <v>472721</v>
       </c>
       <c r="R216" t="n">
-        <v>6815035</v>
+        <v>6815373</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22985,10 +22985,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289609</v>
+        <v>122289714</v>
       </c>
       <c r="B217" t="n">
-        <v>80617</v>
+        <v>78660</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23001,21 +23001,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23025,10 +23025,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>472975</v>
+        <v>472966</v>
       </c>
       <c r="R217" t="n">
-        <v>6815664</v>
+        <v>6815345</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23194,10 +23194,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289581</v>
+        <v>122289532</v>
       </c>
       <c r="B219" t="n">
-        <v>57384</v>
+        <v>79249</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23210,39 +23210,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>472821</v>
+        <v>473191</v>
       </c>
       <c r="R219" t="n">
-        <v>6815364</v>
+        <v>6815504</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23275,11 +23270,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23306,10 +23296,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289588</v>
+        <v>122289526</v>
       </c>
       <c r="B220" t="n">
-        <v>57384</v>
+        <v>79249</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23322,39 +23312,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>472971</v>
+        <v>473224</v>
       </c>
       <c r="R220" t="n">
-        <v>6815298</v>
+        <v>6815616</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23387,11 +23372,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23418,10 +23398,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289532</v>
+        <v>122289608</v>
       </c>
       <c r="B221" t="n">
-        <v>79249</v>
+        <v>78397</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23434,21 +23414,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23458,10 +23438,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>473191</v>
+        <v>472951</v>
       </c>
       <c r="R221" t="n">
-        <v>6815504</v>
+        <v>6815418</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23520,10 +23500,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289526</v>
+        <v>122289599</v>
       </c>
       <c r="B222" t="n">
-        <v>79249</v>
+        <v>78397</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23536,21 +23516,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23560,10 +23540,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>473224</v>
+        <v>472912</v>
       </c>
       <c r="R222" t="n">
-        <v>6815616</v>
+        <v>6815662</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23622,7 +23602,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289608</v>
+        <v>122289602</v>
       </c>
       <c r="B223" t="n">
         <v>78397</v>
@@ -23662,10 +23642,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>472951</v>
+        <v>472810</v>
       </c>
       <c r="R223" t="n">
-        <v>6815418</v>
+        <v>6815367</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23724,10 +23704,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122289599</v>
+        <v>122289581</v>
       </c>
       <c r="B224" t="n">
-        <v>78397</v>
+        <v>57384</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23740,34 +23720,39 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>472912</v>
+        <v>472821</v>
       </c>
       <c r="R224" t="n">
-        <v>6815662</v>
+        <v>6815364</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23800,6 +23785,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23826,10 +23816,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122289602</v>
+        <v>122289588</v>
       </c>
       <c r="B225" t="n">
-        <v>78397</v>
+        <v>57384</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23842,34 +23832,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>472810</v>
+        <v>472971</v>
       </c>
       <c r="R225" t="n">
-        <v>6815367</v>
+        <v>6815298</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23902,6 +23897,11 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25152,10 +25152,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122289485</v>
+        <v>122289518</v>
       </c>
       <c r="B238" t="n">
-        <v>79278</v>
+        <v>78694</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25168,21 +25168,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25192,10 +25192,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>473014</v>
+        <v>473192</v>
       </c>
       <c r="R238" t="n">
-        <v>6815496</v>
+        <v>6815502</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25254,10 +25254,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122289630</v>
+        <v>122289520</v>
       </c>
       <c r="B239" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25270,21 +25270,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25294,10 +25294,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>473038</v>
+        <v>473245</v>
       </c>
       <c r="R239" t="n">
-        <v>6815393</v>
+        <v>6815602</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25356,10 +25356,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122289751</v>
+        <v>122289485</v>
       </c>
       <c r="B240" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25372,21 +25372,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25396,10 +25396,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>473230</v>
+        <v>473014</v>
       </c>
       <c r="R240" t="n">
-        <v>6815539</v>
+        <v>6815496</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25458,10 +25458,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>122289612</v>
+        <v>122289630</v>
       </c>
       <c r="B241" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25474,21 +25474,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25498,10 +25498,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>472742</v>
+        <v>473038</v>
       </c>
       <c r="R241" t="n">
-        <v>6815075</v>
+        <v>6815393</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25560,7 +25560,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122289657</v>
+        <v>122289751</v>
       </c>
       <c r="B242" t="n">
         <v>78660</v>
@@ -25600,10 +25600,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>472730</v>
+        <v>473230</v>
       </c>
       <c r="R242" t="n">
-        <v>6815383</v>
+        <v>6815539</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25662,10 +25662,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122289666</v>
+        <v>122289612</v>
       </c>
       <c r="B243" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25678,21 +25678,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25702,10 +25702,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>472737</v>
+        <v>472742</v>
       </c>
       <c r="R243" t="n">
-        <v>6815084</v>
+        <v>6815075</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25764,7 +25764,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122289656</v>
+        <v>122289657</v>
       </c>
       <c r="B244" t="n">
         <v>78660</v>
@@ -25804,10 +25804,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>472748</v>
+        <v>472730</v>
       </c>
       <c r="R244" t="n">
-        <v>6815374</v>
+        <v>6815383</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25866,10 +25866,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122289615</v>
+        <v>122289666</v>
       </c>
       <c r="B245" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25882,39 +25882,34 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>472712</v>
+        <v>472737</v>
       </c>
       <c r="R245" t="n">
-        <v>6815141</v>
+        <v>6815084</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25947,11 +25942,6 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25978,10 +25968,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122289564</v>
+        <v>122289656</v>
       </c>
       <c r="B246" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25994,39 +25984,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>472724</v>
+        <v>472748</v>
       </c>
       <c r="R246" t="n">
-        <v>6815345</v>
+        <v>6815374</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26059,11 +26044,6 @@
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26090,7 +26070,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122289570</v>
+        <v>122289615</v>
       </c>
       <c r="B247" t="n">
         <v>57384</v>
@@ -26135,10 +26115,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>473034</v>
+        <v>472712</v>
       </c>
       <c r="R247" t="n">
-        <v>6815167</v>
+        <v>6815141</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26202,10 +26182,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122289518</v>
+        <v>122289564</v>
       </c>
       <c r="B248" t="n">
-        <v>78694</v>
+        <v>57384</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26218,34 +26198,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>473192</v>
+        <v>472724</v>
       </c>
       <c r="R248" t="n">
-        <v>6815502</v>
+        <v>6815345</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26278,6 +26263,11 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26304,10 +26294,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122289520</v>
+        <v>122289570</v>
       </c>
       <c r="B249" t="n">
-        <v>78694</v>
+        <v>57384</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26320,34 +26310,39 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>473245</v>
+        <v>473034</v>
       </c>
       <c r="R249" t="n">
-        <v>6815602</v>
+        <v>6815167</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26380,6 +26375,11 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26610,10 +26610,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122289510</v>
+        <v>122289712</v>
       </c>
       <c r="B252" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26626,21 +26626,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26650,10 +26650,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>472986</v>
+        <v>472971</v>
       </c>
       <c r="R252" t="n">
-        <v>6815203</v>
+        <v>6815298</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26712,10 +26712,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289598</v>
+        <v>122289773</v>
       </c>
       <c r="B253" t="n">
-        <v>78397</v>
+        <v>78044</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26728,21 +26728,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26752,10 +26752,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>473022</v>
+        <v>473042</v>
       </c>
       <c r="R253" t="n">
-        <v>6815732</v>
+        <v>6815081</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26814,7 +26814,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289712</v>
+        <v>122289753</v>
       </c>
       <c r="B254" t="n">
         <v>78660</v>
@@ -26854,10 +26854,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>472971</v>
+        <v>473242</v>
       </c>
       <c r="R254" t="n">
-        <v>6815298</v>
+        <v>6815602</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26916,10 +26916,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289773</v>
+        <v>122289619</v>
       </c>
       <c r="B255" t="n">
-        <v>78044</v>
+        <v>78660</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26932,21 +26932,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26956,10 +26956,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>473042</v>
+        <v>473228</v>
       </c>
       <c r="R255" t="n">
-        <v>6815081</v>
+        <v>6815569</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27018,10 +27018,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289753</v>
+        <v>122289484</v>
       </c>
       <c r="B256" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27034,21 +27034,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -27058,10 +27058,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>473242</v>
+        <v>472950</v>
       </c>
       <c r="R256" t="n">
-        <v>6815602</v>
+        <v>6815417</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27120,10 +27120,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289619</v>
+        <v>122289480</v>
       </c>
       <c r="B257" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27136,21 +27136,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27160,10 +27160,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>473228</v>
+        <v>472742</v>
       </c>
       <c r="R257" t="n">
-        <v>6815569</v>
+        <v>6815075</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27222,10 +27222,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289484</v>
+        <v>122289693</v>
       </c>
       <c r="B258" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27238,21 +27238,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27262,10 +27262,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>472950</v>
+        <v>473002</v>
       </c>
       <c r="R258" t="n">
-        <v>6815417</v>
+        <v>6814987</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27324,10 +27324,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289480</v>
+        <v>122289669</v>
       </c>
       <c r="B259" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27340,21 +27340,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27364,10 +27364,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>472742</v>
+        <v>472718</v>
       </c>
       <c r="R259" t="n">
-        <v>6815075</v>
+        <v>6815041</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27426,10 +27426,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122289693</v>
+        <v>122289510</v>
       </c>
       <c r="B260" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27442,21 +27442,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27466,10 +27466,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>473002</v>
+        <v>472986</v>
       </c>
       <c r="R260" t="n">
-        <v>6814987</v>
+        <v>6815203</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27528,10 +27528,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122289669</v>
+        <v>122289586</v>
       </c>
       <c r="B261" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27544,34 +27544,39 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>472718</v>
+        <v>473036</v>
       </c>
       <c r="R261" t="n">
-        <v>6815041</v>
+        <v>6815173</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27604,6 +27609,11 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27630,10 +27640,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122289586</v>
+        <v>122289598</v>
       </c>
       <c r="B262" t="n">
-        <v>57384</v>
+        <v>78397</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27646,39 +27656,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>473036</v>
+        <v>473022</v>
       </c>
       <c r="R262" t="n">
-        <v>6815173</v>
+        <v>6815732</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27711,11 +27716,6 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD262" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122289507</v>
+        <v>122289752</v>
       </c>
       <c r="B5" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473043</v>
+        <v>473224</v>
       </c>
       <c r="R5" t="n">
-        <v>6815153</v>
+        <v>6815578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122289525</v>
+        <v>122289756</v>
       </c>
       <c r="B6" t="n">
-        <v>95790</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472724</v>
+        <v>473239</v>
       </c>
       <c r="R6" t="n">
-        <v>6815100</v>
+        <v>6815673</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122289504</v>
+        <v>122289648</v>
       </c>
       <c r="B7" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472835</v>
+        <v>472874</v>
       </c>
       <c r="R7" t="n">
-        <v>6815089</v>
+        <v>6815282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122289587</v>
+        <v>122289631</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,39 +1350,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473000</v>
+        <v>472746</v>
       </c>
       <c r="R8" t="n">
-        <v>6815184</v>
+        <v>6815730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,11 +1410,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122289571</v>
+        <v>122289482</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>79278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,39 +1452,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472895</v>
+        <v>472988</v>
       </c>
       <c r="R9" t="n">
-        <v>6815359</v>
+        <v>6815002</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,11 +1512,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122289590</v>
+        <v>122289653</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,39 +1554,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472945</v>
+        <v>472794</v>
       </c>
       <c r="R10" t="n">
-        <v>6815381</v>
+        <v>6815364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,11 +1614,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122289752</v>
+        <v>122289754</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1710,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473224</v>
+        <v>473240</v>
       </c>
       <c r="R11" t="n">
-        <v>6815578</v>
+        <v>6815620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1742,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122289756</v>
+        <v>122289744</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1812,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473239</v>
+        <v>473188</v>
       </c>
       <c r="R12" t="n">
-        <v>6815673</v>
+        <v>6815489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1844,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122289648</v>
+        <v>122289629</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1914,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472874</v>
+        <v>472833</v>
       </c>
       <c r="R13" t="n">
-        <v>6815282</v>
+        <v>6815744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122289631</v>
+        <v>122289587</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,34 +1962,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472746</v>
+        <v>473000</v>
       </c>
       <c r="R14" t="n">
-        <v>6815730</v>
+        <v>6815184</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,6 +2027,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122289482</v>
+        <v>122289571</v>
       </c>
       <c r="B15" t="n">
-        <v>79278</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,34 +2074,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472988</v>
+        <v>472895</v>
       </c>
       <c r="R15" t="n">
-        <v>6815002</v>
+        <v>6815359</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,6 +2139,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122289653</v>
+        <v>122289590</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,34 +2186,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472794</v>
+        <v>472945</v>
       </c>
       <c r="R16" t="n">
-        <v>6815364</v>
+        <v>6815381</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,6 +2251,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122289754</v>
+        <v>122289601</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473240</v>
+        <v>472894</v>
       </c>
       <c r="R17" t="n">
-        <v>6815620</v>
+        <v>6815448</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122289744</v>
+        <v>122289529</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>79249</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473188</v>
+        <v>472881</v>
       </c>
       <c r="R18" t="n">
-        <v>6815489</v>
+        <v>6815396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122289629</v>
+        <v>122289507</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472833</v>
+        <v>473043</v>
       </c>
       <c r="R19" t="n">
-        <v>6815744</v>
+        <v>6815153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122289601</v>
+        <v>122289525</v>
       </c>
       <c r="B20" t="n">
-        <v>78397</v>
+        <v>95790</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472894</v>
+        <v>472724</v>
       </c>
       <c r="R20" t="n">
-        <v>6815448</v>
+        <v>6815100</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122289529</v>
+        <v>122289504</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>78694</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472881</v>
+        <v>472835</v>
       </c>
       <c r="R21" t="n">
-        <v>6815396</v>
+        <v>6815089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122289597</v>
+        <v>122289486</v>
       </c>
       <c r="B22" t="n">
-        <v>78397</v>
+        <v>79278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,21 +2808,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473041</v>
+        <v>473115</v>
       </c>
       <c r="R22" t="n">
-        <v>6815720</v>
+        <v>6815359</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122289486</v>
+        <v>122289710</v>
       </c>
       <c r="B23" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473115</v>
+        <v>472998</v>
       </c>
       <c r="R23" t="n">
-        <v>6815359</v>
+        <v>6815243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122289710</v>
+        <v>122289495</v>
       </c>
       <c r="B24" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,21 +3012,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472998</v>
+        <v>473212</v>
       </c>
       <c r="R24" t="n">
-        <v>6815243</v>
+        <v>6815464</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122289495</v>
+        <v>122289494</v>
       </c>
       <c r="B25" t="n">
         <v>74761</v>
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473212</v>
+        <v>473044</v>
       </c>
       <c r="R25" t="n">
-        <v>6815464</v>
+        <v>6815169</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122289494</v>
+        <v>122289490</v>
       </c>
       <c r="B26" t="n">
         <v>74761</v>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473044</v>
+        <v>472713</v>
       </c>
       <c r="R26" t="n">
-        <v>6815169</v>
+        <v>6815143</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,10 +3302,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122289490</v>
+        <v>122289627</v>
       </c>
       <c r="B27" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3318,21 +3318,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472713</v>
+        <v>472837</v>
       </c>
       <c r="R27" t="n">
-        <v>6815143</v>
+        <v>6815704</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122289627</v>
+        <v>122289476</v>
       </c>
       <c r="B28" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472837</v>
+        <v>472813</v>
       </c>
       <c r="R28" t="n">
-        <v>6815704</v>
+        <v>6815369</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122289476</v>
+        <v>122289524</v>
       </c>
       <c r="B29" t="n">
-        <v>79278</v>
+        <v>78694</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3522,21 +3522,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472813</v>
+        <v>473242</v>
       </c>
       <c r="R29" t="n">
-        <v>6815369</v>
+        <v>6815724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122289524</v>
+        <v>122289515</v>
       </c>
       <c r="B30" t="n">
         <v>78694</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473242</v>
+        <v>473035</v>
       </c>
       <c r="R30" t="n">
-        <v>6815724</v>
+        <v>6815416</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122289515</v>
+        <v>122289597</v>
       </c>
       <c r="B31" t="n">
-        <v>78694</v>
+        <v>78397</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3726,21 +3726,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473035</v>
+        <v>473041</v>
       </c>
       <c r="R31" t="n">
-        <v>6815416</v>
+        <v>6815720</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -7198,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122289556</v>
+        <v>122289621</v>
       </c>
       <c r="B65" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7214,39 +7214,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>472995</v>
+        <v>473076</v>
       </c>
       <c r="R65" t="n">
-        <v>6815217</v>
+        <v>6815660</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7279,11 +7274,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7310,10 +7300,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122289566</v>
+        <v>122289691</v>
       </c>
       <c r="B66" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7326,39 +7316,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472846</v>
+        <v>472974</v>
       </c>
       <c r="R66" t="n">
-        <v>6815099</v>
+        <v>6815012</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7391,11 +7376,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7422,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122289603</v>
+        <v>122289643</v>
       </c>
       <c r="B67" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7438,21 +7418,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7462,10 +7442,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472794</v>
+        <v>472856</v>
       </c>
       <c r="R67" t="n">
-        <v>6815363</v>
+        <v>6815448</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7524,10 +7504,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122289621</v>
+        <v>122289551</v>
       </c>
       <c r="B68" t="n">
-        <v>78660</v>
+        <v>79645</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7536,25 +7516,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7564,10 +7544,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473076</v>
+        <v>472884</v>
       </c>
       <c r="R68" t="n">
-        <v>6815660</v>
+        <v>6815478</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7626,10 +7606,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122289691</v>
+        <v>122289603</v>
       </c>
       <c r="B69" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7642,21 +7622,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7666,10 +7646,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472974</v>
+        <v>472794</v>
       </c>
       <c r="R69" t="n">
-        <v>6815012</v>
+        <v>6815363</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7728,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289643</v>
+        <v>122289556</v>
       </c>
       <c r="B70" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7744,34 +7724,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472856</v>
+        <v>472995</v>
       </c>
       <c r="R70" t="n">
-        <v>6815448</v>
+        <v>6815217</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7804,6 +7789,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7830,10 +7820,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289551</v>
+        <v>122289566</v>
       </c>
       <c r="B71" t="n">
-        <v>79645</v>
+        <v>57384</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7842,38 +7832,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472884</v>
+        <v>472846</v>
       </c>
       <c r="R71" t="n">
-        <v>6815478</v>
+        <v>6815099</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7906,6 +7901,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -19671,10 +19671,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122289537</v>
+        <v>122289616</v>
       </c>
       <c r="B185" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19687,39 +19687,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>472724</v>
+        <v>473244</v>
       </c>
       <c r="R185" t="n">
-        <v>6815093</v>
+        <v>6815667</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19778,10 +19773,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289533</v>
+        <v>122289697</v>
       </c>
       <c r="B186" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19794,39 +19789,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>473021</v>
+        <v>473033</v>
       </c>
       <c r="R186" t="n">
-        <v>6815478</v>
+        <v>6815058</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19885,10 +19875,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289584</v>
+        <v>122289723</v>
       </c>
       <c r="B187" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19901,39 +19891,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>473037</v>
+        <v>472901</v>
       </c>
       <c r="R187" t="n">
-        <v>6815020</v>
+        <v>6815361</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19966,11 +19951,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19997,10 +19977,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289575</v>
+        <v>122289762</v>
       </c>
       <c r="B188" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20013,39 +19993,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>473231</v>
+        <v>473222</v>
       </c>
       <c r="R188" t="n">
-        <v>6815546</v>
+        <v>6815741</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20078,11 +20053,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20109,10 +20079,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122289565</v>
+        <v>122289768</v>
       </c>
       <c r="B189" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20125,39 +20095,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>472697</v>
+        <v>472877</v>
       </c>
       <c r="R189" t="n">
-        <v>6815151</v>
+        <v>6815103</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20190,11 +20155,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20221,10 +20181,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289585</v>
+        <v>122289681</v>
       </c>
       <c r="B190" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20237,39 +20197,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>473030</v>
+        <v>472834</v>
       </c>
       <c r="R190" t="n">
-        <v>6815053</v>
+        <v>6815094</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20302,11 +20257,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20333,10 +20283,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122289616</v>
+        <v>122289738</v>
       </c>
       <c r="B191" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20349,21 +20299,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20373,10 +20323,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>473244</v>
+        <v>473045</v>
       </c>
       <c r="R191" t="n">
-        <v>6815667</v>
+        <v>6815390</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20435,10 +20385,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122289697</v>
+        <v>122289491</v>
       </c>
       <c r="B192" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20451,21 +20401,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20475,10 +20425,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>473033</v>
+        <v>472841</v>
       </c>
       <c r="R192" t="n">
-        <v>6815058</v>
+        <v>6815128</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20537,7 +20487,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122289723</v>
+        <v>122289637</v>
       </c>
       <c r="B193" t="n">
         <v>78660</v>
@@ -20577,10 +20527,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>472901</v>
+        <v>472863</v>
       </c>
       <c r="R193" t="n">
-        <v>6815361</v>
+        <v>6815525</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20639,10 +20589,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122289762</v>
+        <v>122289517</v>
       </c>
       <c r="B194" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20655,21 +20605,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20679,10 +20629,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>473222</v>
+        <v>473149</v>
       </c>
       <c r="R194" t="n">
-        <v>6815741</v>
+        <v>6815391</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20741,10 +20691,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122289768</v>
+        <v>122289537</v>
       </c>
       <c r="B195" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20757,34 +20707,39 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>472877</v>
+        <v>472724</v>
       </c>
       <c r="R195" t="n">
-        <v>6815103</v>
+        <v>6815093</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20843,10 +20798,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122289681</v>
+        <v>122289533</v>
       </c>
       <c r="B196" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20859,34 +20814,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>472834</v>
+        <v>473021</v>
       </c>
       <c r="R196" t="n">
-        <v>6815094</v>
+        <v>6815478</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20945,10 +20905,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122289738</v>
+        <v>122289584</v>
       </c>
       <c r="B197" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20961,34 +20921,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>473045</v>
+        <v>473037</v>
       </c>
       <c r="R197" t="n">
-        <v>6815390</v>
+        <v>6815020</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21021,6 +20986,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21047,10 +21017,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122289491</v>
+        <v>122289575</v>
       </c>
       <c r="B198" t="n">
-        <v>74761</v>
+        <v>57384</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21063,34 +21033,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>472841</v>
+        <v>473231</v>
       </c>
       <c r="R198" t="n">
-        <v>6815128</v>
+        <v>6815546</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21123,6 +21098,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21149,10 +21129,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122289637</v>
+        <v>122289565</v>
       </c>
       <c r="B199" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21165,34 +21145,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>472863</v>
+        <v>472697</v>
       </c>
       <c r="R199" t="n">
-        <v>6815525</v>
+        <v>6815151</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21225,6 +21210,11 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21251,10 +21241,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122289517</v>
+        <v>122289585</v>
       </c>
       <c r="B200" t="n">
-        <v>78694</v>
+        <v>57384</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21267,34 +21257,39 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>473149</v>
+        <v>473030</v>
       </c>
       <c r="R200" t="n">
-        <v>6815391</v>
+        <v>6815053</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21327,6 +21322,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22373,10 +22373,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122289502</v>
+        <v>122289696</v>
       </c>
       <c r="B211" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22389,21 +22389,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22413,10 +22413,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>472693</v>
+        <v>473033</v>
       </c>
       <c r="R211" t="n">
-        <v>6815202</v>
+        <v>6815029</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22475,10 +22475,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122289503</v>
+        <v>122289747</v>
       </c>
       <c r="B212" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22491,21 +22491,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22515,10 +22515,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>472704</v>
+        <v>473203</v>
       </c>
       <c r="R212" t="n">
-        <v>6815035</v>
+        <v>6815521</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22577,10 +22577,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122289609</v>
+        <v>122289658</v>
       </c>
       <c r="B213" t="n">
-        <v>80617</v>
+        <v>78660</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22593,21 +22593,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22617,10 +22617,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>472975</v>
+        <v>472721</v>
       </c>
       <c r="R213" t="n">
-        <v>6815664</v>
+        <v>6815373</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22679,7 +22679,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122289696</v>
+        <v>122289714</v>
       </c>
       <c r="B214" t="n">
         <v>78660</v>
@@ -22719,10 +22719,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>473033</v>
+        <v>472966</v>
       </c>
       <c r="R214" t="n">
-        <v>6815029</v>
+        <v>6815345</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22781,10 +22781,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122289747</v>
+        <v>122289502</v>
       </c>
       <c r="B215" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22797,21 +22797,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22821,10 +22821,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>473203</v>
+        <v>472693</v>
       </c>
       <c r="R215" t="n">
-        <v>6815521</v>
+        <v>6815202</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22883,10 +22883,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122289658</v>
+        <v>122289503</v>
       </c>
       <c r="B216" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22899,21 +22899,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22923,10 +22923,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>472721</v>
+        <v>472704</v>
       </c>
       <c r="R216" t="n">
-        <v>6815373</v>
+        <v>6815035</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22985,10 +22985,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122289714</v>
+        <v>122289609</v>
       </c>
       <c r="B217" t="n">
-        <v>78660</v>
+        <v>80617</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23001,21 +23001,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23025,10 +23025,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>472966</v>
+        <v>472975</v>
       </c>
       <c r="R217" t="n">
-        <v>6815345</v>
+        <v>6815664</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23194,10 +23194,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122289532</v>
+        <v>122289581</v>
       </c>
       <c r="B219" t="n">
-        <v>79249</v>
+        <v>57384</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23210,34 +23210,39 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>473191</v>
+        <v>472821</v>
       </c>
       <c r="R219" t="n">
-        <v>6815504</v>
+        <v>6815364</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23270,6 +23275,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23296,10 +23306,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122289526</v>
+        <v>122289588</v>
       </c>
       <c r="B220" t="n">
-        <v>79249</v>
+        <v>57384</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23312,34 +23322,39 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>473224</v>
+        <v>472971</v>
       </c>
       <c r="R220" t="n">
-        <v>6815616</v>
+        <v>6815298</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23372,6 +23387,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23398,10 +23418,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122289608</v>
+        <v>122289532</v>
       </c>
       <c r="B221" t="n">
-        <v>78397</v>
+        <v>79249</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23414,21 +23434,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23438,10 +23458,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>472951</v>
+        <v>473191</v>
       </c>
       <c r="R221" t="n">
-        <v>6815418</v>
+        <v>6815504</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23500,10 +23520,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122289599</v>
+        <v>122289526</v>
       </c>
       <c r="B222" t="n">
-        <v>78397</v>
+        <v>79249</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23516,21 +23536,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23540,10 +23560,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>472912</v>
+        <v>473224</v>
       </c>
       <c r="R222" t="n">
-        <v>6815662</v>
+        <v>6815616</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23602,7 +23622,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122289602</v>
+        <v>122289608</v>
       </c>
       <c r="B223" t="n">
         <v>78397</v>
@@ -23642,10 +23662,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>472810</v>
+        <v>472951</v>
       </c>
       <c r="R223" t="n">
-        <v>6815367</v>
+        <v>6815418</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23704,10 +23724,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122289581</v>
+        <v>122289599</v>
       </c>
       <c r="B224" t="n">
-        <v>57384</v>
+        <v>78397</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23720,39 +23740,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>472821</v>
+        <v>472912</v>
       </c>
       <c r="R224" t="n">
-        <v>6815364</v>
+        <v>6815662</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23785,11 +23800,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23816,10 +23826,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122289588</v>
+        <v>122289602</v>
       </c>
       <c r="B225" t="n">
-        <v>57384</v>
+        <v>78397</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23832,39 +23842,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>472971</v>
+        <v>472810</v>
       </c>
       <c r="R225" t="n">
-        <v>6815298</v>
+        <v>6815367</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23897,11 +23902,6 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25152,10 +25152,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122289518</v>
+        <v>122289485</v>
       </c>
       <c r="B238" t="n">
-        <v>78694</v>
+        <v>79278</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25168,21 +25168,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25192,10 +25192,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>473192</v>
+        <v>473014</v>
       </c>
       <c r="R238" t="n">
-        <v>6815502</v>
+        <v>6815496</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25254,10 +25254,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122289520</v>
+        <v>122289630</v>
       </c>
       <c r="B239" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25270,21 +25270,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25294,10 +25294,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>473245</v>
+        <v>473038</v>
       </c>
       <c r="R239" t="n">
-        <v>6815602</v>
+        <v>6815393</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25356,10 +25356,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122289485</v>
+        <v>122289751</v>
       </c>
       <c r="B240" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25372,21 +25372,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25396,10 +25396,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>473014</v>
+        <v>473230</v>
       </c>
       <c r="R240" t="n">
-        <v>6815496</v>
+        <v>6815539</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25458,10 +25458,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>122289630</v>
+        <v>122289612</v>
       </c>
       <c r="B241" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25474,21 +25474,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25498,10 +25498,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>473038</v>
+        <v>472742</v>
       </c>
       <c r="R241" t="n">
-        <v>6815393</v>
+        <v>6815075</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25560,7 +25560,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122289751</v>
+        <v>122289657</v>
       </c>
       <c r="B242" t="n">
         <v>78660</v>
@@ -25600,10 +25600,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>473230</v>
+        <v>472730</v>
       </c>
       <c r="R242" t="n">
-        <v>6815539</v>
+        <v>6815383</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25662,10 +25662,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122289612</v>
+        <v>122289666</v>
       </c>
       <c r="B243" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25678,21 +25678,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25702,10 +25702,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>472742</v>
+        <v>472737</v>
       </c>
       <c r="R243" t="n">
-        <v>6815075</v>
+        <v>6815084</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25764,7 +25764,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122289657</v>
+        <v>122289656</v>
       </c>
       <c r="B244" t="n">
         <v>78660</v>
@@ -25804,10 +25804,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>472730</v>
+        <v>472748</v>
       </c>
       <c r="R244" t="n">
-        <v>6815383</v>
+        <v>6815374</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25866,10 +25866,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122289666</v>
+        <v>122289615</v>
       </c>
       <c r="B245" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25882,34 +25882,39 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>472737</v>
+        <v>472712</v>
       </c>
       <c r="R245" t="n">
-        <v>6815084</v>
+        <v>6815141</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25942,6 +25947,11 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25968,10 +25978,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122289656</v>
+        <v>122289564</v>
       </c>
       <c r="B246" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25984,34 +25994,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>472748</v>
+        <v>472724</v>
       </c>
       <c r="R246" t="n">
-        <v>6815374</v>
+        <v>6815345</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26044,6 +26059,11 @@
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26070,7 +26090,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122289615</v>
+        <v>122289570</v>
       </c>
       <c r="B247" t="n">
         <v>57384</v>
@@ -26115,10 +26135,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>472712</v>
+        <v>473034</v>
       </c>
       <c r="R247" t="n">
-        <v>6815141</v>
+        <v>6815167</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26182,10 +26202,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122289564</v>
+        <v>122289518</v>
       </c>
       <c r="B248" t="n">
-        <v>57384</v>
+        <v>78694</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26198,39 +26218,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>472724</v>
+        <v>473192</v>
       </c>
       <c r="R248" t="n">
-        <v>6815345</v>
+        <v>6815502</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26263,11 +26278,6 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26294,10 +26304,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122289570</v>
+        <v>122289520</v>
       </c>
       <c r="B249" t="n">
-        <v>57384</v>
+        <v>78694</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26310,39 +26320,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>473034</v>
+        <v>473245</v>
       </c>
       <c r="R249" t="n">
-        <v>6815167</v>
+        <v>6815602</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26375,11 +26380,6 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD249" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122289752</v>
+        <v>122289507</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473224</v>
+        <v>473043</v>
       </c>
       <c r="R5" t="n">
-        <v>6815578</v>
+        <v>6815153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122289756</v>
+        <v>122289525</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>95790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473239</v>
+        <v>472724</v>
       </c>
       <c r="R6" t="n">
-        <v>6815673</v>
+        <v>6815100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122289648</v>
+        <v>122289504</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472874</v>
+        <v>472835</v>
       </c>
       <c r="R7" t="n">
-        <v>6815282</v>
+        <v>6815089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122289631</v>
+        <v>122289587</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,34 +1350,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472746</v>
+        <v>473000</v>
       </c>
       <c r="R8" t="n">
-        <v>6815730</v>
+        <v>6815184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,6 +1415,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122289482</v>
+        <v>122289571</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,34 +1462,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472988</v>
+        <v>472895</v>
       </c>
       <c r="R9" t="n">
-        <v>6815002</v>
+        <v>6815359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,6 +1527,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122289653</v>
+        <v>122289590</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,34 +1574,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472794</v>
+        <v>472945</v>
       </c>
       <c r="R10" t="n">
-        <v>6815364</v>
+        <v>6815381</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1639,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,7 +1670,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122289754</v>
+        <v>122289752</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1680,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473240</v>
+        <v>473224</v>
       </c>
       <c r="R11" t="n">
-        <v>6815620</v>
+        <v>6815578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1772,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122289744</v>
+        <v>122289756</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1782,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473188</v>
+        <v>473239</v>
       </c>
       <c r="R12" t="n">
-        <v>6815489</v>
+        <v>6815673</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1874,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122289629</v>
+        <v>122289648</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1884,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472833</v>
+        <v>472874</v>
       </c>
       <c r="R13" t="n">
-        <v>6815744</v>
+        <v>6815282</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122289587</v>
+        <v>122289631</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,39 +1992,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473000</v>
+        <v>472746</v>
       </c>
       <c r="R14" t="n">
-        <v>6815184</v>
+        <v>6815730</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,11 +2052,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122289571</v>
+        <v>122289482</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>79278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,39 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472895</v>
+        <v>472988</v>
       </c>
       <c r="R15" t="n">
-        <v>6815359</v>
+        <v>6815002</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,11 +2154,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122289590</v>
+        <v>122289653</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,39 +2196,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472945</v>
+        <v>472794</v>
       </c>
       <c r="R16" t="n">
-        <v>6815381</v>
+        <v>6815364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,11 +2256,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122289601</v>
+        <v>122289754</v>
       </c>
       <c r="B17" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472894</v>
+        <v>473240</v>
       </c>
       <c r="R17" t="n">
-        <v>6815448</v>
+        <v>6815620</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122289529</v>
+        <v>122289744</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472881</v>
+        <v>473188</v>
       </c>
       <c r="R18" t="n">
-        <v>6815396</v>
+        <v>6815489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122289507</v>
+        <v>122289629</v>
       </c>
       <c r="B19" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473043</v>
+        <v>472833</v>
       </c>
       <c r="R19" t="n">
-        <v>6815153</v>
+        <v>6815744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122289525</v>
+        <v>122289601</v>
       </c>
       <c r="B20" t="n">
-        <v>95790</v>
+        <v>78397</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472724</v>
+        <v>472894</v>
       </c>
       <c r="R20" t="n">
-        <v>6815100</v>
+        <v>6815448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122289504</v>
+        <v>122289529</v>
       </c>
       <c r="B21" t="n">
-        <v>78694</v>
+        <v>79249</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472835</v>
+        <v>472881</v>
       </c>
       <c r="R21" t="n">
-        <v>6815089</v>
+        <v>6815396</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -7198,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122289621</v>
+        <v>122289556</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7214,34 +7214,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473076</v>
+        <v>472995</v>
       </c>
       <c r="R65" t="n">
-        <v>6815660</v>
+        <v>6815217</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,6 +7279,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7300,10 +7310,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122289691</v>
+        <v>122289566</v>
       </c>
       <c r="B66" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7316,34 +7326,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472974</v>
+        <v>472846</v>
       </c>
       <c r="R66" t="n">
-        <v>6815012</v>
+        <v>6815099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7376,6 +7391,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,10 +7422,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122289643</v>
+        <v>122289603</v>
       </c>
       <c r="B67" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7418,21 +7438,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7442,10 +7462,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472856</v>
+        <v>472794</v>
       </c>
       <c r="R67" t="n">
-        <v>6815448</v>
+        <v>6815363</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7504,10 +7524,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122289551</v>
+        <v>122289621</v>
       </c>
       <c r="B68" t="n">
-        <v>79645</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7516,25 +7536,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7544,10 +7564,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472884</v>
+        <v>473076</v>
       </c>
       <c r="R68" t="n">
-        <v>6815478</v>
+        <v>6815660</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7606,10 +7626,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122289603</v>
+        <v>122289691</v>
       </c>
       <c r="B69" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7622,21 +7642,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7646,10 +7666,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472794</v>
+        <v>472974</v>
       </c>
       <c r="R69" t="n">
-        <v>6815363</v>
+        <v>6815012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7708,10 +7728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122289556</v>
+        <v>122289643</v>
       </c>
       <c r="B70" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7724,39 +7744,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472995</v>
+        <v>472856</v>
       </c>
       <c r="R70" t="n">
-        <v>6815217</v>
+        <v>6815448</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7789,11 +7804,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre rnghack (tall)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7820,10 +7830,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122289566</v>
+        <v>122289551</v>
       </c>
       <c r="B71" t="n">
-        <v>57384</v>
+        <v>79645</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7832,43 +7842,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472846</v>
+        <v>472884</v>
       </c>
       <c r="R71" t="n">
-        <v>6815099</v>
+        <v>6815478</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,11 +7906,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10721,10 +10721,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122289771</v>
+        <v>122289692</v>
       </c>
       <c r="B99" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10737,21 +10737,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>473227</v>
+        <v>472970</v>
       </c>
       <c r="R99" t="n">
-        <v>6815737</v>
+        <v>6814989</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10823,7 +10823,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122289692</v>
+        <v>122289689</v>
       </c>
       <c r="B100" t="n">
         <v>78660</v>
@@ -10863,10 +10863,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472970</v>
+        <v>472954</v>
       </c>
       <c r="R100" t="n">
-        <v>6814989</v>
+        <v>6815041</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10925,7 +10925,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122289689</v>
+        <v>122289737</v>
       </c>
       <c r="B101" t="n">
         <v>78660</v>
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>472954</v>
+        <v>473035</v>
       </c>
       <c r="R101" t="n">
-        <v>6815041</v>
+        <v>6815416</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11027,10 +11027,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122289737</v>
+        <v>122289481</v>
       </c>
       <c r="B102" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11043,21 +11043,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>473035</v>
+        <v>472871</v>
       </c>
       <c r="R102" t="n">
-        <v>6815416</v>
+        <v>6815157</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11129,10 +11129,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122289481</v>
+        <v>122289730</v>
       </c>
       <c r="B103" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11145,21 +11145,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11169,10 +11169,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472871</v>
+        <v>472958</v>
       </c>
       <c r="R103" t="n">
-        <v>6815157</v>
+        <v>6815427</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122289730</v>
+        <v>122289650</v>
       </c>
       <c r="B104" t="n">
         <v>78660</v>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472958</v>
+        <v>472845</v>
       </c>
       <c r="R104" t="n">
-        <v>6815427</v>
+        <v>6815328</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11333,7 +11333,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122289650</v>
+        <v>122289718</v>
       </c>
       <c r="B105" t="n">
         <v>78660</v>
@@ -11373,10 +11373,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472845</v>
+        <v>472942</v>
       </c>
       <c r="R105" t="n">
-        <v>6815328</v>
+        <v>6815355</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122289718</v>
+        <v>122289774</v>
       </c>
       <c r="B106" t="n">
-        <v>78660</v>
+        <v>78044</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11451,21 +11451,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472942</v>
+        <v>473192</v>
       </c>
       <c r="R106" t="n">
-        <v>6815355</v>
+        <v>6815503</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11537,10 +11537,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122289774</v>
+        <v>122289688</v>
       </c>
       <c r="B107" t="n">
-        <v>78044</v>
+        <v>78660</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11553,21 +11553,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11577,10 +11577,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>473192</v>
+        <v>472911</v>
       </c>
       <c r="R107" t="n">
-        <v>6815503</v>
+        <v>6815063</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11639,7 +11639,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122289688</v>
+        <v>122289642</v>
       </c>
       <c r="B108" t="n">
         <v>78660</v>
@@ -11679,10 +11679,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472911</v>
+        <v>472875</v>
       </c>
       <c r="R108" t="n">
-        <v>6815063</v>
+        <v>6815470</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11741,10 +11741,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122289642</v>
+        <v>122289771</v>
       </c>
       <c r="B109" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11757,21 +11757,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472875</v>
+        <v>473227</v>
       </c>
       <c r="R109" t="n">
-        <v>6815470</v>
+        <v>6815737</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -18432,10 +18432,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122289534</v>
+        <v>122289521</v>
       </c>
       <c r="B173" t="n">
-        <v>57384</v>
+        <v>78694</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18448,39 +18448,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>472993</v>
+        <v>473236</v>
       </c>
       <c r="R173" t="n">
-        <v>6814991</v>
+        <v>6815621</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18539,10 +18534,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122289560</v>
+        <v>122289531</v>
       </c>
       <c r="B174" t="n">
-        <v>57384</v>
+        <v>79249</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18555,39 +18550,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>472880</v>
+        <v>473013</v>
       </c>
       <c r="R174" t="n">
-        <v>6815442</v>
+        <v>6815498</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18620,11 +18610,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19467,10 +19452,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122289521</v>
+        <v>122289534</v>
       </c>
       <c r="B183" t="n">
-        <v>78694</v>
+        <v>57384</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19483,34 +19468,39 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>473236</v>
+        <v>472993</v>
       </c>
       <c r="R183" t="n">
-        <v>6815621</v>
+        <v>6814991</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19569,10 +19559,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122289531</v>
+        <v>122289560</v>
       </c>
       <c r="B184" t="n">
-        <v>79249</v>
+        <v>57384</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19585,34 +19575,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>473013</v>
+        <v>472880</v>
       </c>
       <c r="R184" t="n">
-        <v>6815498</v>
+        <v>6815442</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19645,6 +19640,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19671,10 +19671,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122289616</v>
+        <v>122289537</v>
       </c>
       <c r="B185" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19687,34 +19687,39 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>473244</v>
+        <v>472724</v>
       </c>
       <c r="R185" t="n">
-        <v>6815667</v>
+        <v>6815093</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19773,10 +19778,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122289697</v>
+        <v>122289533</v>
       </c>
       <c r="B186" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19789,34 +19794,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>473033</v>
+        <v>473021</v>
       </c>
       <c r="R186" t="n">
-        <v>6815058</v>
+        <v>6815478</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19875,10 +19885,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122289723</v>
+        <v>122289584</v>
       </c>
       <c r="B187" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19891,34 +19901,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>472901</v>
+        <v>473037</v>
       </c>
       <c r="R187" t="n">
-        <v>6815361</v>
+        <v>6815020</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19951,6 +19966,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19977,10 +19997,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122289762</v>
+        <v>122289575</v>
       </c>
       <c r="B188" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19993,34 +20013,39 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>473222</v>
+        <v>473231</v>
       </c>
       <c r="R188" t="n">
-        <v>6815741</v>
+        <v>6815546</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20053,6 +20078,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20079,10 +20109,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122289768</v>
+        <v>122289565</v>
       </c>
       <c r="B189" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20095,34 +20125,39 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>472877</v>
+        <v>472697</v>
       </c>
       <c r="R189" t="n">
-        <v>6815103</v>
+        <v>6815151</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20155,6 +20190,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20181,10 +20221,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122289681</v>
+        <v>122289585</v>
       </c>
       <c r="B190" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20197,34 +20237,39 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>472834</v>
+        <v>473030</v>
       </c>
       <c r="R190" t="n">
-        <v>6815094</v>
+        <v>6815053</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20257,6 +20302,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20283,10 +20333,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122289738</v>
+        <v>122289616</v>
       </c>
       <c r="B191" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20299,21 +20349,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20323,10 +20373,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>473045</v>
+        <v>473244</v>
       </c>
       <c r="R191" t="n">
-        <v>6815390</v>
+        <v>6815667</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20385,10 +20435,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122289491</v>
+        <v>122289697</v>
       </c>
       <c r="B192" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20401,21 +20451,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20425,10 +20475,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>472841</v>
+        <v>473033</v>
       </c>
       <c r="R192" t="n">
-        <v>6815128</v>
+        <v>6815058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20487,7 +20537,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122289637</v>
+        <v>122289723</v>
       </c>
       <c r="B193" t="n">
         <v>78660</v>
@@ -20527,10 +20577,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>472863</v>
+        <v>472901</v>
       </c>
       <c r="R193" t="n">
-        <v>6815525</v>
+        <v>6815361</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20589,10 +20639,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122289517</v>
+        <v>122289762</v>
       </c>
       <c r="B194" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20605,21 +20655,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20629,10 +20679,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>473149</v>
+        <v>473222</v>
       </c>
       <c r="R194" t="n">
-        <v>6815391</v>
+        <v>6815741</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20691,10 +20741,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122289537</v>
+        <v>122289768</v>
       </c>
       <c r="B195" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20707,39 +20757,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>472724</v>
+        <v>472877</v>
       </c>
       <c r="R195" t="n">
-        <v>6815093</v>
+        <v>6815103</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20798,10 +20843,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122289533</v>
+        <v>122289681</v>
       </c>
       <c r="B196" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20814,39 +20859,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>473021</v>
+        <v>472834</v>
       </c>
       <c r="R196" t="n">
-        <v>6815478</v>
+        <v>6815094</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20905,10 +20945,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122289584</v>
+        <v>122289738</v>
       </c>
       <c r="B197" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20921,39 +20961,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>473037</v>
+        <v>473045</v>
       </c>
       <c r="R197" t="n">
-        <v>6815020</v>
+        <v>6815390</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20986,11 +21021,6 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21017,10 +21047,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122289575</v>
+        <v>122289491</v>
       </c>
       <c r="B198" t="n">
-        <v>57384</v>
+        <v>74761</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21033,39 +21063,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>473231</v>
+        <v>472841</v>
       </c>
       <c r="R198" t="n">
-        <v>6815546</v>
+        <v>6815128</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21098,11 +21123,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21129,10 +21149,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122289565</v>
+        <v>122289637</v>
       </c>
       <c r="B199" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21145,39 +21165,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>472697</v>
+        <v>472863</v>
       </c>
       <c r="R199" t="n">
-        <v>6815151</v>
+        <v>6815525</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21210,11 +21225,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21241,10 +21251,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122289585</v>
+        <v>122289517</v>
       </c>
       <c r="B200" t="n">
-        <v>57384</v>
+        <v>78694</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21257,39 +21267,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>473030</v>
+        <v>473149</v>
       </c>
       <c r="R200" t="n">
-        <v>6815053</v>
+        <v>6815391</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21322,11 +21327,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21353,10 +21353,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122289514</v>
+        <v>122289661</v>
       </c>
       <c r="B201" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21369,21 +21369,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21393,10 +21393,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>472965</v>
+        <v>472693</v>
       </c>
       <c r="R201" t="n">
-        <v>6815434</v>
+        <v>6815202</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21455,10 +21455,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122289500</v>
+        <v>122289492</v>
       </c>
       <c r="B202" t="n">
-        <v>78694</v>
+        <v>74761</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21471,21 +21471,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21495,10 +21495,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>472769</v>
+        <v>472897</v>
       </c>
       <c r="R202" t="n">
-        <v>6815363</v>
+        <v>6815078</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21557,10 +21557,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122289501</v>
+        <v>122289743</v>
       </c>
       <c r="B203" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21573,21 +21573,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>472722</v>
+        <v>473207</v>
       </c>
       <c r="R203" t="n">
-        <v>6815373</v>
+        <v>6815471</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21659,7 +21659,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122289661</v>
+        <v>122289749</v>
       </c>
       <c r="B204" t="n">
         <v>78660</v>
@@ -21699,10 +21699,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>472693</v>
+        <v>473236</v>
       </c>
       <c r="R204" t="n">
-        <v>6815202</v>
+        <v>6815526</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122289492</v>
+        <v>122289474</v>
       </c>
       <c r="B205" t="n">
-        <v>74761</v>
+        <v>79278</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>472897</v>
+        <v>473224</v>
       </c>
       <c r="R205" t="n">
-        <v>6815078</v>
+        <v>6815618</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21863,7 +21863,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122289743</v>
+        <v>122289755</v>
       </c>
       <c r="B206" t="n">
         <v>78660</v>
@@ -21903,10 +21903,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>473207</v>
+        <v>473241</v>
       </c>
       <c r="R206" t="n">
-        <v>6815471</v>
+        <v>6815645</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21965,7 +21965,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122289749</v>
+        <v>122289739</v>
       </c>
       <c r="B207" t="n">
         <v>78660</v>
@@ -22005,10 +22005,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>473236</v>
+        <v>473062</v>
       </c>
       <c r="R207" t="n">
-        <v>6815526</v>
+        <v>6815374</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22067,10 +22067,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122289474</v>
+        <v>122289514</v>
       </c>
       <c r="B208" t="n">
-        <v>79278</v>
+        <v>78694</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22083,21 +22083,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22107,10 +22107,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>473224</v>
+        <v>472965</v>
       </c>
       <c r="R208" t="n">
-        <v>6815618</v>
+        <v>6815434</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22169,10 +22169,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122289755</v>
+        <v>122289500</v>
       </c>
       <c r="B209" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22185,21 +22185,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22209,10 +22209,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>473241</v>
+        <v>472769</v>
       </c>
       <c r="R209" t="n">
-        <v>6815645</v>
+        <v>6815363</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22271,10 +22271,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122289739</v>
+        <v>122289501</v>
       </c>
       <c r="B210" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22287,21 +22287,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22311,10 +22311,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>473062</v>
+        <v>472722</v>
       </c>
       <c r="R210" t="n">
-        <v>6815374</v>
+        <v>6815373</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -26610,10 +26610,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122289712</v>
+        <v>122289510</v>
       </c>
       <c r="B252" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26626,21 +26626,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26650,10 +26650,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>472971</v>
+        <v>472986</v>
       </c>
       <c r="R252" t="n">
-        <v>6815298</v>
+        <v>6815203</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26712,10 +26712,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122289773</v>
+        <v>122289598</v>
       </c>
       <c r="B253" t="n">
-        <v>78044</v>
+        <v>78397</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26728,21 +26728,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26752,10 +26752,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>473042</v>
+        <v>473022</v>
       </c>
       <c r="R253" t="n">
-        <v>6815081</v>
+        <v>6815732</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26814,7 +26814,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122289753</v>
+        <v>122289712</v>
       </c>
       <c r="B254" t="n">
         <v>78660</v>
@@ -26854,10 +26854,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>473242</v>
+        <v>472971</v>
       </c>
       <c r="R254" t="n">
-        <v>6815602</v>
+        <v>6815298</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26916,10 +26916,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122289619</v>
+        <v>122289773</v>
       </c>
       <c r="B255" t="n">
-        <v>78660</v>
+        <v>78044</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26932,21 +26932,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26956,10 +26956,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>473228</v>
+        <v>473042</v>
       </c>
       <c r="R255" t="n">
-        <v>6815569</v>
+        <v>6815081</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27018,10 +27018,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122289484</v>
+        <v>122289753</v>
       </c>
       <c r="B256" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27034,21 +27034,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -27058,10 +27058,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>472950</v>
+        <v>473242</v>
       </c>
       <c r="R256" t="n">
-        <v>6815417</v>
+        <v>6815602</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27120,10 +27120,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122289480</v>
+        <v>122289619</v>
       </c>
       <c r="B257" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27136,21 +27136,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27160,10 +27160,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>472742</v>
+        <v>473228</v>
       </c>
       <c r="R257" t="n">
-        <v>6815075</v>
+        <v>6815569</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27222,10 +27222,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122289693</v>
+        <v>122289484</v>
       </c>
       <c r="B258" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27238,21 +27238,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27262,10 +27262,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>473002</v>
+        <v>472950</v>
       </c>
       <c r="R258" t="n">
-        <v>6814987</v>
+        <v>6815417</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27324,10 +27324,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122289669</v>
+        <v>122289480</v>
       </c>
       <c r="B259" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27340,21 +27340,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27364,10 +27364,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>472718</v>
+        <v>472742</v>
       </c>
       <c r="R259" t="n">
-        <v>6815041</v>
+        <v>6815075</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27426,10 +27426,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122289510</v>
+        <v>122289693</v>
       </c>
       <c r="B260" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27442,21 +27442,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27466,10 +27466,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>472986</v>
+        <v>473002</v>
       </c>
       <c r="R260" t="n">
-        <v>6815203</v>
+        <v>6814987</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27528,10 +27528,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122289586</v>
+        <v>122289669</v>
       </c>
       <c r="B261" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27544,39 +27544,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>473036</v>
+        <v>472718</v>
       </c>
       <c r="R261" t="n">
-        <v>6815173</v>
+        <v>6815041</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27609,11 +27604,6 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27640,10 +27630,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122289598</v>
+        <v>122289586</v>
       </c>
       <c r="B262" t="n">
-        <v>78397</v>
+        <v>57384</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27656,34 +27646,39 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>473022</v>
+        <v>473036</v>
       </c>
       <c r="R262" t="n">
-        <v>6815732</v>
+        <v>6815173</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27716,6 +27711,11 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD262" t="b">

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>122289587</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>122289571</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>122289590</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>122289568</v>
       </c>
       <c r="B35" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>122289578</v>
       </c>
       <c r="B63" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>122289556</v>
       </c>
       <c r="B65" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>122289566</v>
       </c>
       <c r="B66" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>122289583</v>
       </c>
       <c r="B84" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>122289591</v>
       </c>
       <c r="B85" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>122289589</v>
       </c>
       <c r="B98" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>122289536</v>
       </c>
       <c r="B110" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>122289572</v>
       </c>
       <c r="B111" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>122289561</v>
       </c>
       <c r="B112" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>122289582</v>
       </c>
       <c r="B122" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>122289569</v>
       </c>
       <c r="B123" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>122289535</v>
       </c>
       <c r="B124" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>122289567</v>
       </c>
       <c r="B127" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>122289563</v>
       </c>
       <c r="B128" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>122289553</v>
       </c>
       <c r="B129" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>122289559</v>
       </c>
       <c r="B130" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>122289557</v>
       </c>
       <c r="B152" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>122289558</v>
       </c>
       <c r="B153" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>122289579</v>
       </c>
       <c r="B154" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>122289555</v>
       </c>
       <c r="B155" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>122289580</v>
       </c>
       <c r="B156" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>122289562</v>
       </c>
       <c r="B170" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>122289769</v>
       </c>
       <c r="B171" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>122289534</v>
       </c>
       <c r="B183" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>122289560</v>
       </c>
       <c r="B184" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>122289537</v>
       </c>
       <c r="B185" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>122289533</v>
       </c>
       <c r="B186" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>122289584</v>
       </c>
       <c r="B187" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>122289575</v>
       </c>
       <c r="B188" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>122289565</v>
       </c>
       <c r="B189" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>122289585</v>
       </c>
       <c r="B190" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>122289592</v>
       </c>
       <c r="B218" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>122289581</v>
       </c>
       <c r="B219" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>122289588</v>
       </c>
       <c r="B220" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>122289615</v>
       </c>
       <c r="B245" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>122289564</v>
       </c>
       <c r="B246" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>122289570</v>
       </c>
       <c r="B247" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>122289586</v>
       </c>
       <c r="B262" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>122289576</v>
       </c>
       <c r="B271" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>122289577</v>
       </c>
       <c r="B272" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>122289573</v>
       </c>
       <c r="B273" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>122289574</v>
       </c>
       <c r="B274" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>

--- a/artfynd/A 61390-2024 artfynd.xlsx
+++ b/artfynd/A 61390-2024 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>122289587</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>122289571</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>122289590</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>122289568</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>122289578</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>122289556</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>122289566</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>122289583</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>122289591</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>122289589</v>
       </c>
       <c r="B98" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>122289536</v>
       </c>
       <c r="B110" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>122289572</v>
       </c>
       <c r="B111" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>122289561</v>
       </c>
       <c r="B112" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>122289582</v>
       </c>
       <c r="B122" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>122289569</v>
       </c>
       <c r="B123" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>122289535</v>
       </c>
       <c r="B124" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>122289567</v>
       </c>
       <c r="B127" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>122289563</v>
       </c>
       <c r="B128" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>122289553</v>
       </c>
       <c r="B129" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>122289559</v>
       </c>
       <c r="B130" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>122289557</v>
       </c>
       <c r="B152" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>122289558</v>
       </c>
       <c r="B153" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>122289579</v>
       </c>
       <c r="B154" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>122289555</v>
       </c>
       <c r="B155" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>122289580</v>
       </c>
       <c r="B156" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>122289562</v>
       </c>
       <c r="B170" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>122289769</v>
       </c>
       <c r="B171" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>122289534</v>
       </c>
       <c r="B183" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>122289560</v>
       </c>
       <c r="B184" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>122289537</v>
       </c>
       <c r="B185" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>122289533</v>
       </c>
       <c r="B186" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>122289584</v>
       </c>
       <c r="B187" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>122289575</v>
       </c>
       <c r="B188" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>122289565</v>
       </c>
       <c r="B189" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>122289585</v>
       </c>
       <c r="B190" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>122289592</v>
       </c>
       <c r="B218" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>122289581</v>
       </c>
       <c r="B219" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>122289588</v>
       </c>
       <c r="B220" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>122289615</v>
       </c>
       <c r="B245" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>122289564</v>
       </c>
       <c r="B246" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>122289570</v>
       </c>
       <c r="B247" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>122289586</v>
       </c>
       <c r="B262" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>122289576</v>
       </c>
       <c r="B271" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>122289577</v>
       </c>
       <c r="B272" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>122289573</v>
       </c>
       <c r="B273" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>122289574</v>
       </c>
       <c r="B274" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
